--- a/websdk-property/docs/data-collection-reconciliation.xlsx
+++ b/websdk-property/docs/data-collection-reconciliation.xlsx
@@ -12,14 +12,16 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Events" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Elements" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Issues" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="List Vars" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Issues" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'eVars'!$A$1:$G$54</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Props'!$A$1:$G$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Events'!$A$1:$E$39</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Data Elements'!$A$1:$D$72</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Data Issues'!$A$1:$F$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'List Vars'!$A$1:$F$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Data Issues'!$A$1:$F$12</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -5556,7 +5558,154 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>List Var</t>
+        </is>
+      </c>
+      <c r="B1" s="14" t="inlineStr">
+        <is>
+          <t>Report Suite Name</t>
+        </is>
+      </c>
+      <c r="C1" s="14" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="D1" s="14" t="inlineStr">
+        <is>
+          <t>Data Element(s)</t>
+        </is>
+      </c>
+      <c r="E1" s="14" t="inlineStr">
+        <is>
+          <t>Sent By Rule(s)</t>
+        </is>
+      </c>
+      <c r="F1" s="14" t="inlineStr">
+        <is>
+          <t>Notes / Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="15" t="inlineStr">
+        <is>
+          <t>list1</t>
+        </is>
+      </c>
+      <c r="B2" s="15" t="inlineStr">
+        <is>
+          <t>(config not captured — see note)</t>
+        </is>
+      </c>
+      <c r="C2" s="16" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D2" s="17" t="inlineStr">
+        <is>
+          <t>Form: Error Name; Page: Error</t>
+        </is>
+      </c>
+      <c r="E2" s="17" t="inlineStr">
+        <is>
+          <t>Form Error Tracking; Global Page Load Rule; Site Error</t>
+        </is>
+      </c>
+      <c r="F2" s="17" t="inlineStr">
+        <is>
+          <t>SHARED list: carries Form: Error Name + Page: Error from different rules (a unified error list). Parity with the source property — confirm with the analytics owner it is intended, not a collision.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="15" t="inlineStr">
+        <is>
+          <t>list2</t>
+        </is>
+      </c>
+      <c r="B3" s="15" t="inlineStr">
+        <is>
+          <t>(config not captured — see note)</t>
+        </is>
+      </c>
+      <c r="C3" s="16" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D3" s="17" t="inlineStr">
+        <is>
+          <t>Content: Hidden Tags</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>Global Page Load Rule</t>
+        </is>
+      </c>
+      <c r="F3" s="17" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="24" t="inlineStr">
+        <is>
+          <t>list3</t>
+        </is>
+      </c>
+      <c r="B4" s="24" t="inlineStr">
+        <is>
+          <t>(config not captured)</t>
+        </is>
+      </c>
+      <c r="C4" s="25" t="inlineStr">
+        <is>
+          <t>Defined, old property never sent</t>
+        </is>
+      </c>
+      <c r="D4" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E4" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="26" t="inlineStr">
+        <is>
+          <t>Not populated by this build. Adobe supports list1-3; provide the report suite List Variables config (Admin &gt; Report Suite &gt; Edit Settings &gt; Conversion &gt; List Variables) to reconcile names/delimiters.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F4"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5875,32 +6024,62 @@
       </c>
       <c r="B11" s="33" t="inlineStr">
         <is>
+          <t>list1 shared across error types</t>
+        </is>
+      </c>
+      <c r="C11" s="34" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D11" s="34" t="inlineStr">
+        <is>
+          <t>list1 · Page: Error · Form: Error Name</t>
+        </is>
+      </c>
+      <c r="E11" s="34" t="inlineStr">
+        <is>
+          <t>list1 carries Site Error (page views + Site Error rule) AND Form Error Name (Form Error Tracking) — a unified error list. Carried from the source property (parity).</t>
+        </is>
+      </c>
+      <c r="F11" s="34" t="inlineStr">
+        <is>
+          <t>Confirm with the analytics owner that list1 is intended as a combined error list. Provide the report suite List Variables config to reconcile names/delimiters and confirm list3 status.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="33" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="33" t="inlineStr">
+        <is>
           <t>Empty values omitted</t>
         </is>
       </c>
-      <c r="C11" s="34" t="inlineStr">
+      <c r="C12" s="34" t="inlineStr">
         <is>
           <t>Info</t>
         </is>
       </c>
-      <c r="D11" s="34" t="inlineStr">
+      <c r="D12" s="34" t="inlineStr">
         <is>
           <t>All payloads</t>
         </is>
       </c>
-      <c r="E11" s="34" t="inlineStr">
+      <c r="E12" s="34" t="inlineStr">
         <is>
           <t>The Web SDK build omits empty values, whereas the old XDM elements could emit empty strings. Beacons are cleaner but hit-level QA diffs will show absent-vs-empty differences.</t>
         </is>
       </c>
-      <c r="F11" s="34" t="inlineStr">
+      <c r="F12" s="34" t="inlineStr">
         <is>
           <t>Expected behavior — note for anyone comparing old vs new beacons during QA.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F11"/>
+  <autoFilter ref="A1:F12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/websdk-property/docs/data-collection-reconciliation.xlsx
+++ b/websdk-property/docs/data-collection-reconciliation.xlsx
@@ -30,7 +30,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -137,13 +137,22 @@
     </font>
     <font>
       <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00808080"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <b val="1"/>
     </font>
     <font>
       <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="001F4E78"/>
+      <sz val="10"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -185,6 +194,11 @@
         <fgColor rgb="00FFE699"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -212,23 +226,82 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -657,14 +730,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="95" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="88" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -691,174 +766,250 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Status legend</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="26" customHeight="1">
+          <t>Status legend &amp; counts</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
+          <t>Counts show how many of each variable / element carry that status. Full detail is on the tabs below.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>eVars</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>Props</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>Lists</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>Data El.</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>What it means</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="n">
+        <v>43</v>
+      </c>
+      <c r="C9" s="9" t="n">
+        <v>19</v>
+      </c>
+      <c r="D9" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="E9" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" s="9" t="n">
+        <v>60</v>
+      </c>
+      <c r="G9" s="10" t="inlineStr">
         <is>
           <t>Element feeds the variable and a rule sends it — data is collected.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="26" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>No data (element is a no-op)</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B10" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="G10" s="13" t="inlineStr">
         <is>
           <t>Element is wired but returns no value (no-op) — the variable never populates. Decision needed.</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>Not wired (orphan element)</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>Element exists but is not sent to any variable (or the variable has no element).</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="26" customHeight="1">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="B11" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="G11" s="16" t="inlineStr">
+        <is>
+          <t>Element exists but is not sent to any variable (data-element-side only).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="17" t="inlineStr">
         <is>
           <t>Defined, old property never sent</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B12" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="C12" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="19" t="inlineStr">
         <is>
           <t>Defined in the report suite but the old property never populated it (parity — stays empty).</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="26" customHeight="1">
-      <c r="A10" s="10" t="inlineStr">
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="20" t="inlineStr">
         <is>
           <t>Not implemented (never built)</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B13" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="C13" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="E13" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="22" t="inlineStr">
         <is>
           <t>Defined in the report suite but never built anywhere — net-new scope if wanted (e.g. Audio).</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="26" customHeight="1">
-      <c r="A11" s="11" t="inlineStr">
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="23" t="inlineStr">
         <is>
           <t>Excluded by design</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B14" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="25" t="inlineStr">
         <is>
           <t>Intentionally not populated under Web SDK (ECID — the SDK manages identity).</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>Summary</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="12" t="inlineStr">
-        <is>
-          <t>Dimension</t>
-        </is>
-      </c>
-      <c r="B14" s="12" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="C14" s="12" t="inlineStr">
-        <is>
-          <t>No-op / deferred</t>
-        </is>
-      </c>
-      <c r="D14" s="12" t="inlineStr">
-        <is>
-          <t>Not populated / excluded</t>
-        </is>
-      </c>
-      <c r="E14" s="12" t="inlineStr">
-        <is>
-          <t>Not implemented</t>
-        </is>
-      </c>
-    </row>
     <row r="15">
-      <c r="A15" s="13" t="inlineStr">
-        <is>
-          <t>eVars (53)</t>
-        </is>
-      </c>
-      <c r="B15" s="13" t="n">
-        <v>43</v>
-      </c>
-      <c r="C15" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="D15" s="13" t="n">
-        <v>4</v>
-      </c>
-      <c r="E15" s="13" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="13" t="inlineStr">
-        <is>
-          <t>Props (20)</t>
-        </is>
-      </c>
-      <c r="B16" s="13" t="n">
-        <v>19</v>
-      </c>
-      <c r="C16" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E16" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="13" t="inlineStr">
-        <is>
-          <t>Events (38)</t>
-        </is>
-      </c>
-      <c r="B17" s="13" t="n">
-        <v>30</v>
-      </c>
-      <c r="C17" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D17" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="E17" s="13" t="n">
-        <v>5</v>
+      <c r="A15" s="26" t="inlineStr">
+        <is>
+          <t>Total (defined)</t>
+        </is>
+      </c>
+      <c r="B15" s="27" t="n">
+        <v>53</v>
+      </c>
+      <c r="C15" s="27" t="n">
+        <v>20</v>
+      </c>
+      <c r="D15" s="27" t="n">
+        <v>38</v>
+      </c>
+      <c r="E15" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="F15" s="27" t="n">
+        <v>71</v>
+      </c>
+      <c r="G15" s="26" t="inlineStr"/>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="28" t="inlineStr">
+        <is>
+          <t>Bottom line: migration is at full parity — every variable the old property populated, the new build populates. The non-green rows are report-suite definitions the old property never used (client decisions), not migration gaps.</t>
+        </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A17:G17"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -882,1720 +1033,1720 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="14" t="inlineStr">
+      <c r="A1" s="29" t="inlineStr">
         <is>
           <t>eVar #</t>
         </is>
       </c>
-      <c r="B1" s="14" t="inlineStr">
+      <c r="B1" s="29" t="inlineStr">
         <is>
           <t>Report Suite Name</t>
         </is>
       </c>
-      <c r="C1" s="14" t="inlineStr">
+      <c r="C1" s="29" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="D1" s="14" t="inlineStr">
+      <c r="D1" s="29" t="inlineStr">
         <is>
           <t>Data Element(s)</t>
         </is>
       </c>
-      <c r="E1" s="14" t="inlineStr">
+      <c r="E1" s="29" t="inlineStr">
         <is>
           <t>Sent By Rule(s)</t>
         </is>
       </c>
-      <c r="F1" s="14" t="inlineStr">
+      <c r="F1" s="29" t="inlineStr">
         <is>
           <t>Data Element Source</t>
         </is>
       </c>
-      <c r="G1" s="14" t="inlineStr">
+      <c r="G1" s="29" t="inlineStr">
         <is>
           <t>Notes / Issue</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="n">
+      <c r="A2" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="15" t="inlineStr">
+      <c r="B2" s="30" t="inlineStr">
         <is>
           <t>Domain</t>
         </is>
       </c>
-      <c r="C2" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D2" s="17" t="inlineStr">
+      <c r="C2" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D2" s="32" t="inlineStr">
         <is>
           <t>Site: Domain</t>
         </is>
       </c>
-      <c r="E2" s="17" t="inlineStr">
+      <c r="E2" s="32" t="inlineStr">
         <is>
           <t>Global Page Load Rule</t>
         </is>
       </c>
-      <c r="F2" s="17" t="inlineStr">
+      <c r="F2" s="32" t="inlineStr">
         <is>
           <t>web.webPageDetails.site</t>
         </is>
       </c>
-      <c r="G2" s="17" t="inlineStr"/>
+      <c r="G2" s="32" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="n">
+      <c r="A3" s="30" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="15" t="inlineStr">
+      <c r="B3" s="30" t="inlineStr">
         <is>
           <t>Previous Page Name</t>
         </is>
       </c>
-      <c r="C3" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D3" s="17" t="inlineStr">
+      <c r="C3" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D3" s="32" t="inlineStr">
         <is>
           <t>Plugin: Previous Page Name</t>
         </is>
       </c>
-      <c r="E3" s="17" t="inlineStr">
+      <c r="E3" s="32" t="inlineStr">
         <is>
           <t>Global Page Load Rule</t>
         </is>
       </c>
-      <c r="F3" s="17" t="inlineStr">
+      <c r="F3" s="32" t="inlineStr">
         <is>
           <t>cwsdkp-getpreviousvalue</t>
         </is>
       </c>
-      <c r="G3" s="17" t="inlineStr"/>
+      <c r="G3" s="32" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="n">
+      <c r="A4" s="30" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="B4" s="30" t="inlineStr">
         <is>
           <t>Page Name</t>
         </is>
       </c>
-      <c r="C4" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="C4" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D4" s="32" t="inlineStr">
         <is>
           <t>Page: Name</t>
         </is>
       </c>
-      <c r="E4" s="17" t="inlineStr">
+      <c r="E4" s="32" t="inlineStr">
         <is>
           <t>Global Page Load Rule</t>
         </is>
       </c>
-      <c r="F4" s="17" t="inlineStr">
+      <c r="F4" s="32" t="inlineStr">
         <is>
           <t>web.webPageDetails.pageName</t>
         </is>
       </c>
-      <c r="G4" s="17" t="inlineStr"/>
+      <c r="G4" s="32" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="n">
+      <c r="A5" s="30" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B5" s="30" t="inlineStr">
         <is>
           <t>Site Section</t>
         </is>
       </c>
-      <c r="C5" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="C5" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D5" s="32" t="inlineStr">
         <is>
           <t>Site: Section</t>
         </is>
       </c>
-      <c r="E5" s="17" t="inlineStr">
+      <c r="E5" s="32" t="inlineStr">
         <is>
           <t>Global Page Load Rule</t>
         </is>
       </c>
-      <c r="F5" s="17" t="inlineStr">
+      <c r="F5" s="32" t="inlineStr">
         <is>
           <t>web.webPageDetails.siteSection</t>
         </is>
       </c>
-      <c r="G5" s="17" t="inlineStr"/>
+      <c r="G5" s="32" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="n">
+      <c r="A6" s="33" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="33" t="inlineStr">
         <is>
           <t>Internal Campaign</t>
         </is>
       </c>
-      <c r="C6" s="19" t="inlineStr">
+      <c r="C6" s="34" t="inlineStr">
         <is>
           <t>No data (element is a no-op)</t>
         </is>
       </c>
-      <c r="D6" s="20" t="inlineStr">
+      <c r="D6" s="35" t="inlineStr">
         <is>
           <t>Campaign: Internal</t>
         </is>
       </c>
-      <c r="E6" s="20" t="inlineStr">
+      <c r="E6" s="35" t="inlineStr">
         <is>
           <t>Global Page Load Rule</t>
         </is>
       </c>
-      <c r="F6" s="20" t="inlineStr">
+      <c r="F6" s="35" t="inlineStr">
         <is>
           <t>custom code</t>
         </is>
       </c>
-      <c r="G6" s="20" t="inlineStr">
+      <c r="G6" s="35" t="inlineStr">
         <is>
           <t>Element wired but returns no value — variable never populates.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="n">
+      <c r="A7" s="30" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" s="30" t="inlineStr">
         <is>
           <t>Internal Search Term</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="C7" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D7" s="32" t="inlineStr">
         <is>
           <t>Search: Term</t>
         </is>
       </c>
-      <c r="E7" s="17" t="inlineStr">
+      <c r="E7" s="32" t="inlineStr">
         <is>
           <t>Internal Search Click; Internal Search ClickThrough; Null Search Tracking; Search Close Click</t>
         </is>
       </c>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="F7" s="32" t="inlineStr">
         <is>
           <t>web.webInteractions.searchTerm</t>
         </is>
       </c>
-      <c r="G7" s="17" t="inlineStr"/>
+      <c r="G7" s="32" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="n">
+      <c r="A8" s="30" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B8" s="30" t="inlineStr">
         <is>
           <t># Search Results</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="C8" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D8" s="32" t="inlineStr">
         <is>
           <t>Search: Results</t>
         </is>
       </c>
-      <c r="E8" s="17" t="inlineStr">
+      <c r="E8" s="32" t="inlineStr">
         <is>
           <t>Internal Search Click; Null Search Tracking; Search Close Click</t>
         </is>
       </c>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="F8" s="32" t="inlineStr">
         <is>
           <t>web.webInteractions.searchResults</t>
         </is>
       </c>
-      <c r="G8" s="17" t="inlineStr"/>
+      <c r="G8" s="32" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="n">
+      <c r="A9" s="30" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="15" t="inlineStr">
+      <c r="B9" s="30" t="inlineStr">
         <is>
           <t>Search Results Page Type</t>
         </is>
       </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="C9" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D9" s="32" t="inlineStr">
         <is>
           <t>Search: Result Page Type</t>
         </is>
       </c>
-      <c r="E9" s="17" t="inlineStr">
+      <c r="E9" s="32" t="inlineStr">
         <is>
           <t>Internal Search Click; Null Search Tracking; Search Close Click</t>
         </is>
       </c>
-      <c r="F9" s="17" t="inlineStr">
+      <c r="F9" s="32" t="inlineStr">
         <is>
           <t>internalSearchInfo.searchResultPageType</t>
         </is>
       </c>
-      <c r="G9" s="17" t="inlineStr"/>
+      <c r="G9" s="32" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="n">
+      <c r="A10" s="30" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="15" t="inlineStr">
+      <c r="B10" s="30" t="inlineStr">
         <is>
           <t>Content Type</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="C10" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D10" s="32" t="inlineStr">
         <is>
           <t>Content: Type</t>
         </is>
       </c>
-      <c r="E10" s="17" t="inlineStr">
+      <c r="E10" s="32" t="inlineStr">
         <is>
           <t>Global Page Load Rule</t>
         </is>
       </c>
-      <c r="F10" s="17" t="inlineStr">
+      <c r="F10" s="32" t="inlineStr">
         <is>
           <t>web.webPageDetails.pageType</t>
         </is>
       </c>
-      <c r="G10" s="17" t="inlineStr"/>
+      <c r="G10" s="32" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="n">
+      <c r="A11" s="30" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="15" t="inlineStr">
+      <c r="B11" s="30" t="inlineStr">
         <is>
           <t>Form Name</t>
         </is>
       </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="C11" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D11" s="32" t="inlineStr">
         <is>
           <t>Form: Name</t>
         </is>
       </c>
-      <c r="E11" s="17" t="inlineStr">
+      <c r="E11" s="32" t="inlineStr">
         <is>
           <t>Form Complete; Form Error Tracking; Form Start</t>
         </is>
       </c>
-      <c r="F11" s="17" t="inlineStr">
+      <c r="F11" s="32" t="inlineStr">
         <is>
           <t>web.webInteractions.formName</t>
         </is>
       </c>
-      <c r="G11" s="17" t="inlineStr"/>
+      <c r="G11" s="32" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="n">
+      <c r="A12" s="30" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="15" t="inlineStr">
+      <c r="B12" s="30" t="inlineStr">
         <is>
           <t>Video Title</t>
         </is>
       </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="C12" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D12" s="32" t="inlineStr">
         <is>
           <t>Video: Name</t>
         </is>
       </c>
-      <c r="E12" s="17" t="inlineStr">
+      <c r="E12" s="32" t="inlineStr">
         <is>
           <t>Video 100 percentage complete; Video 25 percentage complete; Video 50 percentage complete; Video 75 percentage complete; Video Pause; Video Start</t>
         </is>
       </c>
-      <c r="F12" s="17" t="inlineStr">
+      <c r="F12" s="32" t="inlineStr">
         <is>
           <t>web.webInteractions.video.title</t>
         </is>
       </c>
-      <c r="G12" s="17" t="inlineStr"/>
+      <c r="G12" s="32" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="n">
+      <c r="A13" s="30" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="15" t="inlineStr">
+      <c r="B13" s="30" t="inlineStr">
         <is>
           <t>Page URL</t>
         </is>
       </c>
-      <c r="C13" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D13" s="17" t="inlineStr">
+      <c r="C13" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D13" s="32" t="inlineStr">
         <is>
           <t>Page: URL</t>
         </is>
       </c>
-      <c r="E13" s="17" t="inlineStr">
+      <c r="E13" s="32" t="inlineStr">
         <is>
           <t>Global Page Load Rule</t>
         </is>
       </c>
-      <c r="F13" s="17" t="inlineStr">
+      <c r="F13" s="32" t="inlineStr">
         <is>
           <t>web.webPageDetails.pageUrl</t>
         </is>
       </c>
-      <c r="G13" s="17" t="inlineStr"/>
+      <c r="G13" s="32" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="n">
+      <c r="A14" s="30" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="15" t="inlineStr">
+      <c r="B14" s="30" t="inlineStr">
         <is>
           <t>Page Query String</t>
         </is>
       </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D14" s="17" t="inlineStr">
+      <c r="C14" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D14" s="32" t="inlineStr">
         <is>
           <t>Core: Page Query String</t>
         </is>
       </c>
-      <c r="E14" s="17" t="inlineStr">
+      <c r="E14" s="32" t="inlineStr">
         <is>
           <t>Global Page Load Rule</t>
         </is>
       </c>
-      <c r="F14" s="17" t="inlineStr">
+      <c r="F14" s="32" t="inlineStr">
         <is>
           <t>custom code</t>
         </is>
       </c>
-      <c r="G14" s="17" t="inlineStr"/>
+      <c r="G14" s="32" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="21" t="n">
+      <c r="A15" s="36" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="21" t="inlineStr">
+      <c r="B15" s="36" t="inlineStr">
         <is>
           <t>ECID</t>
         </is>
       </c>
-      <c r="C15" s="22" t="inlineStr">
+      <c r="C15" s="37" t="inlineStr">
         <is>
           <t>Excluded by design</t>
         </is>
       </c>
-      <c r="D15" s="23" t="inlineStr">
+      <c r="D15" s="38" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E15" s="23" t="inlineStr">
+      <c r="E15" s="38" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F15" s="23" t="inlineStr">
+      <c r="F15" s="38" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G15" s="23" t="inlineStr">
+      <c r="G15" s="38" t="inlineStr">
         <is>
           <t>ECID intentionally not captured — Web SDK manages identity natively. Source element was a broken recursive stub.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="n">
+      <c r="A16" s="33" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="18" t="inlineStr">
+      <c r="B16" s="33" t="inlineStr">
         <is>
           <t>User Type</t>
         </is>
       </c>
-      <c r="C16" s="19" t="inlineStr">
+      <c r="C16" s="34" t="inlineStr">
         <is>
           <t>No data (element is a no-op)</t>
         </is>
       </c>
-      <c r="D16" s="20" t="inlineStr">
+      <c r="D16" s="35" t="inlineStr">
         <is>
           <t>User: Type</t>
         </is>
       </c>
-      <c r="E16" s="20" t="inlineStr">
+      <c r="E16" s="35" t="inlineStr">
         <is>
           <t>Global Page Load Rule</t>
         </is>
       </c>
-      <c r="F16" s="20" t="inlineStr">
+      <c r="F16" s="35" t="inlineStr">
         <is>
           <t>custom code</t>
         </is>
       </c>
-      <c r="G16" s="20" t="inlineStr">
+      <c r="G16" s="35" t="inlineStr">
         <is>
           <t>Element wired but returns no value — variable never populates.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="24" t="n">
+      <c r="A17" s="39" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="24" t="inlineStr">
+      <c r="B17" s="39" t="inlineStr">
         <is>
           <t>Internal Campaign Displayed</t>
         </is>
       </c>
-      <c r="C17" s="25" t="inlineStr">
+      <c r="C17" s="40" t="inlineStr">
         <is>
           <t>Defined, old property never sent</t>
         </is>
       </c>
-      <c r="D17" s="26" t="inlineStr">
+      <c r="D17" s="41" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E17" s="26" t="inlineStr">
+      <c r="E17" s="41" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F17" s="26" t="inlineStr">
+      <c r="F17" s="41" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G17" s="26" t="inlineStr">
+      <c r="G17" s="41" t="inlineStr">
         <is>
           <t>Old property never sent this.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="n">
+      <c r="A18" s="30" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="15" t="inlineStr">
+      <c r="B18" s="30" t="inlineStr">
         <is>
           <t>Social Link Name</t>
         </is>
       </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D18" s="17" t="inlineStr">
+      <c r="C18" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D18" s="32" t="inlineStr">
         <is>
           <t>Social: Interaction Info</t>
         </is>
       </c>
-      <c r="E18" s="17" t="inlineStr">
+      <c r="E18" s="32" t="inlineStr">
         <is>
           <t>Social Interaction Tracking</t>
         </is>
       </c>
-      <c r="F18" s="17" t="inlineStr">
+      <c r="F18" s="32" t="inlineStr">
         <is>
           <t>web.webInteractions.socialInteractionInfo</t>
         </is>
       </c>
-      <c r="G18" s="17" t="inlineStr"/>
+      <c r="G18" s="32" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="n">
+      <c r="A19" s="30" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="15" t="inlineStr">
+      <c r="B19" s="30" t="inlineStr">
         <is>
           <t>Language</t>
         </is>
       </c>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D19" s="17" t="inlineStr">
+      <c r="C19" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D19" s="32" t="inlineStr">
         <is>
           <t>Geo: Language</t>
         </is>
       </c>
-      <c r="E19" s="17" t="inlineStr">
+      <c r="E19" s="32" t="inlineStr">
         <is>
           <t>Global Page Load Rule</t>
         </is>
       </c>
-      <c r="F19" s="17" t="inlineStr">
+      <c r="F19" s="32" t="inlineStr">
         <is>
           <t>web.webPageDetails.language</t>
         </is>
       </c>
-      <c r="G19" s="17" t="inlineStr"/>
+      <c r="G19" s="32" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="n">
+      <c r="A20" s="30" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="15" t="inlineStr">
+      <c r="B20" s="30" t="inlineStr">
         <is>
           <t>Email Registration Location</t>
         </is>
       </c>
-      <c r="C20" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D20" s="17" t="inlineStr">
+      <c r="C20" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D20" s="32" t="inlineStr">
         <is>
           <t>Form: Location</t>
         </is>
       </c>
-      <c r="E20" s="17" t="inlineStr">
+      <c r="E20" s="32" t="inlineStr">
         <is>
           <t>Form Complete; Form Error Tracking; Form Start</t>
         </is>
       </c>
-      <c r="F20" s="17" t="inlineStr">
+      <c r="F20" s="32" t="inlineStr">
         <is>
           <t>web.webInteractions.formLocation</t>
         </is>
       </c>
-      <c r="G20" s="17" t="inlineStr"/>
+      <c r="G20" s="32" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="15" t="n">
+      <c r="A21" s="30" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="15" t="inlineStr">
+      <c r="B21" s="30" t="inlineStr">
         <is>
           <t>Scroll Depth</t>
         </is>
       </c>
-      <c r="C21" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D21" s="17" t="inlineStr">
+      <c r="C21" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D21" s="32" t="inlineStr">
         <is>
           <t>Scroll Depth</t>
         </is>
       </c>
-      <c r="E21" s="17" t="inlineStr">
+      <c r="E21" s="32" t="inlineStr">
         <is>
           <t>Scroll 100 percentage; Scroll 25 percentage; Scroll 50 percentage; Scroll 75 percentage</t>
         </is>
       </c>
-      <c r="F21" s="17" t="inlineStr">
+      <c r="F21" s="32" t="inlineStr">
         <is>
           <t>web.webInteractions.scrollInfo.depth</t>
         </is>
       </c>
-      <c r="G21" s="17" t="inlineStr"/>
+      <c r="G21" s="32" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="15" t="n">
+      <c r="A22" s="30" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="15" t="inlineStr">
+      <c r="B22" s="30" t="inlineStr">
         <is>
           <t>Redirect Link</t>
         </is>
       </c>
-      <c r="C22" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D22" s="17" t="inlineStr">
+      <c r="C22" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D22" s="32" t="inlineStr">
         <is>
           <t>Link: Redirect Text</t>
         </is>
       </c>
-      <c r="E22" s="17" t="inlineStr">
+      <c r="E22" s="32" t="inlineStr">
         <is>
           <t>Redirect Link Click Tracking</t>
         </is>
       </c>
-      <c r="F22" s="17" t="inlineStr">
+      <c r="F22" s="32" t="inlineStr">
         <is>
           <t>web.webInteractions.RedirectLinkText</t>
         </is>
       </c>
-      <c r="G22" s="17" t="inlineStr"/>
+      <c r="G22" s="32" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="15" t="n">
+      <c r="A23" s="30" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="15" t="inlineStr">
+      <c r="B23" s="30" t="inlineStr">
         <is>
           <t>CTA Button Text</t>
         </is>
       </c>
-      <c r="C23" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D23" s="17" t="inlineStr">
+      <c r="C23" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D23" s="32" t="inlineStr">
         <is>
           <t>Link: CTA Button Name</t>
         </is>
       </c>
-      <c r="E23" s="17" t="inlineStr">
+      <c r="E23" s="32" t="inlineStr">
         <is>
           <t>Global CTA Button Tracking</t>
         </is>
       </c>
-      <c r="F23" s="17" t="inlineStr">
+      <c r="F23" s="32" t="inlineStr">
         <is>
           <t>web.webInteractions.CTAButtonName</t>
         </is>
       </c>
-      <c r="G23" s="17" t="inlineStr"/>
+      <c r="G23" s="32" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="15" t="n">
+      <c r="A24" s="30" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="15" t="inlineStr">
+      <c r="B24" s="30" t="inlineStr">
         <is>
           <t>Destination Link</t>
         </is>
       </c>
-      <c r="C24" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D24" s="17" t="inlineStr">
+      <c r="C24" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D24" s="32" t="inlineStr">
         <is>
           <t>Link: Destination</t>
         </is>
       </c>
-      <c r="E24" s="17" t="inlineStr">
+      <c r="E24" s="32" t="inlineStr">
         <is>
           <t>Amazon Redirect Link Click; Global CTA Button Tracking; Redirect Link Click Tracking</t>
         </is>
       </c>
-      <c r="F24" s="17" t="inlineStr">
+      <c r="F24" s="32" t="inlineStr">
         <is>
           <t>web.webInteractions.DestinationLink</t>
         </is>
       </c>
-      <c r="G24" s="17" t="inlineStr"/>
+      <c r="G24" s="32" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="15" t="n">
+      <c r="A25" s="30" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="15" t="inlineStr">
+      <c r="B25" s="30" t="inlineStr">
         <is>
           <t>Menu Link</t>
         </is>
       </c>
-      <c r="C25" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D25" s="17" t="inlineStr">
+      <c r="C25" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D25" s="32" t="inlineStr">
         <is>
           <t>Link: Menu Name</t>
         </is>
       </c>
-      <c r="E25" s="17" t="inlineStr">
+      <c r="E25" s="32" t="inlineStr">
         <is>
           <t>Menu Link Click Tracking</t>
         </is>
       </c>
-      <c r="F25" s="17" t="inlineStr">
+      <c r="F25" s="32" t="inlineStr">
         <is>
           <t>web.webInteractions.MenuLinkName</t>
         </is>
       </c>
-      <c r="G25" s="17" t="inlineStr"/>
+      <c r="G25" s="32" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="15" t="n">
+      <c r="A26" s="30" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="15" t="inlineStr">
+      <c r="B26" s="30" t="inlineStr">
         <is>
           <t>Publish Date</t>
         </is>
       </c>
-      <c r="C26" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D26" s="17" t="inlineStr">
+      <c r="C26" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D26" s="32" t="inlineStr">
         <is>
           <t>Content: Publish Date</t>
         </is>
       </c>
-      <c r="E26" s="17" t="inlineStr">
+      <c r="E26" s="32" t="inlineStr">
         <is>
           <t>Global Page Load Rule</t>
         </is>
       </c>
-      <c r="F26" s="17" t="inlineStr">
+      <c r="F26" s="32" t="inlineStr">
         <is>
           <t>web.webPageDetails.publishDate</t>
         </is>
       </c>
-      <c r="G26" s="17" t="inlineStr"/>
+      <c r="G26" s="32" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="24" t="n">
+      <c r="A27" s="39" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="24" t="inlineStr">
+      <c r="B27" s="39" t="inlineStr">
         <is>
           <t>Content Type</t>
         </is>
       </c>
-      <c r="C27" s="25" t="inlineStr">
+      <c r="C27" s="40" t="inlineStr">
         <is>
           <t>Defined, old property never sent</t>
         </is>
       </c>
-      <c r="D27" s="26" t="inlineStr">
+      <c r="D27" s="41" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E27" s="26" t="inlineStr">
+      <c r="E27" s="41" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F27" s="26" t="inlineStr">
+      <c r="F27" s="41" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G27" s="26" t="inlineStr">
+      <c r="G27" s="41" t="inlineStr">
         <is>
           <t>Duplicate label of eVar9 (which is populated).</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="15" t="n">
+      <c r="A28" s="30" t="n">
         <v>27</v>
       </c>
-      <c r="B28" s="15" t="inlineStr">
+      <c r="B28" s="30" t="inlineStr">
         <is>
           <t>Filter</t>
         </is>
       </c>
-      <c r="C28" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D28" s="17" t="inlineStr">
+      <c r="C28" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D28" s="32" t="inlineStr">
         <is>
           <t>News: Filter</t>
         </is>
       </c>
-      <c r="E28" s="17" t="inlineStr">
+      <c r="E28" s="32" t="inlineStr">
         <is>
           <t>Filter Click Tracking</t>
         </is>
       </c>
-      <c r="F28" s="17" t="inlineStr">
+      <c r="F28" s="32" t="inlineStr">
         <is>
           <t>web.webInteractions.Filter</t>
         </is>
       </c>
-      <c r="G28" s="17" t="inlineStr"/>
+      <c r="G28" s="32" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="15" t="n">
+      <c r="A29" s="30" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="15" t="inlineStr">
+      <c r="B29" s="30" t="inlineStr">
         <is>
           <t>Amazon Redirect Link</t>
         </is>
       </c>
-      <c r="C29" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D29" s="17" t="inlineStr">
+      <c r="C29" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D29" s="32" t="inlineStr">
         <is>
           <t>Link: Redirect Text</t>
         </is>
       </c>
-      <c r="E29" s="17" t="inlineStr">
+      <c r="E29" s="32" t="inlineStr">
         <is>
           <t>Amazon Redirect Link Click</t>
         </is>
       </c>
-      <c r="F29" s="17" t="inlineStr">
+      <c r="F29" s="32" t="inlineStr">
         <is>
           <t>web.webInteractions.RedirectLinkText</t>
         </is>
       </c>
-      <c r="G29" s="17" t="inlineStr"/>
+      <c r="G29" s="32" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="15" t="n">
+      <c r="A30" s="30" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="15" t="inlineStr">
+      <c r="B30" s="30" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="C30" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D30" s="17" t="inlineStr">
+      <c r="C30" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D30" s="32" t="inlineStr">
         <is>
           <t>Content: Category</t>
         </is>
       </c>
-      <c r="E30" s="17" t="inlineStr">
+      <c r="E30" s="32" t="inlineStr">
         <is>
           <t>Global Page Load Rule</t>
         </is>
       </c>
-      <c r="F30" s="17" t="inlineStr">
+      <c r="F30" s="32" t="inlineStr">
         <is>
           <t>web.webPageDetails.category</t>
         </is>
       </c>
-      <c r="G30" s="17" t="inlineStr"/>
+      <c r="G30" s="32" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="15" t="n">
+      <c r="A31" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="15" t="inlineStr">
+      <c r="B31" s="30" t="inlineStr">
         <is>
           <t>Tag Text</t>
         </is>
       </c>
-      <c r="C31" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D31" s="17" t="inlineStr">
+      <c r="C31" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D31" s="32" t="inlineStr">
         <is>
           <t>Content: Tags</t>
         </is>
       </c>
-      <c r="E31" s="17" t="inlineStr">
+      <c r="E31" s="32" t="inlineStr">
         <is>
           <t>Global Page Load Rule</t>
         </is>
       </c>
-      <c r="F31" s="17" t="inlineStr">
+      <c r="F31" s="32" t="inlineStr">
         <is>
           <t>web.webPageDetails.tags</t>
         </is>
       </c>
-      <c r="G31" s="17" t="inlineStr"/>
+      <c r="G31" s="32" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="24" t="n">
+      <c r="A32" s="39" t="n">
         <v>31</v>
       </c>
-      <c r="B32" s="24" t="inlineStr">
+      <c r="B32" s="39" t="inlineStr">
         <is>
           <t>MetaTags</t>
         </is>
       </c>
-      <c r="C32" s="25" t="inlineStr">
+      <c r="C32" s="40" t="inlineStr">
         <is>
           <t>Defined, old property never sent</t>
         </is>
       </c>
-      <c r="D32" s="26" t="inlineStr">
+      <c r="D32" s="41" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E32" s="26" t="inlineStr">
+      <c r="E32" s="41" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F32" s="26" t="inlineStr">
+      <c r="F32" s="41" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G32" s="26" t="inlineStr">
+      <c r="G32" s="41" t="inlineStr">
         <is>
           <t>Old property never sent this.</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="15" t="n">
+      <c r="A33" s="30" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="15" t="inlineStr">
+      <c r="B33" s="30" t="inlineStr">
         <is>
           <t>Search Result Selection</t>
         </is>
       </c>
-      <c r="C33" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D33" s="17" t="inlineStr">
+      <c r="C33" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D33" s="32" t="inlineStr">
         <is>
           <t>Search: Result Click Name</t>
         </is>
       </c>
-      <c r="E33" s="17" t="inlineStr">
+      <c r="E33" s="32" t="inlineStr">
         <is>
           <t>Internal Search ClickThrough</t>
         </is>
       </c>
-      <c r="F33" s="17" t="inlineStr">
+      <c r="F33" s="32" t="inlineStr">
         <is>
           <t>web.webInteractions.searchResultClickName</t>
         </is>
       </c>
-      <c r="G33" s="17" t="inlineStr"/>
+      <c r="G33" s="32" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="15" t="n">
+      <c r="A34" s="30" t="n">
         <v>33</v>
       </c>
-      <c r="B34" s="15" t="inlineStr">
+      <c r="B34" s="30" t="inlineStr">
         <is>
           <t>File Name</t>
         </is>
       </c>
-      <c r="C34" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D34" s="17" t="inlineStr">
+      <c r="C34" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D34" s="32" t="inlineStr">
         <is>
           <t>File: Name</t>
         </is>
       </c>
-      <c r="E34" s="17" t="inlineStr">
+      <c r="E34" s="32" t="inlineStr">
         <is>
           <t>File Download Tracking</t>
         </is>
       </c>
-      <c r="F34" s="17" t="inlineStr">
+      <c r="F34" s="32" t="inlineStr">
         <is>
           <t>web.webInteractions.FileName</t>
         </is>
       </c>
-      <c r="G34" s="17" t="inlineStr"/>
+      <c r="G34" s="32" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="15" t="n">
+      <c r="A35" s="30" t="n">
         <v>34</v>
       </c>
-      <c r="B35" s="15" t="inlineStr">
+      <c r="B35" s="30" t="inlineStr">
         <is>
           <t>File Type</t>
         </is>
       </c>
-      <c r="C35" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D35" s="17" t="inlineStr">
+      <c r="C35" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D35" s="32" t="inlineStr">
         <is>
           <t>File: Type</t>
         </is>
       </c>
-      <c r="E35" s="17" t="inlineStr">
+      <c r="E35" s="32" t="inlineStr">
         <is>
           <t>File Download Tracking</t>
         </is>
       </c>
-      <c r="F35" s="17" t="inlineStr">
+      <c r="F35" s="32" t="inlineStr">
         <is>
           <t>web.webInteractions.FileType</t>
         </is>
       </c>
-      <c r="G35" s="17" t="inlineStr"/>
+      <c r="G35" s="32" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="15" t="n">
+      <c r="A36" s="30" t="n">
         <v>35</v>
       </c>
-      <c r="B36" s="15" t="inlineStr">
+      <c r="B36" s="30" t="inlineStr">
         <is>
           <t>Video Type</t>
         </is>
       </c>
-      <c r="C36" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D36" s="17" t="inlineStr">
+      <c r="C36" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D36" s="32" t="inlineStr">
         <is>
           <t>Video: Type</t>
         </is>
       </c>
-      <c r="E36" s="17" t="inlineStr">
+      <c r="E36" s="32" t="inlineStr">
         <is>
           <t>Video 100 percentage complete; Video 50 percentage complete; Video 75 percentage complete; Video Start</t>
         </is>
       </c>
-      <c r="F36" s="17" t="inlineStr">
+      <c r="F36" s="32" t="inlineStr">
         <is>
           <t>web.webInteractions.VideoType</t>
         </is>
       </c>
-      <c r="G36" s="17" t="inlineStr"/>
+      <c r="G36" s="32" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="15" t="n">
+      <c r="A37" s="30" t="n">
         <v>37</v>
       </c>
-      <c r="B37" s="15" t="inlineStr">
+      <c r="B37" s="30" t="inlineStr">
         <is>
           <t>Visit Duration</t>
         </is>
       </c>
-      <c r="C37" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D37" s="17" t="inlineStr">
+      <c r="C37" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D37" s="32" t="inlineStr">
         <is>
           <t>Plugin: Visit Duration</t>
         </is>
       </c>
-      <c r="E37" s="17" t="inlineStr">
+      <c r="E37" s="32" t="inlineStr">
         <is>
           <t>Global Page Load Rule</t>
         </is>
       </c>
-      <c r="F37" s="17" t="inlineStr">
+      <c r="F37" s="32" t="inlineStr">
         <is>
           <t>cwsdkp-getvisitduration</t>
         </is>
       </c>
-      <c r="G37" s="17" t="inlineStr"/>
+      <c r="G37" s="32" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="15" t="n">
+      <c r="A38" s="30" t="n">
         <v>38</v>
       </c>
-      <c r="B38" s="15" t="inlineStr">
+      <c r="B38" s="30" t="inlineStr">
         <is>
           <t>UTM Source</t>
         </is>
       </c>
-      <c r="C38" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D38" s="17" t="inlineStr">
+      <c r="C38" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D38" s="32" t="inlineStr">
         <is>
           <t>UTM: Source</t>
         </is>
       </c>
-      <c r="E38" s="17" t="inlineStr">
+      <c r="E38" s="32" t="inlineStr">
         <is>
           <t>Global Page Load Rule</t>
         </is>
       </c>
-      <c r="F38" s="17" t="inlineStr">
+      <c r="F38" s="32" t="inlineStr">
         <is>
           <t>UTM_Source</t>
         </is>
       </c>
-      <c r="G38" s="17" t="inlineStr"/>
+      <c r="G38" s="32" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="15" t="n">
+      <c r="A39" s="30" t="n">
         <v>39</v>
       </c>
-      <c r="B39" s="15" t="inlineStr">
+      <c r="B39" s="30" t="inlineStr">
         <is>
           <t>UTM Medium</t>
         </is>
       </c>
-      <c r="C39" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D39" s="17" t="inlineStr">
+      <c r="C39" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D39" s="32" t="inlineStr">
         <is>
           <t>UTM: Medium</t>
         </is>
       </c>
-      <c r="E39" s="17" t="inlineStr">
+      <c r="E39" s="32" t="inlineStr">
         <is>
           <t>Global Page Load Rule</t>
         </is>
       </c>
-      <c r="F39" s="17" t="inlineStr">
+      <c r="F39" s="32" t="inlineStr">
         <is>
           <t>UTM_Medium</t>
         </is>
       </c>
-      <c r="G39" s="17" t="inlineStr"/>
+      <c r="G39" s="32" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="15" t="n">
+      <c r="A40" s="30" t="n">
         <v>40</v>
       </c>
-      <c r="B40" s="15" t="inlineStr">
+      <c r="B40" s="30" t="inlineStr">
         <is>
           <t>UTM Content</t>
         </is>
       </c>
-      <c r="C40" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D40" s="17" t="inlineStr">
+      <c r="C40" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D40" s="32" t="inlineStr">
         <is>
           <t>UTM: Content</t>
         </is>
       </c>
-      <c r="E40" s="17" t="inlineStr">
+      <c r="E40" s="32" t="inlineStr">
         <is>
           <t>Global Page Load Rule</t>
         </is>
       </c>
-      <c r="F40" s="17" t="inlineStr">
+      <c r="F40" s="32" t="inlineStr">
         <is>
           <t>UTM_Content</t>
         </is>
       </c>
-      <c r="G40" s="17" t="inlineStr"/>
+      <c r="G40" s="32" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="15" t="n">
+      <c r="A41" s="30" t="n">
         <v>41</v>
       </c>
-      <c r="B41" s="15" t="inlineStr">
+      <c r="B41" s="30" t="inlineStr">
         <is>
           <t>UTM Campaign</t>
         </is>
       </c>
-      <c r="C41" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D41" s="17" t="inlineStr">
+      <c r="C41" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D41" s="32" t="inlineStr">
         <is>
           <t>UTM: Campaign</t>
         </is>
       </c>
-      <c r="E41" s="17" t="inlineStr">
+      <c r="E41" s="32" t="inlineStr">
         <is>
           <t>Global Page Load Rule</t>
         </is>
       </c>
-      <c r="F41" s="17" t="inlineStr">
+      <c r="F41" s="32" t="inlineStr">
         <is>
           <t>UTM_Campaign</t>
         </is>
       </c>
-      <c r="G41" s="17" t="inlineStr"/>
+      <c r="G41" s="32" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="15" t="n">
+      <c r="A42" s="30" t="n">
         <v>42</v>
       </c>
-      <c r="B42" s="15" t="inlineStr">
+      <c r="B42" s="30" t="inlineStr">
         <is>
           <t>UTM Term</t>
         </is>
       </c>
-      <c r="C42" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D42" s="17" t="inlineStr">
+      <c r="C42" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D42" s="32" t="inlineStr">
         <is>
           <t>UTM: Term</t>
         </is>
       </c>
-      <c r="E42" s="17" t="inlineStr">
+      <c r="E42" s="32" t="inlineStr">
         <is>
           <t>Global Page Load Rule</t>
         </is>
       </c>
-      <c r="F42" s="17" t="inlineStr">
+      <c r="F42" s="32" t="inlineStr">
         <is>
           <t>UTM_Term</t>
         </is>
       </c>
-      <c r="G42" s="17" t="inlineStr"/>
+      <c r="G42" s="32" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="15" t="n">
+      <c r="A43" s="30" t="n">
         <v>43</v>
       </c>
-      <c r="B43" s="15" t="inlineStr">
+      <c r="B43" s="30" t="inlineStr">
         <is>
           <t>Related Tag Text</t>
         </is>
       </c>
-      <c r="C43" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D43" s="17" t="inlineStr">
+      <c r="C43" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D43" s="32" t="inlineStr">
         <is>
           <t>Link: Related Tag</t>
         </is>
       </c>
-      <c r="E43" s="17" t="inlineStr">
+      <c r="E43" s="32" t="inlineStr">
         <is>
           <t>Related Tag Click Tracking</t>
         </is>
       </c>
-      <c r="F43" s="17" t="inlineStr">
+      <c r="F43" s="32" t="inlineStr">
         <is>
           <t>web.webInteractions.TagLinkClick</t>
         </is>
       </c>
-      <c r="G43" s="17" t="inlineStr"/>
+      <c r="G43" s="32" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="15" t="n">
+      <c r="A44" s="30" t="n">
         <v>44</v>
       </c>
-      <c r="B44" s="15" t="inlineStr">
+      <c r="B44" s="30" t="inlineStr">
         <is>
           <t>More Amazon News Title</t>
         </is>
       </c>
-      <c r="C44" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D44" s="17" t="inlineStr">
+      <c r="C44" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D44" s="32" t="inlineStr">
         <is>
           <t>Link: More Amazon News</t>
         </is>
       </c>
-      <c r="E44" s="17" t="inlineStr">
+      <c r="E44" s="32" t="inlineStr">
         <is>
           <t>Amazon More News Tracking</t>
         </is>
       </c>
-      <c r="F44" s="17" t="inlineStr">
+      <c r="F44" s="32" t="inlineStr">
         <is>
           <t>web.webInteractions.moreAmazonNewsText</t>
         </is>
       </c>
-      <c r="G44" s="17" t="inlineStr"/>
+      <c r="G44" s="32" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="15" t="n">
+      <c r="A45" s="30" t="n">
         <v>45</v>
       </c>
-      <c r="B45" s="15" t="inlineStr">
+      <c r="B45" s="30" t="inlineStr">
         <is>
           <t>Stories Title</t>
         </is>
       </c>
-      <c r="C45" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D45" s="17" t="inlineStr">
+      <c r="C45" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D45" s="32" t="inlineStr">
         <is>
           <t>Link: Stories Text</t>
         </is>
       </c>
-      <c r="E45" s="17" t="inlineStr">
+      <c r="E45" s="32" t="inlineStr">
         <is>
           <t>Amazon Stories Link Click Tracking</t>
         </is>
       </c>
-      <c r="F45" s="17" t="inlineStr">
+      <c r="F45" s="32" t="inlineStr">
         <is>
           <t>web.webInteractions.storiesLinkText</t>
         </is>
       </c>
-      <c r="G45" s="17" t="inlineStr"/>
+      <c r="G45" s="32" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="15" t="n">
+      <c r="A46" s="30" t="n">
         <v>46</v>
       </c>
-      <c r="B46" s="15" t="inlineStr">
+      <c r="B46" s="30" t="inlineStr">
         <is>
           <t>Related Tags Link</t>
         </is>
       </c>
-      <c r="C46" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D46" s="17" t="inlineStr">
+      <c r="C46" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D46" s="32" t="inlineStr">
         <is>
           <t>Link: Related Tag URL</t>
         </is>
       </c>
-      <c r="E46" s="17" t="inlineStr">
+      <c r="E46" s="32" t="inlineStr">
         <is>
           <t>Related Tag Click Tracking</t>
         </is>
       </c>
-      <c r="F46" s="17" t="inlineStr">
+      <c r="F46" s="32" t="inlineStr">
         <is>
           <t>web.webInteractions.linkUrl</t>
         </is>
       </c>
-      <c r="G46" s="17" t="inlineStr"/>
+      <c r="G46" s="32" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="15" t="n">
+      <c r="A47" s="30" t="n">
         <v>47</v>
       </c>
-      <c r="B47" s="15" t="inlineStr">
+      <c r="B47" s="30" t="inlineStr">
         <is>
           <t>Country Code</t>
         </is>
       </c>
-      <c r="C47" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D47" s="17" t="inlineStr">
+      <c r="C47" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D47" s="32" t="inlineStr">
         <is>
           <t>Geo: Country</t>
         </is>
       </c>
-      <c r="E47" s="17" t="inlineStr">
+      <c r="E47" s="32" t="inlineStr">
         <is>
           <t>Global Page Load Rule</t>
         </is>
       </c>
-      <c r="F47" s="17" t="inlineStr">
+      <c r="F47" s="32" t="inlineStr">
         <is>
           <t>web.webPageDetails.country</t>
         </is>
       </c>
-      <c r="G47" s="17" t="inlineStr"/>
+      <c r="G47" s="32" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="15" t="n">
+      <c r="A48" s="30" t="n">
         <v>48</v>
       </c>
-      <c r="B48" s="15" t="inlineStr">
+      <c r="B48" s="30" t="inlineStr">
         <is>
           <t>Cookie Consent Selection</t>
         </is>
       </c>
-      <c r="C48" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D48" s="17" t="inlineStr">
+      <c r="C48" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D48" s="32" t="inlineStr">
         <is>
           <t>Consent: Selected</t>
         </is>
       </c>
-      <c r="E48" s="17" t="inlineStr">
+      <c r="E48" s="32" t="inlineStr">
         <is>
           <t>Consent Selection</t>
         </is>
       </c>
-      <c r="F48" s="17" t="inlineStr">
+      <c r="F48" s="32" t="inlineStr">
         <is>
           <t>web.webInteractions.cookieConsent.consentSelected</t>
         </is>
       </c>
-      <c r="G48" s="17" t="inlineStr"/>
+      <c r="G48" s="32" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="15" t="n">
+      <c r="A49" s="30" t="n">
         <v>49</v>
       </c>
-      <c r="B49" s="15" t="inlineStr">
+      <c r="B49" s="30" t="inlineStr">
         <is>
           <t>Map Name</t>
         </is>
       </c>
-      <c r="C49" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D49" s="17" t="inlineStr">
+      <c r="C49" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D49" s="32" t="inlineStr">
         <is>
           <t>Map: Name</t>
         </is>
       </c>
-      <c r="E49" s="17" t="inlineStr">
+      <c r="E49" s="32" t="inlineStr">
         <is>
           <t>Map Button Click; Map Button Close; Map Zoom In; Map Zoom Out</t>
         </is>
       </c>
-      <c r="F49" s="17" t="inlineStr">
+      <c r="F49" s="32" t="inlineStr">
         <is>
           <t>map.mapName</t>
         </is>
       </c>
-      <c r="G49" s="17" t="inlineStr"/>
+      <c r="G49" s="32" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="15" t="n">
+      <c r="A50" s="30" t="n">
         <v>50</v>
       </c>
-      <c r="B50" s="15" t="inlineStr">
+      <c r="B50" s="30" t="inlineStr">
         <is>
           <t>Map Button Name</t>
         </is>
       </c>
-      <c r="C50" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D50" s="17" t="inlineStr">
+      <c r="C50" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D50" s="32" t="inlineStr">
         <is>
           <t>Map: Button Name</t>
         </is>
       </c>
-      <c r="E50" s="17" t="inlineStr">
+      <c r="E50" s="32" t="inlineStr">
         <is>
           <t>Map Button Click; Map Button Close; Map Zoom In; Map Zoom Out</t>
         </is>
       </c>
-      <c r="F50" s="17" t="inlineStr">
+      <c r="F50" s="32" t="inlineStr">
         <is>
           <t>map.mapButtonName</t>
         </is>
       </c>
-      <c r="G50" s="17" t="inlineStr"/>
+      <c r="G50" s="32" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="27" t="n">
+      <c r="A51" s="42" t="n">
         <v>51</v>
       </c>
-      <c r="B51" s="27" t="inlineStr">
+      <c r="B51" s="42" t="inlineStr">
         <is>
           <t>Audio Title</t>
         </is>
       </c>
-      <c r="C51" s="28" t="inlineStr">
+      <c r="C51" s="43" t="inlineStr">
         <is>
           <t>Not implemented (never built)</t>
         </is>
       </c>
-      <c r="D51" s="29" t="inlineStr">
+      <c r="D51" s="44" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E51" s="29" t="inlineStr">
+      <c r="E51" s="44" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F51" s="29" t="inlineStr">
+      <c r="F51" s="44" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G51" s="29" t="inlineStr">
+      <c r="G51" s="44" t="inlineStr">
         <is>
           <t>AUDIO: defined in report suite but never implemented in the old Launch property. Net-new scope (Web SDK media collection).</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="27" t="n">
+      <c r="A52" s="42" t="n">
         <v>52</v>
       </c>
-      <c r="B52" s="27" t="inlineStr">
+      <c r="B52" s="42" t="inlineStr">
         <is>
           <t>Audio Action</t>
         </is>
       </c>
-      <c r="C52" s="28" t="inlineStr">
+      <c r="C52" s="43" t="inlineStr">
         <is>
           <t>Not implemented (never built)</t>
         </is>
       </c>
-      <c r="D52" s="29" t="inlineStr">
+      <c r="D52" s="44" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E52" s="29" t="inlineStr">
+      <c r="E52" s="44" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F52" s="29" t="inlineStr">
+      <c r="F52" s="44" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G52" s="29" t="inlineStr">
+      <c r="G52" s="44" t="inlineStr">
         <is>
           <t>AUDIO: defined in report suite but never implemented in the old Launch property. Net-new scope (Web SDK media collection).</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="27" t="n">
+      <c r="A53" s="42" t="n">
         <v>53</v>
       </c>
-      <c r="B53" s="27" t="inlineStr">
+      <c r="B53" s="42" t="inlineStr">
         <is>
           <t>Audio Duration</t>
         </is>
       </c>
-      <c r="C53" s="28" t="inlineStr">
+      <c r="C53" s="43" t="inlineStr">
         <is>
           <t>Not implemented (never built)</t>
         </is>
       </c>
-      <c r="D53" s="29" t="inlineStr">
+      <c r="D53" s="44" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E53" s="29" t="inlineStr">
+      <c r="E53" s="44" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F53" s="29" t="inlineStr">
+      <c r="F53" s="44" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G53" s="29" t="inlineStr">
+      <c r="G53" s="44" t="inlineStr">
         <is>
           <t>AUDIO: defined in report suite but never implemented in the old Launch property. Net-new scope (Web SDK media collection).</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="27" t="n">
+      <c r="A54" s="42" t="n">
         <v>54</v>
       </c>
-      <c r="B54" s="27" t="inlineStr">
+      <c r="B54" s="42" t="inlineStr">
         <is>
           <t>Audio Percent Played</t>
         </is>
       </c>
-      <c r="C54" s="28" t="inlineStr">
+      <c r="C54" s="43" t="inlineStr">
         <is>
           <t>Not implemented (never built)</t>
         </is>
       </c>
-      <c r="D54" s="29" t="inlineStr">
+      <c r="D54" s="44" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E54" s="29" t="inlineStr">
+      <c r="E54" s="44" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F54" s="29" t="inlineStr">
+      <c r="F54" s="44" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G54" s="29" t="inlineStr">
+      <c r="G54" s="44" t="inlineStr">
         <is>
           <t>AUDIO: defined in report suite but never implemented in the old Launch property. Net-new scope (Web SDK media collection).</t>
         </is>
@@ -2626,665 +2777,665 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="14" t="inlineStr">
+      <c r="A1" s="29" t="inlineStr">
         <is>
           <t>Prop #</t>
         </is>
       </c>
-      <c r="B1" s="14" t="inlineStr">
+      <c r="B1" s="29" t="inlineStr">
         <is>
           <t>Report Suite Name</t>
         </is>
       </c>
-      <c r="C1" s="14" t="inlineStr">
+      <c r="C1" s="29" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="D1" s="14" t="inlineStr">
+      <c r="D1" s="29" t="inlineStr">
         <is>
           <t>Data Element(s)</t>
         </is>
       </c>
-      <c r="E1" s="14" t="inlineStr">
+      <c r="E1" s="29" t="inlineStr">
         <is>
           <t>Sent By Rule(s)</t>
         </is>
       </c>
-      <c r="F1" s="14" t="inlineStr">
+      <c r="F1" s="29" t="inlineStr">
         <is>
           <t>Data Element Source</t>
         </is>
       </c>
-      <c r="G1" s="14" t="inlineStr">
+      <c r="G1" s="29" t="inlineStr">
         <is>
           <t>Notes / Issue</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="n">
+      <c r="A2" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="15" t="inlineStr">
+      <c r="B2" s="30" t="inlineStr">
         <is>
           <t>Page Name</t>
         </is>
       </c>
-      <c r="C2" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D2" s="17" t="inlineStr">
+      <c r="C2" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D2" s="32" t="inlineStr">
         <is>
           <t>Page: Name</t>
         </is>
       </c>
-      <c r="E2" s="17" t="inlineStr">
+      <c r="E2" s="32" t="inlineStr">
         <is>
           <t>Global Page Load Rule</t>
         </is>
       </c>
-      <c r="F2" s="17" t="inlineStr">
+      <c r="F2" s="32" t="inlineStr">
         <is>
           <t>web.webPageDetails.pageName</t>
         </is>
       </c>
-      <c r="G2" s="17" t="inlineStr"/>
+      <c r="G2" s="32" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="n">
+      <c r="A3" s="30" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="15" t="inlineStr">
+      <c r="B3" s="30" t="inlineStr">
         <is>
           <t>Referrer</t>
         </is>
       </c>
-      <c r="C3" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D3" s="17" t="inlineStr">
+      <c r="C3" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D3" s="32" t="inlineStr">
         <is>
           <t>Core: Referrer</t>
         </is>
       </c>
-      <c r="E3" s="17" t="inlineStr">
+      <c r="E3" s="32" t="inlineStr">
         <is>
           <t>Global Page Load Rule</t>
         </is>
       </c>
-      <c r="F3" s="17" t="inlineStr">
+      <c r="F3" s="32" t="inlineStr">
         <is>
           <t>core-page-info</t>
         </is>
       </c>
-      <c r="G3" s="17" t="inlineStr"/>
+      <c r="G3" s="32" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="n">
+      <c r="A4" s="30" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="B4" s="30" t="inlineStr">
         <is>
           <t>Time Stamp</t>
         </is>
       </c>
-      <c r="C4" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="C4" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D4" s="32" t="inlineStr">
         <is>
           <t>Core: Timestamp</t>
         </is>
       </c>
-      <c r="E4" s="17" t="inlineStr">
+      <c r="E4" s="32" t="inlineStr">
         <is>
           <t>Global Page Load Rule</t>
         </is>
       </c>
-      <c r="F4" s="17" t="inlineStr">
+      <c r="F4" s="32" t="inlineStr">
         <is>
           <t>custom code</t>
         </is>
       </c>
-      <c r="G4" s="17" t="inlineStr"/>
+      <c r="G4" s="32" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="n">
+      <c r="A5" s="30" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B5" s="30" t="inlineStr">
         <is>
           <t>Page Title</t>
         </is>
       </c>
-      <c r="C5" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="C5" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D5" s="32" t="inlineStr">
         <is>
           <t>Page: Title</t>
         </is>
       </c>
-      <c r="E5" s="17" t="inlineStr">
+      <c r="E5" s="32" t="inlineStr">
         <is>
           <t>Global Page Load Rule</t>
         </is>
       </c>
-      <c r="F5" s="17" t="inlineStr">
+      <c r="F5" s="32" t="inlineStr">
         <is>
           <t>web.webPageDetails.pageTitle</t>
         </is>
       </c>
-      <c r="G5" s="17" t="inlineStr"/>
+      <c r="G5" s="32" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="n">
+      <c r="A6" s="30" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B6" s="30" t="inlineStr">
         <is>
           <t>Clean URL</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D6" s="17" t="inlineStr">
+      <c r="C6" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D6" s="32" t="inlineStr">
         <is>
           <t>Core: Clean URL</t>
         </is>
       </c>
-      <c r="E6" s="17" t="inlineStr">
+      <c r="E6" s="32" t="inlineStr">
         <is>
           <t>Global Page Load Rule</t>
         </is>
       </c>
-      <c r="F6" s="17" t="inlineStr">
+      <c r="F6" s="32" t="inlineStr">
         <is>
           <t>custom code</t>
         </is>
       </c>
-      <c r="G6" s="17" t="inlineStr"/>
+      <c r="G6" s="32" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="n">
+      <c r="A7" s="30" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" s="30" t="inlineStr">
         <is>
           <t>Site Section</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="C7" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D7" s="32" t="inlineStr">
         <is>
           <t>Site: Section</t>
         </is>
       </c>
-      <c r="E7" s="17" t="inlineStr">
+      <c r="E7" s="32" t="inlineStr">
         <is>
           <t>Global Page Load Rule</t>
         </is>
       </c>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="F7" s="32" t="inlineStr">
         <is>
           <t>web.webPageDetails.siteSection</t>
         </is>
       </c>
-      <c r="G7" s="17" t="inlineStr"/>
+      <c r="G7" s="32" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="n">
+      <c r="A8" s="30" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B8" s="30" t="inlineStr">
         <is>
           <t>Site Section2</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="C8" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D8" s="32" t="inlineStr">
         <is>
           <t>Site: Section 2</t>
         </is>
       </c>
-      <c r="E8" s="17" t="inlineStr">
+      <c r="E8" s="32" t="inlineStr">
         <is>
           <t>Global Page Load Rule</t>
         </is>
       </c>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="F8" s="32" t="inlineStr">
         <is>
           <t>web.webPageDetails.siteSectionTwo</t>
         </is>
       </c>
-      <c r="G8" s="17" t="inlineStr"/>
+      <c r="G8" s="32" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="n">
+      <c r="A9" s="30" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="15" t="inlineStr">
+      <c r="B9" s="30" t="inlineStr">
         <is>
           <t>Site Section3</t>
         </is>
       </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="C9" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D9" s="32" t="inlineStr">
         <is>
           <t>Site: Section 3</t>
         </is>
       </c>
-      <c r="E9" s="17" t="inlineStr">
+      <c r="E9" s="32" t="inlineStr">
         <is>
           <t>Global Page Load Rule</t>
         </is>
       </c>
-      <c r="F9" s="17" t="inlineStr">
+      <c r="F9" s="32" t="inlineStr">
         <is>
           <t>web.webPageDetails.siteSectionThree</t>
         </is>
       </c>
-      <c r="G9" s="17" t="inlineStr"/>
+      <c r="G9" s="32" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="n">
+      <c r="A10" s="30" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="15" t="inlineStr">
+      <c r="B10" s="30" t="inlineStr">
         <is>
           <t>Site Section4</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="C10" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D10" s="32" t="inlineStr">
         <is>
           <t>Site: Section 4</t>
         </is>
       </c>
-      <c r="E10" s="17" t="inlineStr">
+      <c r="E10" s="32" t="inlineStr">
         <is>
           <t>Global Page Load Rule</t>
         </is>
       </c>
-      <c r="F10" s="17" t="inlineStr">
+      <c r="F10" s="32" t="inlineStr">
         <is>
           <t>siteSection4</t>
         </is>
       </c>
-      <c r="G10" s="17" t="inlineStr"/>
+      <c r="G10" s="32" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="n">
+      <c r="A11" s="30" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="15" t="inlineStr">
+      <c r="B11" s="30" t="inlineStr">
         <is>
           <t>Site Section5</t>
         </is>
       </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="C11" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D11" s="32" t="inlineStr">
         <is>
           <t>Site: Section 5</t>
         </is>
       </c>
-      <c r="E11" s="17" t="inlineStr">
+      <c r="E11" s="32" t="inlineStr">
         <is>
           <t>Global Page Load Rule</t>
         </is>
       </c>
-      <c r="F11" s="17" t="inlineStr">
+      <c r="F11" s="32" t="inlineStr">
         <is>
           <t>siteSection5</t>
         </is>
       </c>
-      <c r="G11" s="17" t="inlineStr"/>
+      <c r="G11" s="32" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="n">
+      <c r="A12" s="30" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="15" t="inlineStr">
+      <c r="B12" s="30" t="inlineStr">
         <is>
           <t>Previous Page Name</t>
         </is>
       </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="C12" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D12" s="32" t="inlineStr">
         <is>
           <t>Plugin: Previous Page Name</t>
         </is>
       </c>
-      <c r="E12" s="17" t="inlineStr">
+      <c r="E12" s="32" t="inlineStr">
         <is>
           <t>Global Page Load Rule</t>
         </is>
       </c>
-      <c r="F12" s="17" t="inlineStr">
+      <c r="F12" s="32" t="inlineStr">
         <is>
           <t>cwsdkp-getpreviousvalue</t>
         </is>
       </c>
-      <c r="G12" s="17" t="inlineStr"/>
+      <c r="G12" s="32" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="n">
+      <c r="A13" s="30" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="15" t="inlineStr">
+      <c r="B13" s="30" t="inlineStr">
         <is>
           <t>Page URL</t>
         </is>
       </c>
-      <c r="C13" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D13" s="17" t="inlineStr">
+      <c r="C13" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D13" s="32" t="inlineStr">
         <is>
           <t>Page: URL</t>
         </is>
       </c>
-      <c r="E13" s="17" t="inlineStr">
+      <c r="E13" s="32" t="inlineStr">
         <is>
           <t>Global Page Load Rule</t>
         </is>
       </c>
-      <c r="F13" s="17" t="inlineStr">
+      <c r="F13" s="32" t="inlineStr">
         <is>
           <t>web.webPageDetails.pageUrl</t>
         </is>
       </c>
-      <c r="G13" s="17" t="inlineStr"/>
+      <c r="G13" s="32" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="21" t="n">
+      <c r="A14" s="36" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="21" t="inlineStr">
+      <c r="B14" s="36" t="inlineStr">
         <is>
           <t>ECID</t>
         </is>
       </c>
-      <c r="C14" s="22" t="inlineStr">
+      <c r="C14" s="37" t="inlineStr">
         <is>
           <t>Excluded by design</t>
         </is>
       </c>
-      <c r="D14" s="23" t="inlineStr">
+      <c r="D14" s="38" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E14" s="23" t="inlineStr">
+      <c r="E14" s="38" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F14" s="23" t="inlineStr">
+      <c r="F14" s="38" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G14" s="23" t="inlineStr">
+      <c r="G14" s="38" t="inlineStr">
         <is>
           <t>ECID intentionally not captured — Web SDK manages identity natively. Source element was a broken recursive stub.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="n">
+      <c r="A15" s="30" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="15" t="inlineStr">
+      <c r="B15" s="30" t="inlineStr">
         <is>
           <t>Visit Number</t>
         </is>
       </c>
-      <c r="C15" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D15" s="17" t="inlineStr">
+      <c r="C15" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D15" s="32" t="inlineStr">
         <is>
           <t>Plugin: Visit Number</t>
         </is>
       </c>
-      <c r="E15" s="17" t="inlineStr">
+      <c r="E15" s="32" t="inlineStr">
         <is>
           <t>Global Page Load Rule</t>
         </is>
       </c>
-      <c r="F15" s="17" t="inlineStr">
+      <c r="F15" s="32" t="inlineStr">
         <is>
           <t>cwsdkp-getvisitnum</t>
         </is>
       </c>
-      <c r="G15" s="17" t="inlineStr"/>
+      <c r="G15" s="32" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="15" t="n">
+      <c r="A16" s="30" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="15" t="inlineStr">
+      <c r="B16" s="30" t="inlineStr">
         <is>
           <t>Time Since Last Visit</t>
         </is>
       </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D16" s="17" t="inlineStr">
+      <c r="C16" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D16" s="32" t="inlineStr">
         <is>
           <t>Plugin: Time Since Last Visit</t>
         </is>
       </c>
-      <c r="E16" s="17" t="inlineStr">
+      <c r="E16" s="32" t="inlineStr">
         <is>
           <t>Global Page Load Rule</t>
         </is>
       </c>
-      <c r="F16" s="17" t="inlineStr">
+      <c r="F16" s="32" t="inlineStr">
         <is>
           <t>cwsdkp-gettimesincelastvisit</t>
         </is>
       </c>
-      <c r="G16" s="17" t="inlineStr"/>
+      <c r="G16" s="32" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="n">
+      <c r="A17" s="30" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="15" t="inlineStr">
+      <c r="B17" s="30" t="inlineStr">
         <is>
           <t>Repeat Vs New</t>
         </is>
       </c>
-      <c r="C17" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D17" s="17" t="inlineStr">
+      <c r="C17" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D17" s="32" t="inlineStr">
         <is>
           <t>Plugin: Repeat Vs New</t>
         </is>
       </c>
-      <c r="E17" s="17" t="inlineStr">
+      <c r="E17" s="32" t="inlineStr">
         <is>
           <t>Global Page Load Rule</t>
         </is>
       </c>
-      <c r="F17" s="17" t="inlineStr">
+      <c r="F17" s="32" t="inlineStr">
         <is>
           <t>cwsdkp-getnewrepeat</t>
         </is>
       </c>
-      <c r="G17" s="17" t="inlineStr"/>
+      <c r="G17" s="32" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="n">
+      <c r="A18" s="30" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="15" t="inlineStr">
+      <c r="B18" s="30" t="inlineStr">
         <is>
           <t>Visit Duration</t>
         </is>
       </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D18" s="17" t="inlineStr">
+      <c r="C18" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D18" s="32" t="inlineStr">
         <is>
           <t>Plugin: Visit Duration</t>
         </is>
       </c>
-      <c r="E18" s="17" t="inlineStr">
+      <c r="E18" s="32" t="inlineStr">
         <is>
           <t>Global Page Load Rule</t>
         </is>
       </c>
-      <c r="F18" s="17" t="inlineStr">
+      <c r="F18" s="32" t="inlineStr">
         <is>
           <t>cwsdkp-getvisitduration</t>
         </is>
       </c>
-      <c r="G18" s="17" t="inlineStr"/>
+      <c r="G18" s="32" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="n">
+      <c r="A19" s="30" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="15" t="inlineStr">
+      <c r="B19" s="30" t="inlineStr">
         <is>
           <t>Page Title</t>
         </is>
       </c>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D19" s="17" t="inlineStr">
+      <c r="C19" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D19" s="32" t="inlineStr">
         <is>
           <t>Page: Title</t>
         </is>
       </c>
-      <c r="E19" s="17" t="inlineStr">
+      <c r="E19" s="32" t="inlineStr">
         <is>
           <t>Global Page Load Rule</t>
         </is>
       </c>
-      <c r="F19" s="17" t="inlineStr">
+      <c r="F19" s="32" t="inlineStr">
         <is>
           <t>web.webPageDetails.pageTitle</t>
         </is>
       </c>
-      <c r="G19" s="17" t="inlineStr"/>
+      <c r="G19" s="32" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="n">
+      <c r="A20" s="30" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="15" t="inlineStr">
+      <c r="B20" s="30" t="inlineStr">
         <is>
           <t>Site Error</t>
         </is>
       </c>
-      <c r="C20" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D20" s="17" t="inlineStr">
+      <c r="C20" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D20" s="32" t="inlineStr">
         <is>
           <t>Page: Error</t>
         </is>
       </c>
-      <c r="E20" s="17" t="inlineStr">
+      <c r="E20" s="32" t="inlineStr">
         <is>
           <t>Global Page Load Rule; Site Error</t>
         </is>
       </c>
-      <c r="F20" s="17" t="inlineStr">
+      <c r="F20" s="32" t="inlineStr">
         <is>
           <t>web.webPageDetails.siteError</t>
         </is>
       </c>
-      <c r="G20" s="17" t="inlineStr"/>
+      <c r="G20" s="32" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="15" t="n">
+      <c r="A21" s="30" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="15" t="inlineStr">
+      <c r="B21" s="30" t="inlineStr">
         <is>
           <t>Locale</t>
         </is>
       </c>
-      <c r="C21" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D21" s="17" t="inlineStr">
+      <c r="C21" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D21" s="32" t="inlineStr">
         <is>
           <t>Geo: Locale</t>
         </is>
       </c>
-      <c r="E21" s="17" t="inlineStr">
+      <c r="E21" s="32" t="inlineStr">
         <is>
           <t>Global Page Load Rule</t>
         </is>
       </c>
-      <c r="F21" s="17" t="inlineStr">
+      <c r="F21" s="32" t="inlineStr">
         <is>
           <t>web.webPageDetails.locale</t>
         </is>
       </c>
-      <c r="G21" s="17" t="inlineStr"/>
+      <c r="G21" s="32" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:G21"/>
@@ -3309,861 +3460,861 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="14" t="inlineStr">
+      <c r="A1" s="29" t="inlineStr">
         <is>
           <t>Event #</t>
         </is>
       </c>
-      <c r="B1" s="14" t="inlineStr">
+      <c r="B1" s="29" t="inlineStr">
         <is>
           <t>Report Suite Name</t>
         </is>
       </c>
-      <c r="C1" s="14" t="inlineStr">
+      <c r="C1" s="29" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="D1" s="14" t="inlineStr">
+      <c r="D1" s="29" t="inlineStr">
         <is>
           <t>Sent By Rule(s)</t>
         </is>
       </c>
-      <c r="E1" s="14" t="inlineStr">
+      <c r="E1" s="29" t="inlineStr">
         <is>
           <t>Notes / Issue</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="n">
+      <c r="A2" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="15" t="inlineStr">
+      <c r="B2" s="30" t="inlineStr">
         <is>
           <t>Social Interactions</t>
         </is>
       </c>
-      <c r="C2" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D2" s="17" t="inlineStr">
+      <c r="C2" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D2" s="32" t="inlineStr">
         <is>
           <t>Social Interaction Tracking</t>
         </is>
       </c>
-      <c r="E2" s="17" t="inlineStr"/>
+      <c r="E2" s="32" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="n">
+      <c r="A3" s="30" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="15" t="inlineStr">
+      <c r="B3" s="30" t="inlineStr">
         <is>
           <t>Page Load</t>
         </is>
       </c>
-      <c r="C3" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D3" s="17" t="inlineStr">
+      <c r="C3" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D3" s="32" t="inlineStr">
         <is>
           <t>Global Page Load Rule</t>
         </is>
       </c>
-      <c r="E3" s="17" t="inlineStr"/>
+      <c r="E3" s="32" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="24" t="n">
+      <c r="A4" s="39" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="24" t="inlineStr">
+      <c r="B4" s="39" t="inlineStr">
         <is>
           <t>Internal Campaign Click</t>
         </is>
       </c>
-      <c r="C4" s="25" t="inlineStr">
+      <c r="C4" s="40" t="inlineStr">
         <is>
           <t>Defined, old property never sent</t>
         </is>
       </c>
-      <c r="D4" s="26" t="inlineStr">
+      <c r="D4" s="41" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E4" s="26" t="inlineStr">
+      <c r="E4" s="41" t="inlineStr">
         <is>
           <t>Old property never sent it (deferred internal-campaign feature).</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="n">
+      <c r="A5" s="33" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B5" s="33" t="inlineStr">
         <is>
           <t>Internal Campaign Impressions</t>
         </is>
       </c>
-      <c r="C5" s="19" t="inlineStr">
+      <c r="C5" s="34" t="inlineStr">
         <is>
           <t>No data (element is a no-op)</t>
         </is>
       </c>
-      <c r="D5" s="20" t="inlineStr">
+      <c r="D5" s="35" t="inlineStr">
         <is>
           <t>Global Page Load Rule</t>
         </is>
       </c>
-      <c r="E5" s="20" t="inlineStr">
+      <c r="E5" s="35" t="inlineStr">
         <is>
           <t>Filtered out of the page view (valued event fed by a no-op counter) — deferred with Internal Campaign.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="24" t="n">
+      <c r="A6" s="39" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="24" t="inlineStr">
+      <c r="B6" s="39" t="inlineStr">
         <is>
           <t>Internal Search</t>
         </is>
       </c>
-      <c r="C6" s="25" t="inlineStr">
+      <c r="C6" s="40" t="inlineStr">
         <is>
           <t>Defined, old property never sent</t>
         </is>
       </c>
-      <c r="D6" s="26" t="inlineStr">
+      <c r="D6" s="41" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E6" s="26" t="inlineStr">
+      <c r="E6" s="41" t="inlineStr">
         <is>
           <t>Old property used event26 (Internal Search Click) instead.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="n">
+      <c r="A7" s="30" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" s="30" t="inlineStr">
         <is>
           <t>Null Search Results</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="C7" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D7" s="32" t="inlineStr">
         <is>
           <t>Null Search Tracking</t>
         </is>
       </c>
-      <c r="E7" s="17" t="inlineStr"/>
+      <c r="E7" s="32" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="n">
+      <c r="A8" s="30" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B8" s="30" t="inlineStr">
         <is>
           <t>Internal Search Click-through</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="C8" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D8" s="32" t="inlineStr">
         <is>
           <t>Internal Search ClickThrough</t>
         </is>
       </c>
-      <c r="E8" s="17" t="inlineStr"/>
+      <c r="E8" s="32" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="n">
+      <c r="A9" s="30" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="15" t="inlineStr">
+      <c r="B9" s="30" t="inlineStr">
         <is>
           <t>Form Error</t>
         </is>
       </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="C9" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D9" s="32" t="inlineStr">
         <is>
           <t>Form Error Tracking</t>
         </is>
       </c>
-      <c r="E9" s="17" t="inlineStr"/>
+      <c r="E9" s="32" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="n">
+      <c r="A10" s="30" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="15" t="inlineStr">
+      <c r="B10" s="30" t="inlineStr">
         <is>
           <t>Form Starts</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="C10" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D10" s="32" t="inlineStr">
         <is>
           <t>Form Start</t>
         </is>
       </c>
-      <c r="E10" s="17" t="inlineStr"/>
+      <c r="E10" s="32" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="n">
+      <c r="A11" s="30" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="15" t="inlineStr">
+      <c r="B11" s="30" t="inlineStr">
         <is>
           <t>Form Completes</t>
         </is>
       </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="C11" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D11" s="32" t="inlineStr">
         <is>
           <t>Form Complete</t>
         </is>
       </c>
-      <c r="E11" s="17" t="inlineStr"/>
+      <c r="E11" s="32" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="n">
+      <c r="A12" s="30" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="15" t="inlineStr">
+      <c r="B12" s="30" t="inlineStr">
         <is>
           <t>Video Start</t>
         </is>
       </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="C12" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D12" s="32" t="inlineStr">
         <is>
           <t>Video Start</t>
         </is>
       </c>
-      <c r="E12" s="17" t="inlineStr"/>
+      <c r="E12" s="32" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="n">
+      <c r="A13" s="30" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="15" t="inlineStr">
+      <c r="B13" s="30" t="inlineStr">
         <is>
           <t>Video Complete</t>
         </is>
       </c>
-      <c r="C13" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D13" s="17" t="inlineStr">
+      <c r="C13" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D13" s="32" t="inlineStr">
         <is>
           <t>Video 100 percentage complete</t>
         </is>
       </c>
-      <c r="E13" s="17" t="inlineStr"/>
+      <c r="E13" s="32" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="n">
+      <c r="A14" s="30" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="15" t="inlineStr">
+      <c r="B14" s="30" t="inlineStr">
         <is>
           <t>Video 25% Milestone</t>
         </is>
       </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D14" s="17" t="inlineStr">
+      <c r="C14" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D14" s="32" t="inlineStr">
         <is>
           <t>Video 25 percentage complete</t>
         </is>
       </c>
-      <c r="E14" s="17" t="inlineStr"/>
+      <c r="E14" s="32" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="n">
+      <c r="A15" s="30" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="15" t="inlineStr">
+      <c r="B15" s="30" t="inlineStr">
         <is>
           <t>Video 50% Milestone</t>
         </is>
       </c>
-      <c r="C15" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D15" s="17" t="inlineStr">
+      <c r="C15" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D15" s="32" t="inlineStr">
         <is>
           <t>Video 50 percentage complete</t>
         </is>
       </c>
-      <c r="E15" s="17" t="inlineStr"/>
+      <c r="E15" s="32" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="15" t="n">
+      <c r="A16" s="30" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="15" t="inlineStr">
+      <c r="B16" s="30" t="inlineStr">
         <is>
           <t>Video 75% Milestone</t>
         </is>
       </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D16" s="17" t="inlineStr">
+      <c r="C16" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D16" s="32" t="inlineStr">
         <is>
           <t>Video 75 percentage complete</t>
         </is>
       </c>
-      <c r="E16" s="17" t="inlineStr"/>
+      <c r="E16" s="32" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="n">
+      <c r="A17" s="30" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="15" t="inlineStr">
+      <c r="B17" s="30" t="inlineStr">
         <is>
           <t>File Downloads</t>
         </is>
       </c>
-      <c r="C17" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D17" s="17" t="inlineStr">
+      <c r="C17" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D17" s="32" t="inlineStr">
         <is>
           <t>File Download Tracking</t>
         </is>
       </c>
-      <c r="E17" s="17" t="inlineStr"/>
+      <c r="E17" s="32" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="n">
+      <c r="A18" s="30" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="15" t="inlineStr">
+      <c r="B18" s="30" t="inlineStr">
         <is>
           <t>Scroll Reach 25%</t>
         </is>
       </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D18" s="17" t="inlineStr">
+      <c r="C18" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D18" s="32" t="inlineStr">
         <is>
           <t>Scroll 25 percentage</t>
         </is>
       </c>
-      <c r="E18" s="17" t="inlineStr"/>
+      <c r="E18" s="32" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="n">
+      <c r="A19" s="30" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="15" t="inlineStr">
+      <c r="B19" s="30" t="inlineStr">
         <is>
           <t>Scroll Reach 50%</t>
         </is>
       </c>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D19" s="17" t="inlineStr">
+      <c r="C19" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D19" s="32" t="inlineStr">
         <is>
           <t>Scroll 50 percentage</t>
         </is>
       </c>
-      <c r="E19" s="17" t="inlineStr"/>
+      <c r="E19" s="32" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="n">
+      <c r="A20" s="30" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="15" t="inlineStr">
+      <c r="B20" s="30" t="inlineStr">
         <is>
           <t>Scroll Reach 75%</t>
         </is>
       </c>
-      <c r="C20" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D20" s="17" t="inlineStr">
+      <c r="C20" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D20" s="32" t="inlineStr">
         <is>
           <t>Scroll 75 percentage</t>
         </is>
       </c>
-      <c r="E20" s="17" t="inlineStr"/>
+      <c r="E20" s="32" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="15" t="n">
+      <c r="A21" s="30" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="15" t="inlineStr">
+      <c r="B21" s="30" t="inlineStr">
         <is>
           <t>Scroll Reach 100%</t>
         </is>
       </c>
-      <c r="C21" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D21" s="17" t="inlineStr">
+      <c r="C21" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D21" s="32" t="inlineStr">
         <is>
           <t>Scroll 100 percentage</t>
         </is>
       </c>
-      <c r="E21" s="17" t="inlineStr"/>
+      <c r="E21" s="32" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="15" t="n">
+      <c r="A22" s="30" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="15" t="inlineStr">
+      <c r="B22" s="30" t="inlineStr">
         <is>
           <t>Link Click</t>
         </is>
       </c>
-      <c r="C22" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D22" s="17" t="inlineStr">
+      <c r="C22" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D22" s="32" t="inlineStr">
         <is>
           <t>Amazon Redirect Link Click; Redirect Link Click Tracking</t>
         </is>
       </c>
-      <c r="E22" s="17" t="inlineStr"/>
+      <c r="E22" s="32" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="15" t="n">
+      <c r="A23" s="30" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="15" t="inlineStr">
+      <c r="B23" s="30" t="inlineStr">
         <is>
           <t>CTA Click</t>
         </is>
       </c>
-      <c r="C23" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D23" s="17" t="inlineStr">
+      <c r="C23" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D23" s="32" t="inlineStr">
         <is>
           <t>Amazon More News Tracking; Amazon Redirect Link Click; Amazon Stories Link Click Tracking; Global CTA Button Tracking; Redirect Link Click Tracking</t>
         </is>
       </c>
-      <c r="E23" s="17" t="inlineStr"/>
+      <c r="E23" s="32" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="15" t="n">
+      <c r="A24" s="30" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="15" t="inlineStr">
+      <c r="B24" s="30" t="inlineStr">
         <is>
           <t>Menu Click</t>
         </is>
       </c>
-      <c r="C24" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D24" s="17" t="inlineStr">
+      <c r="C24" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D24" s="32" t="inlineStr">
         <is>
           <t>Menu Link Click Tracking</t>
         </is>
       </c>
-      <c r="E24" s="17" t="inlineStr"/>
+      <c r="E24" s="32" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="15" t="n">
+      <c r="A25" s="30" t="n">
         <v>25</v>
       </c>
-      <c r="B25" s="15" t="inlineStr">
+      <c r="B25" s="30" t="inlineStr">
         <is>
           <t>Filter Applied</t>
         </is>
       </c>
-      <c r="C25" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D25" s="17" t="inlineStr">
+      <c r="C25" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D25" s="32" t="inlineStr">
         <is>
           <t>Filter Click Tracking</t>
         </is>
       </c>
-      <c r="E25" s="17" t="inlineStr"/>
+      <c r="E25" s="32" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="15" t="n">
+      <c r="A26" s="30" t="n">
         <v>26</v>
       </c>
-      <c r="B26" s="15" t="inlineStr">
+      <c r="B26" s="30" t="inlineStr">
         <is>
           <t>Internal Search Click</t>
         </is>
       </c>
-      <c r="C26" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D26" s="17" t="inlineStr">
+      <c r="C26" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D26" s="32" t="inlineStr">
         <is>
           <t>Internal Search Click</t>
         </is>
       </c>
-      <c r="E26" s="17" t="inlineStr"/>
+      <c r="E26" s="32" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="15" t="n">
+      <c r="A27" s="30" t="n">
         <v>27</v>
       </c>
-      <c r="B27" s="15" t="inlineStr">
+      <c r="B27" s="30" t="inlineStr">
         <is>
           <t>Search Close Click</t>
         </is>
       </c>
-      <c r="C27" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D27" s="17" t="inlineStr">
+      <c r="C27" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D27" s="32" t="inlineStr">
         <is>
           <t>Search Close Click</t>
         </is>
       </c>
-      <c r="E27" s="17" t="inlineStr"/>
+      <c r="E27" s="32" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="15" t="n">
+      <c r="A28" s="30" t="n">
         <v>28</v>
       </c>
-      <c r="B28" s="15" t="inlineStr">
+      <c r="B28" s="30" t="inlineStr">
         <is>
           <t>Video Pause</t>
         </is>
       </c>
-      <c r="C28" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D28" s="17" t="inlineStr">
+      <c r="C28" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D28" s="32" t="inlineStr">
         <is>
           <t>Video Pause</t>
         </is>
       </c>
-      <c r="E28" s="17" t="inlineStr"/>
+      <c r="E28" s="32" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="15" t="n">
+      <c r="A29" s="30" t="n">
         <v>29</v>
       </c>
-      <c r="B29" s="15" t="inlineStr">
+      <c r="B29" s="30" t="inlineStr">
         <is>
           <t>Tag Click</t>
         </is>
       </c>
-      <c r="C29" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D29" s="17" t="inlineStr">
+      <c r="C29" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D29" s="32" t="inlineStr">
         <is>
           <t>Related Tag Click Tracking</t>
         </is>
       </c>
-      <c r="E29" s="17" t="inlineStr"/>
+      <c r="E29" s="32" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="15" t="n">
+      <c r="A30" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="B30" s="15" t="inlineStr">
+      <c r="B30" s="30" t="inlineStr">
         <is>
           <t>Cookie Consent Click</t>
         </is>
       </c>
-      <c r="C30" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D30" s="17" t="inlineStr">
+      <c r="C30" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D30" s="32" t="inlineStr">
         <is>
           <t>Consent Selection</t>
         </is>
       </c>
-      <c r="E30" s="17" t="inlineStr">
+      <c r="E30" s="32" t="inlineStr">
         <is>
           <t>value from: Consent: Click Count</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="15" t="n">
+      <c r="A31" s="30" t="n">
         <v>31</v>
       </c>
-      <c r="B31" s="15" t="inlineStr">
+      <c r="B31" s="30" t="inlineStr">
         <is>
           <t>Map Zoom Out</t>
         </is>
       </c>
-      <c r="C31" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D31" s="17" t="inlineStr">
+      <c r="C31" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D31" s="32" t="inlineStr">
         <is>
           <t>Map Zoom Out</t>
         </is>
       </c>
-      <c r="E31" s="17" t="inlineStr"/>
+      <c r="E31" s="32" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="15" t="n">
+      <c r="A32" s="30" t="n">
         <v>32</v>
       </c>
-      <c r="B32" s="15" t="inlineStr">
+      <c r="B32" s="30" t="inlineStr">
         <is>
           <t>Map Button Click</t>
         </is>
       </c>
-      <c r="C32" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D32" s="17" t="inlineStr">
+      <c r="C32" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D32" s="32" t="inlineStr">
         <is>
           <t>Map Button Click</t>
         </is>
       </c>
-      <c r="E32" s="17" t="inlineStr"/>
+      <c r="E32" s="32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="15" t="n">
+      <c r="A33" s="30" t="n">
         <v>33</v>
       </c>
-      <c r="B33" s="15" t="inlineStr">
+      <c r="B33" s="30" t="inlineStr">
         <is>
           <t>Map Button Close</t>
         </is>
       </c>
-      <c r="C33" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D33" s="17" t="inlineStr">
+      <c r="C33" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D33" s="32" t="inlineStr">
         <is>
           <t>Map Button Close</t>
         </is>
       </c>
-      <c r="E33" s="17" t="inlineStr"/>
+      <c r="E33" s="32" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="15" t="n">
+      <c r="A34" s="30" t="n">
         <v>34</v>
       </c>
-      <c r="B34" s="15" t="inlineStr">
+      <c r="B34" s="30" t="inlineStr">
         <is>
           <t>Map Zoom In</t>
         </is>
       </c>
-      <c r="C34" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D34" s="17" t="inlineStr">
+      <c r="C34" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D34" s="32" t="inlineStr">
         <is>
           <t>Map Zoom In</t>
         </is>
       </c>
-      <c r="E34" s="17" t="inlineStr"/>
+      <c r="E34" s="32" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="27" t="n">
+      <c r="A35" s="42" t="n">
         <v>35</v>
       </c>
-      <c r="B35" s="27" t="inlineStr">
+      <c r="B35" s="42" t="inlineStr">
         <is>
           <t>Audio Start</t>
         </is>
       </c>
-      <c r="C35" s="28" t="inlineStr">
+      <c r="C35" s="43" t="inlineStr">
         <is>
           <t>Not implemented (never built)</t>
         </is>
       </c>
-      <c r="D35" s="29" t="inlineStr">
+      <c r="D35" s="44" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E35" s="29" t="inlineStr">
+      <c r="E35" s="44" t="inlineStr">
         <is>
           <t>AUDIO event — never implemented in the old Launch property.</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="27" t="n">
+      <c r="A36" s="42" t="n">
         <v>36</v>
       </c>
-      <c r="B36" s="27" t="inlineStr">
+      <c r="B36" s="42" t="inlineStr">
         <is>
           <t>Audio Complete</t>
         </is>
       </c>
-      <c r="C36" s="28" t="inlineStr">
+      <c r="C36" s="43" t="inlineStr">
         <is>
           <t>Not implemented (never built)</t>
         </is>
       </c>
-      <c r="D36" s="29" t="inlineStr">
+      <c r="D36" s="44" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E36" s="29" t="inlineStr">
+      <c r="E36" s="44" t="inlineStr">
         <is>
           <t>AUDIO event — never implemented in the old Launch property.</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="27" t="n">
+      <c r="A37" s="42" t="n">
         <v>37</v>
       </c>
-      <c r="B37" s="27" t="inlineStr">
+      <c r="B37" s="42" t="inlineStr">
         <is>
           <t>Audio Milestone 25%</t>
         </is>
       </c>
-      <c r="C37" s="28" t="inlineStr">
+      <c r="C37" s="43" t="inlineStr">
         <is>
           <t>Not implemented (never built)</t>
         </is>
       </c>
-      <c r="D37" s="29" t="inlineStr">
+      <c r="D37" s="44" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E37" s="29" t="inlineStr">
+      <c r="E37" s="44" t="inlineStr">
         <is>
           <t>AUDIO event — never implemented in the old Launch property.</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="27" t="n">
+      <c r="A38" s="42" t="n">
         <v>38</v>
       </c>
-      <c r="B38" s="27" t="inlineStr">
+      <c r="B38" s="42" t="inlineStr">
         <is>
           <t>Audio Milestone 50%</t>
         </is>
       </c>
-      <c r="C38" s="28" t="inlineStr">
+      <c r="C38" s="43" t="inlineStr">
         <is>
           <t>Not implemented (never built)</t>
         </is>
       </c>
-      <c r="D38" s="29" t="inlineStr">
+      <c r="D38" s="44" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E38" s="29" t="inlineStr">
+      <c r="E38" s="44" t="inlineStr">
         <is>
           <t>AUDIO event — never implemented in the old Launch property.</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="27" t="n">
+      <c r="A39" s="42" t="n">
         <v>39</v>
       </c>
-      <c r="B39" s="27" t="inlineStr">
+      <c r="B39" s="42" t="inlineStr">
         <is>
           <t>Audio Milestone 75%</t>
         </is>
       </c>
-      <c r="C39" s="28" t="inlineStr">
+      <c r="C39" s="43" t="inlineStr">
         <is>
           <t>Not implemented (never built)</t>
         </is>
       </c>
-      <c r="D39" s="29" t="inlineStr">
+      <c r="D39" s="44" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E39" s="29" t="inlineStr">
+      <c r="E39" s="44" t="inlineStr">
         <is>
           <t>AUDIO event — never implemented in the old Launch property.</t>
         </is>
@@ -4191,66 +4342,66 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="14" t="inlineStr">
+      <c r="A1" s="29" t="inlineStr">
         <is>
           <t>Data Element</t>
         </is>
       </c>
-      <c r="B1" s="14" t="inlineStr">
+      <c r="B1" s="29" t="inlineStr">
         <is>
           <t>Feeds Variable(s)</t>
         </is>
       </c>
-      <c r="C1" s="14" t="inlineStr">
+      <c r="C1" s="29" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="D1" s="14" t="inlineStr">
+      <c r="D1" s="29" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="30" t="inlineStr">
+      <c r="A2" s="45" t="inlineStr">
         <is>
           <t>Article: Content Type</t>
         </is>
       </c>
-      <c r="B2" s="30" t="inlineStr">
+      <c r="B2" s="45" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C2" s="31" t="inlineStr">
+      <c r="C2" s="46" t="inlineStr">
         <is>
           <t>Not wired (orphan element)</t>
         </is>
       </c>
-      <c r="D2" s="32" t="inlineStr">
+      <c r="D2" s="47" t="inlineStr">
         <is>
           <t>For the excluded (never-published) Article Interaction Tracking rule. Activates only if Article tracking is revived.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="30" t="inlineStr">
+      <c r="A3" s="45" t="inlineStr">
         <is>
           <t>Article: Name</t>
         </is>
       </c>
-      <c r="B3" s="30" t="inlineStr">
+      <c r="B3" s="45" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C3" s="31" t="inlineStr">
+      <c r="C3" s="46" t="inlineStr">
         <is>
           <t>Not wired (orphan element)</t>
         </is>
       </c>
-      <c r="D3" s="32" t="inlineStr">
+      <c r="D3" s="47" t="inlineStr">
         <is>
           <t>For the excluded (never-published) Article Interaction Tracking rule. Activates only if Article tracking is revived.</t>
         </is>
@@ -4264,113 +4415,109 @@
       </c>
       <c r="B4" s="30" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>s.campaign</t>
         </is>
       </c>
       <c r="C4" s="31" t="inlineStr">
         <is>
-          <t>Not wired (orphan element)</t>
-        </is>
-      </c>
-      <c r="D4" s="32" t="inlineStr">
-        <is>
-          <t>Carried but not referenced by any payload.</t>
-        </is>
-      </c>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D4" s="32" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="inlineStr">
+      <c r="A5" s="33" t="inlineStr">
         <is>
           <t>Campaign: Internal</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B5" s="33" t="inlineStr">
         <is>
           <t>eVar5 (Internal Campaign)</t>
         </is>
       </c>
-      <c r="C5" s="19" t="inlineStr">
+      <c r="C5" s="34" t="inlineStr">
         <is>
           <t>No data (element is a no-op)</t>
         </is>
       </c>
-      <c r="D5" s="20" t="inlineStr">
+      <c r="D5" s="35" t="inlineStr">
         <is>
           <t>Returns no value (no-op) — the variable it feeds never populates. Decision needed.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="30" t="inlineStr">
         <is>
           <t>Campaign: Internal Count</t>
         </is>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B6" s="30" t="inlineStr">
         <is>
           <t>event4 value</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D6" s="17" t="inlineStr"/>
+      <c r="C6" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D6" s="32" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="30" t="inlineStr">
         <is>
           <t>Consent: Click Count</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" s="30" t="inlineStr">
         <is>
           <t>event30 value</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D7" s="17" t="inlineStr"/>
+      <c r="C7" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D7" s="32" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="30" t="inlineStr">
         <is>
           <t>Consent: Selected</t>
         </is>
       </c>
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B8" s="30" t="inlineStr">
         <is>
           <t>eVar48 (Cookie Consent Selection)</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D8" s="17" t="inlineStr"/>
+      <c r="C8" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D8" s="32" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="30" t="inlineStr">
         <is>
           <t>Content: Category</t>
         </is>
       </c>
-      <c r="B9" s="15" t="inlineStr">
+      <c r="B9" s="30" t="inlineStr">
         <is>
           <t>eVar29 (Category)</t>
         </is>
       </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D9" s="17" t="inlineStr"/>
+      <c r="C9" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D9" s="32" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="30" t="inlineStr">
@@ -4380,199 +4527,195 @@
       </c>
       <c r="B10" s="30" t="inlineStr">
         <is>
+          <t>list2 (list)</t>
+        </is>
+      </c>
+      <c r="C10" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D10" s="32" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="30" t="inlineStr">
+        <is>
+          <t>Content: Publish Date</t>
+        </is>
+      </c>
+      <c r="B11" s="30" t="inlineStr">
+        <is>
+          <t>eVar25 (Publish Date)</t>
+        </is>
+      </c>
+      <c r="C11" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D11" s="32" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="30" t="inlineStr">
+        <is>
+          <t>Content: Tags</t>
+        </is>
+      </c>
+      <c r="B12" s="30" t="inlineStr">
+        <is>
+          <t>eVar30 (Tag Text)</t>
+        </is>
+      </c>
+      <c r="C12" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D12" s="32" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="30" t="inlineStr">
+        <is>
+          <t>Content: Type</t>
+        </is>
+      </c>
+      <c r="B13" s="30" t="inlineStr">
+        <is>
+          <t>eVar9 (Content Type)</t>
+        </is>
+      </c>
+      <c r="C13" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D13" s="32" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="30" t="inlineStr">
+        <is>
+          <t>Core: Clean URL</t>
+        </is>
+      </c>
+      <c r="B14" s="30" t="inlineStr">
+        <is>
+          <t>prop5 (Clean URL)</t>
+        </is>
+      </c>
+      <c r="C14" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D14" s="32" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="30" t="inlineStr">
+        <is>
+          <t>Core: Page Query String</t>
+        </is>
+      </c>
+      <c r="B15" s="30" t="inlineStr">
+        <is>
+          <t>eVar13 (Page Query String)</t>
+        </is>
+      </c>
+      <c r="C15" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D15" s="32" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="30" t="inlineStr">
+        <is>
+          <t>Core: Referrer</t>
+        </is>
+      </c>
+      <c r="B16" s="30" t="inlineStr">
+        <is>
+          <t>prop2 (Referrer); s.referrer</t>
+        </is>
+      </c>
+      <c r="C16" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D16" s="32" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="30" t="inlineStr">
+        <is>
+          <t>Core: Timestamp</t>
+        </is>
+      </c>
+      <c r="B17" s="30" t="inlineStr">
+        <is>
+          <t>prop3 (Time Stamp)</t>
+        </is>
+      </c>
+      <c r="C17" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D17" s="32" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="30" t="inlineStr">
+        <is>
+          <t>File: Name</t>
+        </is>
+      </c>
+      <c r="B18" s="30" t="inlineStr">
+        <is>
+          <t>eVar33 (File Name)</t>
+        </is>
+      </c>
+      <c r="C18" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D18" s="32" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="30" t="inlineStr">
+        <is>
+          <t>File: Type</t>
+        </is>
+      </c>
+      <c r="B19" s="30" t="inlineStr">
+        <is>
+          <t>eVar34 (File Type)</t>
+        </is>
+      </c>
+      <c r="C19" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D19" s="32" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="45" t="inlineStr">
+        <is>
+          <t>File: URL</t>
+        </is>
+      </c>
+      <c r="B20" s="45" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C10" s="31" t="inlineStr">
+      <c r="C20" s="46" t="inlineStr">
         <is>
           <t>Not wired (orphan element)</t>
         </is>
       </c>
-      <c r="D10" s="32" t="inlineStr">
-        <is>
-          <t>Carried but not referenced by any payload.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="15" t="inlineStr">
-        <is>
-          <t>Content: Publish Date</t>
-        </is>
-      </c>
-      <c r="B11" s="15" t="inlineStr">
-        <is>
-          <t>eVar25 (Publish Date)</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D11" s="17" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="15" t="inlineStr">
-        <is>
-          <t>Content: Tags</t>
-        </is>
-      </c>
-      <c r="B12" s="15" t="inlineStr">
-        <is>
-          <t>eVar30 (Tag Text)</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D12" s="17" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="15" t="inlineStr">
-        <is>
-          <t>Content: Type</t>
-        </is>
-      </c>
-      <c r="B13" s="15" t="inlineStr">
-        <is>
-          <t>eVar9 (Content Type)</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D13" s="17" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="15" t="inlineStr">
-        <is>
-          <t>Core: Clean URL</t>
-        </is>
-      </c>
-      <c r="B14" s="15" t="inlineStr">
-        <is>
-          <t>prop5 (Clean URL)</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D14" s="17" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="15" t="inlineStr">
-        <is>
-          <t>Core: Page Query String</t>
-        </is>
-      </c>
-      <c r="B15" s="15" t="inlineStr">
-        <is>
-          <t>eVar13 (Page Query String)</t>
-        </is>
-      </c>
-      <c r="C15" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D15" s="17" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="15" t="inlineStr">
-        <is>
-          <t>Core: Referrer</t>
-        </is>
-      </c>
-      <c r="B16" s="15" t="inlineStr">
-        <is>
-          <t>prop2 (Referrer)</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D16" s="17" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="15" t="inlineStr">
-        <is>
-          <t>Core: Timestamp</t>
-        </is>
-      </c>
-      <c r="B17" s="15" t="inlineStr">
-        <is>
-          <t>prop3 (Time Stamp)</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D17" s="17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="15" t="inlineStr">
-        <is>
-          <t>File: Name</t>
-        </is>
-      </c>
-      <c r="B18" s="15" t="inlineStr">
-        <is>
-          <t>eVar33 (File Name)</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D18" s="17" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="15" t="inlineStr">
-        <is>
-          <t>File: Type</t>
-        </is>
-      </c>
-      <c r="B19" s="15" t="inlineStr">
-        <is>
-          <t>eVar34 (File Type)</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D19" s="17" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="30" t="inlineStr">
-        <is>
-          <t>File: URL</t>
-        </is>
-      </c>
-      <c r="B20" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C20" s="31" t="inlineStr">
-        <is>
-          <t>Not wired (orphan element)</t>
-        </is>
-      </c>
-      <c r="D20" s="32" t="inlineStr">
+      <c r="D20" s="47" t="inlineStr">
         <is>
           <t>File downloads capture Name + Type; URL is carried but not sent.</t>
         </is>
@@ -4586,965 +4729,961 @@
       </c>
       <c r="B21" s="30" t="inlineStr">
         <is>
+          <t>list1 (list)</t>
+        </is>
+      </c>
+      <c r="C21" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D21" s="32" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="30" t="inlineStr">
+        <is>
+          <t>Form: Location</t>
+        </is>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>eVar19 (Email Registration Location)</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D22" s="32" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="30" t="inlineStr">
+        <is>
+          <t>Form: Name</t>
+        </is>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>eVar10 (Form Name)</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D23" s="32" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="30" t="inlineStr">
+        <is>
+          <t>Geo: Country</t>
+        </is>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>eVar47 (Country Code)</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D24" s="32" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="30" t="inlineStr">
+        <is>
+          <t>Geo: Language</t>
+        </is>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>eVar18 (Language)</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D25" s="32" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="30" t="inlineStr">
+        <is>
+          <t>Geo: Locale</t>
+        </is>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>prop20 (Locale)</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D26" s="32" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="45" t="inlineStr">
+        <is>
+          <t>Link: Amazon Redirect</t>
+        </is>
+      </c>
+      <c r="B27" s="45" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C21" s="31" t="inlineStr">
+      <c r="C27" s="46" t="inlineStr">
         <is>
           <t>Not wired (orphan element)</t>
         </is>
       </c>
-      <c r="D21" s="32" t="inlineStr">
-        <is>
-          <t>Carried but not referenced by any payload.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="15" t="inlineStr">
-        <is>
-          <t>Form: Location</t>
-        </is>
-      </c>
-      <c r="B22" s="15" t="inlineStr">
-        <is>
-          <t>eVar19 (Email Registration Location)</t>
-        </is>
-      </c>
-      <c r="C22" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D22" s="17" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="15" t="inlineStr">
-        <is>
-          <t>Form: Name</t>
-        </is>
-      </c>
-      <c r="B23" s="15" t="inlineStr">
-        <is>
-          <t>eVar10 (Form Name)</t>
-        </is>
-      </c>
-      <c r="C23" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D23" s="17" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="15" t="inlineStr">
-        <is>
-          <t>Geo: Country</t>
-        </is>
-      </c>
-      <c r="B24" s="15" t="inlineStr">
-        <is>
-          <t>eVar47 (Country Code)</t>
-        </is>
-      </c>
-      <c r="C24" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D24" s="17" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="15" t="inlineStr">
-        <is>
-          <t>Geo: Language</t>
-        </is>
-      </c>
-      <c r="B25" s="15" t="inlineStr">
-        <is>
-          <t>eVar18 (Language)</t>
-        </is>
-      </c>
-      <c r="C25" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D25" s="17" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="15" t="inlineStr">
-        <is>
-          <t>Geo: Locale</t>
-        </is>
-      </c>
-      <c r="B26" s="15" t="inlineStr">
-        <is>
-          <t>prop20 (Locale)</t>
-        </is>
-      </c>
-      <c r="C26" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D26" s="17" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="30" t="inlineStr">
-        <is>
-          <t>Link: Amazon Redirect</t>
-        </is>
-      </c>
-      <c r="B27" s="30" t="inlineStr">
+      <c r="D27" s="47" t="inlineStr">
+        <is>
+          <t>Not sent — eVar28 (labeled "Amazon Redirect Link") is fed by Link: Redirect Text instead. Possible pre-existing mislabel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="30" t="inlineStr">
+        <is>
+          <t>Link: CTA Button Name</t>
+        </is>
+      </c>
+      <c r="B28" s="30" t="inlineStr">
+        <is>
+          <t>eVar22 (CTA Button Text)</t>
+        </is>
+      </c>
+      <c r="C28" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D28" s="32" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="30" t="inlineStr">
+        <is>
+          <t>Link: Destination</t>
+        </is>
+      </c>
+      <c r="B29" s="30" t="inlineStr">
+        <is>
+          <t>eVar23 (Destination Link)</t>
+        </is>
+      </c>
+      <c r="C29" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D29" s="32" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="30" t="inlineStr">
+        <is>
+          <t>Link: Menu Name</t>
+        </is>
+      </c>
+      <c r="B30" s="30" t="inlineStr">
+        <is>
+          <t>eVar24 (Menu Link)</t>
+        </is>
+      </c>
+      <c r="C30" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D30" s="32" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="30" t="inlineStr">
+        <is>
+          <t>Link: More Amazon News</t>
+        </is>
+      </c>
+      <c r="B31" s="30" t="inlineStr">
+        <is>
+          <t>eVar44 (More Amazon News Title)</t>
+        </is>
+      </c>
+      <c r="C31" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D31" s="32" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="45" t="inlineStr">
+        <is>
+          <t>Link: Name</t>
+        </is>
+      </c>
+      <c r="B32" s="45" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C27" s="31" t="inlineStr">
+      <c r="C32" s="46" t="inlineStr">
         <is>
           <t>Not wired (orphan element)</t>
         </is>
       </c>
-      <c r="D27" s="32" t="inlineStr">
-        <is>
-          <t>Not sent — eVar28 (labeled "Amazon Redirect Link") is fed by Link: Redirect Text instead. Possible pre-existing mislabel.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="15" t="inlineStr">
-        <is>
-          <t>Link: CTA Button Name</t>
-        </is>
-      </c>
-      <c r="B28" s="15" t="inlineStr">
-        <is>
-          <t>eVar22 (CTA Button Text)</t>
-        </is>
-      </c>
-      <c r="C28" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D28" s="17" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="15" t="inlineStr">
-        <is>
-          <t>Link: Destination</t>
-        </is>
-      </c>
-      <c r="B29" s="15" t="inlineStr">
-        <is>
-          <t>eVar23 (Destination Link)</t>
-        </is>
-      </c>
-      <c r="C29" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D29" s="17" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="15" t="inlineStr">
-        <is>
-          <t>Link: Menu Name</t>
-        </is>
-      </c>
-      <c r="B30" s="15" t="inlineStr">
-        <is>
-          <t>eVar24 (Menu Link)</t>
-        </is>
-      </c>
-      <c r="C30" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D30" s="17" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="15" t="inlineStr">
-        <is>
-          <t>Link: More Amazon News</t>
-        </is>
-      </c>
-      <c r="B31" s="15" t="inlineStr">
-        <is>
-          <t>eVar44 (More Amazon News Title)</t>
-        </is>
-      </c>
-      <c r="C31" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D31" s="17" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="30" t="inlineStr">
-        <is>
-          <t>Link: Name</t>
-        </is>
-      </c>
-      <c r="B32" s="30" t="inlineStr">
+      <c r="D32" s="47" t="inlineStr">
+        <is>
+          <t>Generic link name — carried but not wired to any variable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="30" t="inlineStr">
+        <is>
+          <t>Link: Redirect Text</t>
+        </is>
+      </c>
+      <c r="B33" s="30" t="inlineStr">
+        <is>
+          <t>eVar21 (Redirect Link); eVar28 (Amazon Redirect Link)</t>
+        </is>
+      </c>
+      <c r="C33" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D33" s="32" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="30" t="inlineStr">
+        <is>
+          <t>Link: Related Tag</t>
+        </is>
+      </c>
+      <c r="B34" s="30" t="inlineStr">
+        <is>
+          <t>eVar43 (Related Tag Text)</t>
+        </is>
+      </c>
+      <c r="C34" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D34" s="32" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="30" t="inlineStr">
+        <is>
+          <t>Link: Related Tag URL</t>
+        </is>
+      </c>
+      <c r="B35" s="30" t="inlineStr">
+        <is>
+          <t>eVar46 (Related Tags Link)</t>
+        </is>
+      </c>
+      <c r="C35" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D35" s="32" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="30" t="inlineStr">
+        <is>
+          <t>Link: Stories Text</t>
+        </is>
+      </c>
+      <c r="B36" s="30" t="inlineStr">
+        <is>
+          <t>eVar45 (Stories Title)</t>
+        </is>
+      </c>
+      <c r="C36" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D36" s="32" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="30" t="inlineStr">
+        <is>
+          <t>Map: Button Name</t>
+        </is>
+      </c>
+      <c r="B37" s="30" t="inlineStr">
+        <is>
+          <t>eVar50 (Map Button Name)</t>
+        </is>
+      </c>
+      <c r="C37" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D37" s="32" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="30" t="inlineStr">
+        <is>
+          <t>Map: Name</t>
+        </is>
+      </c>
+      <c r="B38" s="30" t="inlineStr">
+        <is>
+          <t>eVar49 (Map Name)</t>
+        </is>
+      </c>
+      <c r="C38" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D38" s="32" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="30" t="inlineStr">
+        <is>
+          <t>News: Filter</t>
+        </is>
+      </c>
+      <c r="B39" s="30" t="inlineStr">
+        <is>
+          <t>eVar27 (Filter)</t>
+        </is>
+      </c>
+      <c r="C39" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D39" s="32" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="30" t="inlineStr">
+        <is>
+          <t>Page: Error</t>
+        </is>
+      </c>
+      <c r="B40" s="30" t="inlineStr">
+        <is>
+          <t>list1 (list); prop19 (Site Error)</t>
+        </is>
+      </c>
+      <c r="C40" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D40" s="32" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="30" t="inlineStr">
+        <is>
+          <t>Page: Name</t>
+        </is>
+      </c>
+      <c r="B41" s="30" t="inlineStr">
+        <is>
+          <t>eVar3 (Page Name); prop1 (Page Name); s.pageName</t>
+        </is>
+      </c>
+      <c r="C41" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D41" s="32" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="30" t="inlineStr">
+        <is>
+          <t>Page: Title</t>
+        </is>
+      </c>
+      <c r="B42" s="30" t="inlineStr">
+        <is>
+          <t>prop18 (Page Title); prop4 (Page Title)</t>
+        </is>
+      </c>
+      <c r="C42" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D42" s="32" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="30" t="inlineStr">
+        <is>
+          <t>Page: URL</t>
+        </is>
+      </c>
+      <c r="B43" s="30" t="inlineStr">
+        <is>
+          <t>eVar12 (Page URL); prop12 (Page URL); s.pageURL</t>
+        </is>
+      </c>
+      <c r="C43" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D43" s="32" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="45" t="inlineStr">
+        <is>
+          <t>Page: View Count</t>
+        </is>
+      </c>
+      <c r="B44" s="45" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C32" s="31" t="inlineStr">
+      <c r="C44" s="46" t="inlineStr">
         <is>
           <t>Not wired (orphan element)</t>
         </is>
       </c>
-      <c r="D32" s="32" t="inlineStr">
-        <is>
-          <t>Generic link name — carried but not wired to any variable.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="15" t="inlineStr">
-        <is>
-          <t>Link: Redirect Text</t>
-        </is>
-      </c>
-      <c r="B33" s="15" t="inlineStr">
-        <is>
-          <t>eVar21 (Redirect Link); eVar28 (Amazon Redirect Link)</t>
-        </is>
-      </c>
-      <c r="C33" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D33" s="17" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="15" t="inlineStr">
-        <is>
-          <t>Link: Related Tag</t>
-        </is>
-      </c>
-      <c r="B34" s="15" t="inlineStr">
-        <is>
-          <t>eVar43 (Related Tag Text)</t>
-        </is>
-      </c>
-      <c r="C34" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D34" s="17" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="15" t="inlineStr">
-        <is>
-          <t>Link: Related Tag URL</t>
-        </is>
-      </c>
-      <c r="B35" s="15" t="inlineStr">
-        <is>
-          <t>eVar46 (Related Tags Link)</t>
-        </is>
-      </c>
-      <c r="C35" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D35" s="17" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="15" t="inlineStr">
-        <is>
-          <t>Link: Stories Text</t>
-        </is>
-      </c>
-      <c r="B36" s="15" t="inlineStr">
-        <is>
-          <t>eVar45 (Stories Title)</t>
-        </is>
-      </c>
-      <c r="C36" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D36" s="17" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="15" t="inlineStr">
-        <is>
-          <t>Map: Button Name</t>
-        </is>
-      </c>
-      <c r="B37" s="15" t="inlineStr">
-        <is>
-          <t>eVar50 (Map Button Name)</t>
-        </is>
-      </c>
-      <c r="C37" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D37" s="17" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="15" t="inlineStr">
-        <is>
-          <t>Map: Name</t>
-        </is>
-      </c>
-      <c r="B38" s="15" t="inlineStr">
-        <is>
-          <t>eVar49 (Map Name)</t>
-        </is>
-      </c>
-      <c r="C38" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D38" s="17" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="15" t="inlineStr">
-        <is>
-          <t>News: Filter</t>
-        </is>
-      </c>
-      <c r="B39" s="15" t="inlineStr">
-        <is>
-          <t>eVar27 (Filter)</t>
-        </is>
-      </c>
-      <c r="C39" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D39" s="17" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="15" t="inlineStr">
-        <is>
-          <t>Page: Error</t>
-        </is>
-      </c>
-      <c r="B40" s="15" t="inlineStr">
-        <is>
-          <t>prop19 (Site Error)</t>
-        </is>
-      </c>
-      <c r="C40" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D40" s="17" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="15" t="inlineStr">
-        <is>
-          <t>Page: Name</t>
-        </is>
-      </c>
-      <c r="B41" s="15" t="inlineStr">
-        <is>
-          <t>eVar3 (Page Name); prop1 (Page Name)</t>
-        </is>
-      </c>
-      <c r="C41" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D41" s="17" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="15" t="inlineStr">
-        <is>
-          <t>Page: Title</t>
-        </is>
-      </c>
-      <c r="B42" s="15" t="inlineStr">
-        <is>
-          <t>prop18 (Page Title); prop4 (Page Title)</t>
-        </is>
-      </c>
-      <c r="C42" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D42" s="17" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="15" t="inlineStr">
-        <is>
-          <t>Page: URL</t>
-        </is>
-      </c>
-      <c r="B43" s="15" t="inlineStr">
-        <is>
-          <t>eVar12 (Page URL); prop12 (Page URL)</t>
-        </is>
-      </c>
-      <c r="C43" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D43" s="17" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="30" t="inlineStr">
-        <is>
-          <t>Page: View Count</t>
-        </is>
-      </c>
-      <c r="B44" s="30" t="inlineStr">
+      <c r="D44" s="47" t="inlineStr">
+        <is>
+          <t>Reads pageLoaded.value; not assigned to any variable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="30" t="inlineStr">
+        <is>
+          <t>Plugin: Previous Page Name</t>
+        </is>
+      </c>
+      <c r="B45" s="30" t="inlineStr">
+        <is>
+          <t>eVar2 (Previous Page Name); prop11 (Previous Page Name)</t>
+        </is>
+      </c>
+      <c r="C45" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D45" s="32" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="30" t="inlineStr">
+        <is>
+          <t>Plugin: Repeat Vs New</t>
+        </is>
+      </c>
+      <c r="B46" s="30" t="inlineStr">
+        <is>
+          <t>prop16 (Repeat Vs New)</t>
+        </is>
+      </c>
+      <c r="C46" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D46" s="32" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="45" t="inlineStr">
+        <is>
+          <t>Plugin: Time Parting</t>
+        </is>
+      </c>
+      <c r="B47" s="45" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C44" s="31" t="inlineStr">
+      <c r="C47" s="46" t="inlineStr">
         <is>
           <t>Not wired (orphan element)</t>
         </is>
       </c>
-      <c r="D44" s="32" t="inlineStr">
-        <is>
-          <t>Reads pageLoaded.value; not assigned to any variable.</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="15" t="inlineStr">
-        <is>
-          <t>Plugin: Previous Page Name</t>
-        </is>
-      </c>
-      <c r="B45" s="15" t="inlineStr">
-        <is>
-          <t>eVar2 (Previous Page Name); prop11 (Previous Page Name)</t>
-        </is>
-      </c>
-      <c r="C45" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D45" s="17" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="15" t="inlineStr">
-        <is>
-          <t>Plugin: Repeat Vs New</t>
-        </is>
-      </c>
-      <c r="B46" s="15" t="inlineStr">
-        <is>
-          <t>prop16 (Repeat Vs New)</t>
-        </is>
-      </c>
-      <c r="C46" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D46" s="17" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="30" t="inlineStr">
-        <is>
-          <t>Plugin: Time Parting</t>
-        </is>
-      </c>
-      <c r="B47" s="30" t="inlineStr">
+      <c r="D47" s="47" t="inlineStr">
+        <is>
+          <t>Time-parting plugin value; carried but not wired to any variable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="30" t="inlineStr">
+        <is>
+          <t>Plugin: Time Since Last Visit</t>
+        </is>
+      </c>
+      <c r="B48" s="30" t="inlineStr">
+        <is>
+          <t>prop15 (Time Since Last Visit)</t>
+        </is>
+      </c>
+      <c r="C48" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D48" s="32" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="30" t="inlineStr">
+        <is>
+          <t>Plugin: Visit Duration</t>
+        </is>
+      </c>
+      <c r="B49" s="30" t="inlineStr">
+        <is>
+          <t>eVar37 (Visit Duration); prop17 (Visit Duration)</t>
+        </is>
+      </c>
+      <c r="C49" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D49" s="32" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="30" t="inlineStr">
+        <is>
+          <t>Plugin: Visit Number</t>
+        </is>
+      </c>
+      <c r="B50" s="30" t="inlineStr">
+        <is>
+          <t>prop14 (Visit Number)</t>
+        </is>
+      </c>
+      <c r="C50" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D50" s="32" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="30" t="inlineStr">
+        <is>
+          <t>Scroll Depth</t>
+        </is>
+      </c>
+      <c r="B51" s="30" t="inlineStr">
+        <is>
+          <t>eVar20 (Scroll Depth)</t>
+        </is>
+      </c>
+      <c r="C51" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D51" s="32" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="45" t="inlineStr">
+        <is>
+          <t>Search: Filter</t>
+        </is>
+      </c>
+      <c r="B52" s="45" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C47" s="31" t="inlineStr">
+      <c r="C52" s="46" t="inlineStr">
         <is>
           <t>Not wired (orphan element)</t>
         </is>
       </c>
-      <c r="D47" s="32" t="inlineStr">
-        <is>
-          <t>Time-parting plugin value; carried but not wired to any variable.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="15" t="inlineStr">
-        <is>
-          <t>Plugin: Time Since Last Visit</t>
-        </is>
-      </c>
-      <c r="B48" s="15" t="inlineStr">
-        <is>
-          <t>prop15 (Time Since Last Visit)</t>
-        </is>
-      </c>
-      <c r="C48" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D48" s="17" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="15" t="inlineStr">
-        <is>
-          <t>Plugin: Visit Duration</t>
-        </is>
-      </c>
-      <c r="B49" s="15" t="inlineStr">
-        <is>
-          <t>eVar37 (Visit Duration); prop17 (Visit Duration)</t>
-        </is>
-      </c>
-      <c r="C49" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D49" s="17" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="15" t="inlineStr">
-        <is>
-          <t>Plugin: Visit Number</t>
-        </is>
-      </c>
-      <c r="B50" s="15" t="inlineStr">
-        <is>
-          <t>prop14 (Visit Number)</t>
-        </is>
-      </c>
-      <c r="C50" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D50" s="17" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="15" t="inlineStr">
-        <is>
-          <t>Scroll Depth</t>
-        </is>
-      </c>
-      <c r="B51" s="15" t="inlineStr">
-        <is>
-          <t>eVar20 (Scroll Depth)</t>
-        </is>
-      </c>
-      <c r="C51" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D51" s="17" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="30" t="inlineStr">
-        <is>
-          <t>Search: Filter</t>
-        </is>
-      </c>
-      <c r="B52" s="30" t="inlineStr">
+      <c r="D52" s="47" t="inlineStr">
+        <is>
+          <t>Carried but not sent (eVar27 Filter is fed by News: Filter).</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="30" t="inlineStr">
+        <is>
+          <t>Search: Result Click Name</t>
+        </is>
+      </c>
+      <c r="B53" s="30" t="inlineStr">
+        <is>
+          <t>eVar32 (Search Result Selection)</t>
+        </is>
+      </c>
+      <c r="C53" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D53" s="32" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="30" t="inlineStr">
+        <is>
+          <t>Search: Result Page Type</t>
+        </is>
+      </c>
+      <c r="B54" s="30" t="inlineStr">
+        <is>
+          <t>eVar8 (Search Results Page Type)</t>
+        </is>
+      </c>
+      <c r="C54" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D54" s="32" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="30" t="inlineStr">
+        <is>
+          <t>Search: Results</t>
+        </is>
+      </c>
+      <c r="B55" s="30" t="inlineStr">
+        <is>
+          <t>eVar7 (# Search Results)</t>
+        </is>
+      </c>
+      <c r="C55" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D55" s="32" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="30" t="inlineStr">
+        <is>
+          <t>Search: Term</t>
+        </is>
+      </c>
+      <c r="B56" s="30" t="inlineStr">
+        <is>
+          <t>eVar6 (Internal Search Term)</t>
+        </is>
+      </c>
+      <c r="C56" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D56" s="32" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="30" t="inlineStr">
+        <is>
+          <t>Site: Domain</t>
+        </is>
+      </c>
+      <c r="B57" s="30" t="inlineStr">
+        <is>
+          <t>eVar1 (Domain)</t>
+        </is>
+      </c>
+      <c r="C57" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D57" s="32" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="30" t="inlineStr">
+        <is>
+          <t>Site: Section</t>
+        </is>
+      </c>
+      <c r="B58" s="30" t="inlineStr">
+        <is>
+          <t>eVar4 (Site Section); prop6 (Site Section); s.channel</t>
+        </is>
+      </c>
+      <c r="C58" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D58" s="32" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="30" t="inlineStr">
+        <is>
+          <t>Site: Section 2</t>
+        </is>
+      </c>
+      <c r="B59" s="30" t="inlineStr">
+        <is>
+          <t>prop7 (Site Section2)</t>
+        </is>
+      </c>
+      <c r="C59" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D59" s="32" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="30" t="inlineStr">
+        <is>
+          <t>Site: Section 3</t>
+        </is>
+      </c>
+      <c r="B60" s="30" t="inlineStr">
+        <is>
+          <t>prop8 (Site Section3)</t>
+        </is>
+      </c>
+      <c r="C60" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D60" s="32" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="30" t="inlineStr">
+        <is>
+          <t>Site: Section 4</t>
+        </is>
+      </c>
+      <c r="B61" s="30" t="inlineStr">
+        <is>
+          <t>prop9 (Site Section4)</t>
+        </is>
+      </c>
+      <c r="C61" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D61" s="32" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="30" t="inlineStr">
+        <is>
+          <t>Site: Section 5</t>
+        </is>
+      </c>
+      <c r="B62" s="30" t="inlineStr">
+        <is>
+          <t>prop10 (Site Section5)</t>
+        </is>
+      </c>
+      <c r="C62" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D62" s="32" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="30" t="inlineStr">
+        <is>
+          <t>Social: Interaction Info</t>
+        </is>
+      </c>
+      <c r="B63" s="30" t="inlineStr">
+        <is>
+          <t>eVar17 (Social Link Name)</t>
+        </is>
+      </c>
+      <c r="C63" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D63" s="32" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="30" t="inlineStr">
+        <is>
+          <t>UTM: Campaign</t>
+        </is>
+      </c>
+      <c r="B64" s="30" t="inlineStr">
+        <is>
+          <t>eVar41 (UTM Campaign)</t>
+        </is>
+      </c>
+      <c r="C64" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D64" s="32" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="30" t="inlineStr">
+        <is>
+          <t>UTM: Content</t>
+        </is>
+      </c>
+      <c r="B65" s="30" t="inlineStr">
+        <is>
+          <t>eVar40 (UTM Content)</t>
+        </is>
+      </c>
+      <c r="C65" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D65" s="32" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="30" t="inlineStr">
+        <is>
+          <t>UTM: Medium</t>
+        </is>
+      </c>
+      <c r="B66" s="30" t="inlineStr">
+        <is>
+          <t>eVar39 (UTM Medium)</t>
+        </is>
+      </c>
+      <c r="C66" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D66" s="32" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="30" t="inlineStr">
+        <is>
+          <t>UTM: Source</t>
+        </is>
+      </c>
+      <c r="B67" s="30" t="inlineStr">
+        <is>
+          <t>eVar38 (UTM Source)</t>
+        </is>
+      </c>
+      <c r="C67" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D67" s="32" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="30" t="inlineStr">
+        <is>
+          <t>UTM: Term</t>
+        </is>
+      </c>
+      <c r="B68" s="30" t="inlineStr">
+        <is>
+          <t>eVar42 (UTM Term)</t>
+        </is>
+      </c>
+      <c r="C68" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D68" s="32" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="45" t="inlineStr">
+        <is>
+          <t>User: Login ID</t>
+        </is>
+      </c>
+      <c r="B69" s="45" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C52" s="31" t="inlineStr">
+      <c r="C69" s="46" t="inlineStr">
         <is>
           <t>Not wired (orphan element)</t>
         </is>
       </c>
-      <c r="D52" s="32" t="inlineStr">
-        <is>
-          <t>Carried but not sent (eVar27 Filter is fed by News: Filter).</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="15" t="inlineStr">
-        <is>
-          <t>Search: Result Click Name</t>
-        </is>
-      </c>
-      <c r="B53" s="15" t="inlineStr">
-        <is>
-          <t>eVar32 (Search Result Selection)</t>
-        </is>
-      </c>
-      <c r="C53" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D53" s="17" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="15" t="inlineStr">
-        <is>
-          <t>Search: Result Page Type</t>
-        </is>
-      </c>
-      <c r="B54" s="15" t="inlineStr">
-        <is>
-          <t>eVar8 (Search Results Page Type)</t>
-        </is>
-      </c>
-      <c r="C54" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D54" s="17" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="15" t="inlineStr">
-        <is>
-          <t>Search: Results</t>
-        </is>
-      </c>
-      <c r="B55" s="15" t="inlineStr">
-        <is>
-          <t>eVar7 (# Search Results)</t>
-        </is>
-      </c>
-      <c r="C55" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D55" s="17" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="15" t="inlineStr">
-        <is>
-          <t>Search: Term</t>
-        </is>
-      </c>
-      <c r="B56" s="15" t="inlineStr">
-        <is>
-          <t>eVar6 (Internal Search Term)</t>
-        </is>
-      </c>
-      <c r="C56" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D56" s="17" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="15" t="inlineStr">
-        <is>
-          <t>Site: Domain</t>
-        </is>
-      </c>
-      <c r="B57" s="15" t="inlineStr">
-        <is>
-          <t>eVar1 (Domain)</t>
-        </is>
-      </c>
-      <c r="C57" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D57" s="17" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="15" t="inlineStr">
-        <is>
-          <t>Site: Section</t>
-        </is>
-      </c>
-      <c r="B58" s="15" t="inlineStr">
-        <is>
-          <t>eVar4 (Site Section); prop6 (Site Section)</t>
-        </is>
-      </c>
-      <c r="C58" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D58" s="17" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="15" t="inlineStr">
-        <is>
-          <t>Site: Section 2</t>
-        </is>
-      </c>
-      <c r="B59" s="15" t="inlineStr">
-        <is>
-          <t>prop7 (Site Section2)</t>
-        </is>
-      </c>
-      <c r="C59" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D59" s="17" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="15" t="inlineStr">
-        <is>
-          <t>Site: Section 3</t>
-        </is>
-      </c>
-      <c r="B60" s="15" t="inlineStr">
-        <is>
-          <t>prop8 (Site Section3)</t>
-        </is>
-      </c>
-      <c r="C60" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D60" s="17" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="15" t="inlineStr">
-        <is>
-          <t>Site: Section 4</t>
-        </is>
-      </c>
-      <c r="B61" s="15" t="inlineStr">
-        <is>
-          <t>prop9 (Site Section4)</t>
-        </is>
-      </c>
-      <c r="C61" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D61" s="17" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="15" t="inlineStr">
-        <is>
-          <t>Site: Section 5</t>
-        </is>
-      </c>
-      <c r="B62" s="15" t="inlineStr">
-        <is>
-          <t>prop10 (Site Section5)</t>
-        </is>
-      </c>
-      <c r="C62" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D62" s="17" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="15" t="inlineStr">
-        <is>
-          <t>Social: Interaction Info</t>
-        </is>
-      </c>
-      <c r="B63" s="15" t="inlineStr">
-        <is>
-          <t>eVar17 (Social Link Name)</t>
-        </is>
-      </c>
-      <c r="C63" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D63" s="17" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="15" t="inlineStr">
-        <is>
-          <t>UTM: Campaign</t>
-        </is>
-      </c>
-      <c r="B64" s="15" t="inlineStr">
-        <is>
-          <t>eVar41 (UTM Campaign)</t>
-        </is>
-      </c>
-      <c r="C64" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D64" s="17" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="15" t="inlineStr">
-        <is>
-          <t>UTM: Content</t>
-        </is>
-      </c>
-      <c r="B65" s="15" t="inlineStr">
-        <is>
-          <t>eVar40 (UTM Content)</t>
-        </is>
-      </c>
-      <c r="C65" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D65" s="17" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="15" t="inlineStr">
-        <is>
-          <t>UTM: Medium</t>
-        </is>
-      </c>
-      <c r="B66" s="15" t="inlineStr">
-        <is>
-          <t>eVar39 (UTM Medium)</t>
-        </is>
-      </c>
-      <c r="C66" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D66" s="17" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="15" t="inlineStr">
-        <is>
-          <t>UTM: Source</t>
-        </is>
-      </c>
-      <c r="B67" s="15" t="inlineStr">
-        <is>
-          <t>eVar38 (UTM Source)</t>
-        </is>
-      </c>
-      <c r="C67" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D67" s="17" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="15" t="inlineStr">
-        <is>
-          <t>UTM: Term</t>
-        </is>
-      </c>
-      <c r="B68" s="15" t="inlineStr">
-        <is>
-          <t>eVar42 (UTM Term)</t>
-        </is>
-      </c>
-      <c r="C68" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D68" s="17" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="30" t="inlineStr">
-        <is>
-          <t>User: Login ID</t>
-        </is>
-      </c>
-      <c r="B69" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C69" s="31" t="inlineStr">
-        <is>
-          <t>Not wired (orphan element)</t>
-        </is>
-      </c>
-      <c r="D69" s="32" t="inlineStr">
+      <c r="D69" s="47" t="inlineStr">
         <is>
           <t>Reads loginID from the data layer but no rule sends it and no eVar/prop is assigned. PII review needed.</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="18" t="inlineStr">
+      <c r="A70" s="33" t="inlineStr">
         <is>
           <t>User: Type</t>
         </is>
       </c>
-      <c r="B70" s="18" t="inlineStr">
+      <c r="B70" s="33" t="inlineStr">
         <is>
           <t>eVar15 (User Type)</t>
         </is>
       </c>
-      <c r="C70" s="19" t="inlineStr">
+      <c r="C70" s="34" t="inlineStr">
         <is>
           <t>No data (element is a no-op)</t>
         </is>
       </c>
-      <c r="D70" s="20" t="inlineStr">
+      <c r="D70" s="35" t="inlineStr">
         <is>
           <t>Returns no value (no-op) — the variable it feeds never populates. Decision needed.</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="15" t="inlineStr">
+      <c r="A71" s="30" t="inlineStr">
         <is>
           <t>Video: Name</t>
         </is>
       </c>
-      <c r="B71" s="15" t="inlineStr">
+      <c r="B71" s="30" t="inlineStr">
         <is>
           <t>eVar11 (Video Title)</t>
         </is>
       </c>
-      <c r="C71" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D71" s="17" t="inlineStr"/>
+      <c r="C71" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D71" s="32" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="15" t="inlineStr">
+      <c r="A72" s="30" t="inlineStr">
         <is>
           <t>Video: Type</t>
         </is>
       </c>
-      <c r="B72" s="15" t="inlineStr">
+      <c r="B72" s="30" t="inlineStr">
         <is>
           <t>eVar35 (Video Type)</t>
         </is>
       </c>
-      <c r="C72" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D72" s="17" t="inlineStr"/>
+      <c r="C72" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D72" s="32" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D72"/>
@@ -5570,124 +5709,124 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="14" t="inlineStr">
+      <c r="A1" s="29" t="inlineStr">
         <is>
           <t>List Var</t>
         </is>
       </c>
-      <c r="B1" s="14" t="inlineStr">
+      <c r="B1" s="29" t="inlineStr">
         <is>
           <t>Report Suite Name</t>
         </is>
       </c>
-      <c r="C1" s="14" t="inlineStr">
+      <c r="C1" s="29" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="D1" s="14" t="inlineStr">
+      <c r="D1" s="29" t="inlineStr">
         <is>
           <t>Data Element(s)</t>
         </is>
       </c>
-      <c r="E1" s="14" t="inlineStr">
+      <c r="E1" s="29" t="inlineStr">
         <is>
           <t>Sent By Rule(s)</t>
         </is>
       </c>
-      <c r="F1" s="14" t="inlineStr">
+      <c r="F1" s="29" t="inlineStr">
         <is>
           <t>Notes / Issue</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="30" t="inlineStr">
         <is>
           <t>list1</t>
         </is>
       </c>
-      <c r="B2" s="15" t="inlineStr">
+      <c r="B2" s="30" t="inlineStr">
         <is>
           <t>(config not captured — see note)</t>
         </is>
       </c>
-      <c r="C2" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D2" s="17" t="inlineStr">
+      <c r="C2" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D2" s="32" t="inlineStr">
         <is>
           <t>Form: Error Name; Page: Error</t>
         </is>
       </c>
-      <c r="E2" s="17" t="inlineStr">
+      <c r="E2" s="32" t="inlineStr">
         <is>
           <t>Form Error Tracking; Global Page Load Rule; Site Error</t>
         </is>
       </c>
-      <c r="F2" s="17" t="inlineStr">
+      <c r="F2" s="32" t="inlineStr">
         <is>
           <t>SHARED list: carries Form: Error Name + Page: Error from different rules (a unified error list). Parity with the source property — confirm with the analytics owner it is intended, not a collision.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="30" t="inlineStr">
         <is>
           <t>list2</t>
         </is>
       </c>
-      <c r="B3" s="15" t="inlineStr">
+      <c r="B3" s="30" t="inlineStr">
         <is>
           <t>(config not captured — see note)</t>
         </is>
       </c>
-      <c r="C3" s="16" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D3" s="17" t="inlineStr">
+      <c r="C3" s="31" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D3" s="32" t="inlineStr">
         <is>
           <t>Content: Hidden Tags</t>
         </is>
       </c>
-      <c r="E3" s="17" t="inlineStr">
+      <c r="E3" s="32" t="inlineStr">
         <is>
           <t>Global Page Load Rule</t>
         </is>
       </c>
-      <c r="F3" s="17" t="inlineStr"/>
+      <c r="F3" s="32" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="24" t="inlineStr">
+      <c r="A4" s="39" t="inlineStr">
         <is>
           <t>list3</t>
         </is>
       </c>
-      <c r="B4" s="24" t="inlineStr">
+      <c r="B4" s="39" t="inlineStr">
         <is>
           <t>(config not captured)</t>
         </is>
       </c>
-      <c r="C4" s="25" t="inlineStr">
+      <c r="C4" s="40" t="inlineStr">
         <is>
           <t>Defined, old property never sent</t>
         </is>
       </c>
-      <c r="D4" s="26" t="inlineStr">
+      <c r="D4" s="41" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E4" s="26" t="inlineStr">
+      <c r="E4" s="41" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F4" s="26" t="inlineStr">
+      <c r="F4" s="41" t="inlineStr">
         <is>
           <t>Not populated by this build. Adobe supports list1-3; provide the report suite List Variables config (Admin &gt; Report Suite &gt; Edit Settings &gt; Conversion &gt; List Variables) to reconcile names/delimiters.</t>
         </is>
@@ -5717,362 +5856,362 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="14" t="inlineStr">
+      <c r="A1" s="29" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B1" s="14" t="inlineStr">
+      <c r="B1" s="29" t="inlineStr">
         <is>
           <t>Issue</t>
         </is>
       </c>
-      <c r="C1" s="14" t="inlineStr">
+      <c r="C1" s="29" t="inlineStr">
         <is>
           <t>Severity</t>
         </is>
       </c>
-      <c r="D1" s="14" t="inlineStr">
+      <c r="D1" s="29" t="inlineStr">
         <is>
           <t>Affected Variables / Elements</t>
         </is>
       </c>
-      <c r="E1" s="14" t="inlineStr">
+      <c r="E1" s="29" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="F1" s="14" t="inlineStr">
+      <c r="F1" s="29" t="inlineStr">
         <is>
           <t>Recommendation</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="33" t="n">
+      <c r="A2" s="48" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="33" t="inlineStr">
+      <c r="B2" s="48" t="inlineStr">
         <is>
           <t>User Type never collects</t>
         </is>
       </c>
-      <c r="C2" s="34" t="inlineStr">
+      <c r="C2" s="49" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="D2" s="34" t="inlineStr">
+      <c r="D2" s="49" t="inlineStr">
         <is>
           <t>eVar15 · User: Type</t>
         </is>
       </c>
-      <c r="E2" s="34" t="inlineStr">
+      <c r="E2" s="49" t="inlineStr">
         <is>
           <t>The User: Type element is a stub that returns an empty string, so eVar15 has never captured a value in the current property.</t>
         </is>
       </c>
-      <c r="F2" s="34" t="inlineStr">
+      <c r="F2" s="49" t="inlineStr">
         <is>
           <t>Confirm what defines "user type" (logged-in vs anonymous, subscriber tier, etc.) and where it lives, then implement — or exclude. See client email #1.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="33" t="n">
+      <c r="A3" s="48" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="33" t="inlineStr">
+      <c r="B3" s="48" t="inlineStr">
         <is>
           <t>Login ID orphan + PII</t>
         </is>
       </c>
-      <c r="C3" s="34" t="inlineStr">
+      <c r="C3" s="49" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="D3" s="34" t="inlineStr">
+      <c r="D3" s="49" t="inlineStr">
         <is>
           <t>User: Login ID (no eVar/prop)</t>
         </is>
       </c>
-      <c r="E3" s="34" t="inlineStr">
+      <c r="E3" s="49" t="inlineStr">
         <is>
           <t>The User: Login ID element reads loginID from the data layer, but no rule sends it and no report variable is assigned — it is never collected.</t>
         </is>
       </c>
-      <c r="F3" s="34" t="inlineStr">
+      <c r="F3" s="49" t="inlineStr">
         <is>
           <t>Confirm whether login ID is wanted and which variable holds it. If it can identify a person, hash before collection. See client email #2.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="33" t="n">
+      <c r="A4" s="48" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="33" t="inlineStr">
+      <c r="B4" s="48" t="inlineStr">
         <is>
           <t>Internal Campaign no-op</t>
         </is>
       </c>
-      <c r="C4" s="34" t="inlineStr">
+      <c r="C4" s="49" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="D4" s="34" t="inlineStr">
+      <c r="D4" s="49" t="inlineStr">
         <is>
           <t>eVar5 · event4 · Campaign: Internal</t>
         </is>
       </c>
-      <c r="E4" s="34" t="inlineStr">
+      <c r="E4" s="49" t="inlineStr">
         <is>
           <t>Campaign: Internal is console.log(); (returns undefined) — parity with the source, where eVar5/event4 have never populated. event4 is filtered out of the page view.</t>
         </is>
       </c>
-      <c r="F4" s="34" t="inlineStr">
+      <c r="F4" s="49" t="inlineStr">
         <is>
           <t>Keep as-is for parity, or supply the real internal-campaign parameter to activate eVar5/event4. Deferred by design.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="33" t="n">
+      <c r="A5" s="48" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="33" t="inlineStr">
+      <c r="B5" s="48" t="inlineStr">
         <is>
           <t>Audio feature not implemented</t>
         </is>
       </c>
-      <c r="C5" s="34" t="inlineStr">
+      <c r="C5" s="49" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="D5" s="34" t="inlineStr">
+      <c r="D5" s="49" t="inlineStr">
         <is>
           <t>eVar51-54 · event35-39</t>
         </is>
       </c>
-      <c r="E5" s="34" t="inlineStr">
+      <c r="E5" s="49" t="inlineStr">
         <is>
           <t>A complete audio tracking feature (Start/Complete/Milestones + Title/Action/Duration/% Played) is defined in the report suite but was NEVER implemented in the old Launch property. Video is implemented; audio is not.</t>
         </is>
       </c>
-      <c r="F5" s="34" t="inlineStr">
+      <c r="F5" s="49" t="inlineStr">
         <is>
           <t>Net-new scope if wanted — typically Web SDK media (streaming) collection, separate from data-layer rules. Scope + estimate separately. See client email #3.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="33" t="n">
+      <c r="A6" s="48" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="33" t="inlineStr">
+      <c r="B6" s="48" t="inlineStr">
         <is>
           <t>ECID not captured (by design)</t>
         </is>
       </c>
-      <c r="C6" s="34" t="inlineStr">
+      <c r="C6" s="49" t="inlineStr">
         <is>
           <t>Info</t>
         </is>
       </c>
-      <c r="D6" s="34" t="inlineStr">
+      <c r="D6" s="49" t="inlineStr">
         <is>
           <t>eVar14 · prop13</t>
         </is>
       </c>
-      <c r="E6" s="34" t="inlineStr">
+      <c r="E6" s="49" t="inlineStr">
         <is>
           <t>ECID is intentionally not written to an eVar/prop under Web SDK — the SDK manages identity natively. The source ECID element was a broken recursive stub (excluded).</t>
         </is>
       </c>
-      <c r="F6" s="34" t="inlineStr">
+      <c r="F6" s="49" t="inlineStr">
         <is>
           <t>No action — correct Web SDK design. Confirm the client does not specifically need ECID surfaced in a variable.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="33" t="n">
+      <c r="A7" s="48" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="33" t="inlineStr">
+      <c r="B7" s="48" t="inlineStr">
         <is>
           <t>event28 double-booked</t>
         </is>
       </c>
-      <c r="C7" s="34" t="inlineStr">
+      <c r="C7" s="49" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="D7" s="34" t="inlineStr">
+      <c r="D7" s="49" t="inlineStr">
         <is>
           <t>event28 (Video Pause + Article draft)</t>
         </is>
       </c>
-      <c r="E7" s="34" t="inlineStr">
+      <c r="E7" s="49" t="inlineStr">
         <is>
           <t>event28 is used by Video Pause (live) and by the excluded, never-published Article Interaction Tracking draft. Currently latent because the Article rule is excluded.</t>
         </is>
       </c>
-      <c r="F7" s="34" t="inlineStr">
+      <c r="F7" s="49" t="inlineStr">
         <is>
           <t>If Article tracking is ever revived, assign it a fresh event number so it does not collide with Video Pause.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="33" t="n">
+      <c r="A8" s="48" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="33" t="inlineStr">
+      <c r="B8" s="48" t="inlineStr">
         <is>
           <t>eVar28 label vs value</t>
         </is>
       </c>
-      <c r="C8" s="34" t="inlineStr">
+      <c r="C8" s="49" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="D8" s="34" t="inlineStr">
+      <c r="D8" s="49" t="inlineStr">
         <is>
           <t>eVar28 · Link: Redirect Text · Link: Amazon Redirect</t>
         </is>
       </c>
-      <c r="E8" s="34" t="inlineStr">
+      <c r="E8" s="49" t="inlineStr">
         <is>
           <t>eVar28 is labeled "Amazon Redirect Link" in the report suite but is fed by Link: Redirect Text (the redirect link TEXT). eVar21 (Redirect Link) is also fed by Link: Redirect Text. The Link: Amazon Redirect element is unused.</t>
         </is>
       </c>
-      <c r="F8" s="34" t="inlineStr">
+      <c r="F8" s="49" t="inlineStr">
         <is>
           <t>Carried as-is for parity. Analytics owner should confirm the intended eVar28 mapping (label vs value) — likely a pre-existing mislabel in the source.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="33" t="n">
+      <c r="A9" s="48" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="33" t="inlineStr">
+      <c r="B9" s="48" t="inlineStr">
         <is>
           <t>eVar26 duplicate label</t>
         </is>
       </c>
-      <c r="C9" s="34" t="inlineStr">
+      <c r="C9" s="49" t="inlineStr">
         <is>
           <t>Info</t>
         </is>
       </c>
-      <c r="D9" s="34" t="inlineStr">
+      <c r="D9" s="49" t="inlineStr">
         <is>
           <t>eVar26 (duplicate of eVar9)</t>
         </is>
       </c>
-      <c r="E9" s="34" t="inlineStr">
+      <c r="E9" s="49" t="inlineStr">
         <is>
           <t>eVar26 is labeled "Content Type", the same as eVar9. eVar9 is populated; eVar26 is not — it appears to be an unused duplicate.</t>
         </is>
       </c>
-      <c r="F9" s="34" t="inlineStr">
+      <c r="F9" s="49" t="inlineStr">
         <is>
           <t>No action needed, or repurpose eVar26 for a new dimension. Confirm with analytics owner.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="33" t="n">
+      <c r="A10" s="48" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="33" t="inlineStr">
+      <c r="B10" s="48" t="inlineStr">
         <is>
           <t>Orphan data elements</t>
         </is>
       </c>
-      <c r="C10" s="34" t="inlineStr">
+      <c r="C10" s="49" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="D10" s="34" t="inlineStr">
+      <c r="D10" s="49" t="inlineStr">
         <is>
           <t>9 elements (see Data Elements tab)</t>
         </is>
       </c>
-      <c r="E10" s="34" t="inlineStr">
+      <c r="E10" s="49" t="inlineStr">
         <is>
           <t>Nine carried elements are not wired to any variable: Article: Content Type/Name (excluded rule), File: URL, Link: Amazon Redirect, Link: Name, Page: View Count, Plugin: Time Parting, Search: Filter, User: Login ID.</t>
         </is>
       </c>
-      <c r="F10" s="34" t="inlineStr">
+      <c r="F10" s="49" t="inlineStr">
         <is>
           <t>Review use-or-remove. Most are harmless carry-overs; User: Login ID and Link: Amazon Redirect are called out separately (issues #2, #7).</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="33" t="n">
+      <c r="A11" s="48" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="33" t="inlineStr">
+      <c r="B11" s="48" t="inlineStr">
         <is>
           <t>list1 shared across error types</t>
         </is>
       </c>
-      <c r="C11" s="34" t="inlineStr">
+      <c r="C11" s="49" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="D11" s="34" t="inlineStr">
+      <c r="D11" s="49" t="inlineStr">
         <is>
           <t>list1 · Page: Error · Form: Error Name</t>
         </is>
       </c>
-      <c r="E11" s="34" t="inlineStr">
+      <c r="E11" s="49" t="inlineStr">
         <is>
           <t>list1 carries Site Error (page views + Site Error rule) AND Form Error Name (Form Error Tracking) — a unified error list. Carried from the source property (parity).</t>
         </is>
       </c>
-      <c r="F11" s="34" t="inlineStr">
+      <c r="F11" s="49" t="inlineStr">
         <is>
           <t>Confirm with the analytics owner that list1 is intended as a combined error list. Provide the report suite List Variables config to reconcile names/delimiters and confirm list3 status.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="33" t="n">
+      <c r="A12" s="48" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="33" t="inlineStr">
+      <c r="B12" s="48" t="inlineStr">
         <is>
           <t>Empty values omitted</t>
         </is>
       </c>
-      <c r="C12" s="34" t="inlineStr">
+      <c r="C12" s="49" t="inlineStr">
         <is>
           <t>Info</t>
         </is>
       </c>
-      <c r="D12" s="34" t="inlineStr">
+      <c r="D12" s="49" t="inlineStr">
         <is>
           <t>All payloads</t>
         </is>
       </c>
-      <c r="E12" s="34" t="inlineStr">
+      <c r="E12" s="49" t="inlineStr">
         <is>
           <t>The Web SDK build omits empty values, whereas the old XDM elements could emit empty strings. Beacons are cleaner but hit-level QA diffs will show absent-vs-empty differences.</t>
         </is>
       </c>
-      <c r="F12" s="34" t="inlineStr">
+      <c r="F12" s="49" t="inlineStr">
         <is>
           <t>Expected behavior — note for anyone comparing old vs new beacons during QA.</t>
         </is>

--- a/websdk-property/docs/data-collection-reconciliation.xlsx
+++ b/websdk-property/docs/data-collection-reconciliation.xlsx
@@ -8,20 +8,21 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="eVars" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Events" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Elements" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="List Vars" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Issues" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommendations" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="eVars" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Events" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Elements" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="List Vars" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Issues" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'eVars'!$A$1:$G$54</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Props'!$A$1:$G$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Events'!$A$1:$E$39</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Data Elements'!$A$1:$D$72</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'List Vars'!$A$1:$F$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Data Issues'!$A$1:$F$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'eVars'!$A$1:$G$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Props'!$A$1:$G$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Events'!$A$1:$E$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Data Elements'!$A$1:$D$72</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'List Vars'!$A$1:$F$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Data Issues'!$A$1:$F$12</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -30,7 +31,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="22">
+  <fonts count="28">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -151,8 +152,43 @@
       <color rgb="001F4E78"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00808080"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00BF8F00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="001F6E43"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -199,8 +235,23 @@
         <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C00000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00BF8F00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F6E43"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -222,11 +273,16 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="00E0E0E0"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -300,6 +356,34 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1020,6 +1104,325 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="B1:D23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
+    <col width="74" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Recommendations &amp; Next Steps</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="42" customHeight="1">
+      <c r="B2" s="29" t="inlineStr">
+        <is>
+          <t>Migration is at full parity — every variable the current property collects, the new Web SDK property collects. The items below are decisions and clean-ups the reconciliation surfaced, not migration blockers. Detail per item is on the Data Issues tab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="B4" s="30" t="inlineStr">
+        <is>
+          <t>Decisions we need from Amazon News</t>
+        </is>
+      </c>
+      <c r="C4" s="30" t="n"/>
+      <c r="D4" s="30" t="n"/>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="B5" s="31" t="inlineStr">
+        <is>
+          <t>Recommendation</t>
+        </is>
+      </c>
+      <c r="C5" s="31" t="inlineStr">
+        <is>
+          <t>Why it matters</t>
+        </is>
+      </c>
+      <c r="D5" s="31" t="inlineStr">
+        <is>
+          <t>When</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="34" customHeight="1">
+      <c r="B6" s="32" t="inlineStr">
+        <is>
+          <t>Decide User Type</t>
+        </is>
+      </c>
+      <c r="C6" s="33" t="inlineStr">
+        <is>
+          <t>Define what "user type" means (logged-in vs anonymous, subscriber tier, …) and where it lives — or retire it. eVar15 returns empty today and never has collected.</t>
+        </is>
+      </c>
+      <c r="D6" s="34" t="inlineStr">
+        <is>
+          <t>Before cutover</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="34" customHeight="1">
+      <c r="B7" s="32" t="inlineStr">
+        <is>
+          <t>Decide Login ID (with privacy)</t>
+        </is>
+      </c>
+      <c r="C7" s="33" t="inlineStr">
+        <is>
+          <t>Confirm whether login ID is wanted and which variable holds it. If it can identify a person, we hash before collection. Orphan today — never sent.</t>
+        </is>
+      </c>
+      <c r="D7" s="34" t="inlineStr">
+        <is>
+          <t>Before cutover</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="34" customHeight="1">
+      <c r="B8" s="32" t="inlineStr">
+        <is>
+          <t>Decide Audio tracking</t>
+        </is>
+      </c>
+      <c r="C8" s="33" t="inlineStr">
+        <is>
+          <t>Audio is fully defined in the report suite (events 35-39 + eVars 51-54) but was never built. If wanted, it is net-new streaming-media scope — we estimate separately.</t>
+        </is>
+      </c>
+      <c r="D8" s="34" t="inlineStr">
+        <is>
+          <t>Before cutover</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="34" customHeight="1">
+      <c r="B9" s="32" t="inlineStr">
+        <is>
+          <t>Confirm consent values</t>
+        </is>
+      </c>
+      <c r="C9" s="33" t="inlineStr">
+        <is>
+          <t>Tell us the exact strings the cookie banner pushes for opt-out vs opt-in so the consent mapping matches reality (currently best-guess).</t>
+        </is>
+      </c>
+      <c r="D9" s="34" t="inlineStr">
+        <is>
+          <t>Before cutover</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="B11" s="35" t="inlineStr">
+        <is>
+          <t>Analytics-owner confirmations (no build change)</t>
+        </is>
+      </c>
+      <c r="C11" s="35" t="n"/>
+      <c r="D11" s="35" t="n"/>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="B12" s="31" t="inlineStr">
+        <is>
+          <t>Recommendation</t>
+        </is>
+      </c>
+      <c r="C12" s="31" t="inlineStr">
+        <is>
+          <t>Why it matters</t>
+        </is>
+      </c>
+      <c r="D12" s="31" t="inlineStr">
+        <is>
+          <t>When</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="34" customHeight="1">
+      <c r="B13" s="32" t="inlineStr">
+        <is>
+          <t>Confirm list1 as a shared error list</t>
+        </is>
+      </c>
+      <c r="C13" s="33" t="inlineStr">
+        <is>
+          <t>list1 carries Site Error and Form Error together (parity with today). Confirm that unified error list is intended, not a collision.</t>
+        </is>
+      </c>
+      <c r="D13" s="36" t="inlineStr">
+        <is>
+          <t>Quick confirm</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="34" customHeight="1">
+      <c r="B14" s="32" t="inlineStr">
+        <is>
+          <t>Confirm eVar28 mapping</t>
+        </is>
+      </c>
+      <c r="C14" s="33" t="inlineStr">
+        <is>
+          <t>eVar28 is labeled "Amazon Redirect Link" but carries the redirect link TEXT (as it does today). Confirm the intended value, or relabel — likely a pre-existing mislabel.</t>
+        </is>
+      </c>
+      <c r="D14" s="36" t="inlineStr">
+        <is>
+          <t>Quick confirm</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="34" customHeight="1">
+      <c r="B15" s="32" t="inlineStr">
+        <is>
+          <t>Resolve eVar26 duplicate</t>
+        </is>
+      </c>
+      <c r="C15" s="33" t="inlineStr">
+        <is>
+          <t>eVar26 duplicates eVar9 ("Content Type") and is unused. Repurpose it for a new dimension or leave as-is.</t>
+        </is>
+      </c>
+      <c r="D15" s="36" t="inlineStr">
+        <is>
+          <t>Quick confirm</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="34" customHeight="1">
+      <c r="B16" s="32" t="inlineStr">
+        <is>
+          <t>Re-number event28 if Article is revived</t>
+        </is>
+      </c>
+      <c r="C16" s="33" t="inlineStr">
+        <is>
+          <t>event28 is shared with the excluded (never-published) Article draft. Latent today; assign a fresh number before reviving Article tracking.</t>
+        </is>
+      </c>
+      <c r="D16" s="36" t="inlineStr">
+        <is>
+          <t>If reviving Article</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="B18" s="37" t="inlineStr">
+        <is>
+          <t>Housekeeping to finalize the picture</t>
+        </is>
+      </c>
+      <c r="C18" s="37" t="n"/>
+      <c r="D18" s="37" t="n"/>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="B19" s="31" t="inlineStr">
+        <is>
+          <t>Recommendation</t>
+        </is>
+      </c>
+      <c r="C19" s="31" t="inlineStr">
+        <is>
+          <t>Why it matters</t>
+        </is>
+      </c>
+      <c r="D19" s="31" t="inlineStr">
+        <is>
+          <t>When</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="34" customHeight="1">
+      <c r="B20" s="32" t="inlineStr">
+        <is>
+          <t>Review 9 orphan data elements</t>
+        </is>
+      </c>
+      <c r="C20" s="33" t="inlineStr">
+        <is>
+          <t>Nine carried elements feed no variable (see Data Elements tab). Decide keep-or-remove; most are harmless carry-overs.</t>
+        </is>
+      </c>
+      <c r="D20" s="38" t="inlineStr">
+        <is>
+          <t>Post-cutover OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="34" customHeight="1">
+      <c r="B21" s="32" t="inlineStr">
+        <is>
+          <t>Send List Variables report-suite config</t>
+        </is>
+      </c>
+      <c r="C21" s="33" t="inlineStr">
+        <is>
+          <t>The one screenshot we do not have (Admin &gt; Report Suite &gt; Conversion &gt; List Variables). Lets us complete names/delimiters and confirm list3.</t>
+        </is>
+      </c>
+      <c r="D21" s="38" t="inlineStr">
+        <is>
+          <t>Anytime</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="34" customHeight="1">
+      <c r="B22" s="32" t="inlineStr">
+        <is>
+          <t>Internal Campaign stays a no-op</t>
+        </is>
+      </c>
+      <c r="C22" s="33" t="inlineStr">
+        <is>
+          <t>Kept verbatim (console.log) for parity — eVar5/event4 stay inactive until a real internal-campaign parameter is confirmed. No action unless you want it live.</t>
+        </is>
+      </c>
+      <c r="D22" s="38" t="inlineStr">
+        <is>
+          <t>No action</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="34" customHeight="1">
+      <c r="B23" s="32" t="inlineStr">
+        <is>
+          <t>Document the cutover date</t>
+        </is>
+      </c>
+      <c r="C23" s="33" t="inlineStr">
+        <is>
+          <t>Record the go-live date as the historical-trend boundary (per the audit) so analysts read pre/post data correctly.</t>
+        </is>
+      </c>
+      <c r="D23" s="38" t="inlineStr">
+        <is>
+          <t>At cutover</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1033,1720 +1436,1720 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="29" t="inlineStr">
+      <c r="A1" s="39" t="inlineStr">
         <is>
           <t>eVar #</t>
         </is>
       </c>
-      <c r="B1" s="29" t="inlineStr">
+      <c r="B1" s="39" t="inlineStr">
         <is>
           <t>Report Suite Name</t>
         </is>
       </c>
-      <c r="C1" s="29" t="inlineStr">
+      <c r="C1" s="39" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="D1" s="29" t="inlineStr">
+      <c r="D1" s="39" t="inlineStr">
         <is>
           <t>Data Element(s)</t>
         </is>
       </c>
-      <c r="E1" s="29" t="inlineStr">
+      <c r="E1" s="39" t="inlineStr">
         <is>
           <t>Sent By Rule(s)</t>
         </is>
       </c>
-      <c r="F1" s="29" t="inlineStr">
+      <c r="F1" s="39" t="inlineStr">
         <is>
           <t>Data Element Source</t>
         </is>
       </c>
-      <c r="G1" s="29" t="inlineStr">
+      <c r="G1" s="39" t="inlineStr">
         <is>
           <t>Notes / Issue</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="30" t="n">
+      <c r="A2" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="30" t="inlineStr">
+      <c r="B2" s="40" t="inlineStr">
         <is>
           <t>Domain</t>
         </is>
       </c>
-      <c r="C2" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D2" s="32" t="inlineStr">
+      <c r="C2" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D2" s="42" t="inlineStr">
         <is>
           <t>Site: Domain</t>
         </is>
       </c>
-      <c r="E2" s="32" t="inlineStr">
+      <c r="E2" s="42" t="inlineStr">
         <is>
           <t>Global Page Load Rule</t>
         </is>
       </c>
-      <c r="F2" s="32" t="inlineStr">
+      <c r="F2" s="42" t="inlineStr">
         <is>
           <t>web.webPageDetails.site</t>
         </is>
       </c>
-      <c r="G2" s="32" t="inlineStr"/>
+      <c r="G2" s="42" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="30" t="n">
+      <c r="A3" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="30" t="inlineStr">
+      <c r="B3" s="40" t="inlineStr">
         <is>
           <t>Previous Page Name</t>
         </is>
       </c>
-      <c r="C3" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D3" s="32" t="inlineStr">
+      <c r="C3" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D3" s="42" t="inlineStr">
         <is>
           <t>Plugin: Previous Page Name</t>
         </is>
       </c>
-      <c r="E3" s="32" t="inlineStr">
+      <c r="E3" s="42" t="inlineStr">
         <is>
           <t>Global Page Load Rule</t>
         </is>
       </c>
-      <c r="F3" s="32" t="inlineStr">
+      <c r="F3" s="42" t="inlineStr">
         <is>
           <t>cwsdkp-getpreviousvalue</t>
         </is>
       </c>
-      <c r="G3" s="32" t="inlineStr"/>
+      <c r="G3" s="42" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="30" t="n">
+      <c r="A4" s="40" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="30" t="inlineStr">
+      <c r="B4" s="40" t="inlineStr">
         <is>
           <t>Page Name</t>
         </is>
       </c>
-      <c r="C4" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D4" s="32" t="inlineStr">
+      <c r="C4" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D4" s="42" t="inlineStr">
         <is>
           <t>Page: Name</t>
         </is>
       </c>
-      <c r="E4" s="32" t="inlineStr">
+      <c r="E4" s="42" t="inlineStr">
         <is>
           <t>Global Page Load Rule</t>
         </is>
       </c>
-      <c r="F4" s="32" t="inlineStr">
+      <c r="F4" s="42" t="inlineStr">
         <is>
           <t>web.webPageDetails.pageName</t>
         </is>
       </c>
-      <c r="G4" s="32" t="inlineStr"/>
+      <c r="G4" s="42" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="30" t="n">
+      <c r="A5" s="40" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="30" t="inlineStr">
+      <c r="B5" s="40" t="inlineStr">
         <is>
           <t>Site Section</t>
         </is>
       </c>
-      <c r="C5" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D5" s="32" t="inlineStr">
+      <c r="C5" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D5" s="42" t="inlineStr">
         <is>
           <t>Site: Section</t>
         </is>
       </c>
-      <c r="E5" s="32" t="inlineStr">
+      <c r="E5" s="42" t="inlineStr">
         <is>
           <t>Global Page Load Rule</t>
         </is>
       </c>
-      <c r="F5" s="32" t="inlineStr">
+      <c r="F5" s="42" t="inlineStr">
         <is>
           <t>web.webPageDetails.siteSection</t>
         </is>
       </c>
-      <c r="G5" s="32" t="inlineStr"/>
+      <c r="G5" s="42" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="33" t="n">
+      <c r="A6" s="43" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="33" t="inlineStr">
+      <c r="B6" s="43" t="inlineStr">
         <is>
           <t>Internal Campaign</t>
         </is>
       </c>
-      <c r="C6" s="34" t="inlineStr">
+      <c r="C6" s="44" t="inlineStr">
         <is>
           <t>No data (element is a no-op)</t>
         </is>
       </c>
-      <c r="D6" s="35" t="inlineStr">
+      <c r="D6" s="45" t="inlineStr">
         <is>
           <t>Campaign: Internal</t>
         </is>
       </c>
-      <c r="E6" s="35" t="inlineStr">
+      <c r="E6" s="45" t="inlineStr">
         <is>
           <t>Global Page Load Rule</t>
         </is>
       </c>
-      <c r="F6" s="35" t="inlineStr">
+      <c r="F6" s="45" t="inlineStr">
         <is>
           <t>custom code</t>
         </is>
       </c>
-      <c r="G6" s="35" t="inlineStr">
+      <c r="G6" s="45" t="inlineStr">
         <is>
           <t>Element wired but returns no value — variable never populates.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="30" t="n">
+      <c r="A7" s="40" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="30" t="inlineStr">
+      <c r="B7" s="40" t="inlineStr">
         <is>
           <t>Internal Search Term</t>
         </is>
       </c>
-      <c r="C7" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D7" s="32" t="inlineStr">
+      <c r="C7" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D7" s="42" t="inlineStr">
         <is>
           <t>Search: Term</t>
         </is>
       </c>
-      <c r="E7" s="32" t="inlineStr">
+      <c r="E7" s="42" t="inlineStr">
         <is>
           <t>Internal Search Click; Internal Search ClickThrough; Null Search Tracking; Search Close Click</t>
         </is>
       </c>
-      <c r="F7" s="32" t="inlineStr">
+      <c r="F7" s="42" t="inlineStr">
         <is>
           <t>web.webInteractions.searchTerm</t>
         </is>
       </c>
-      <c r="G7" s="32" t="inlineStr"/>
+      <c r="G7" s="42" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="30" t="n">
+      <c r="A8" s="40" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="30" t="inlineStr">
+      <c r="B8" s="40" t="inlineStr">
         <is>
           <t># Search Results</t>
         </is>
       </c>
-      <c r="C8" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D8" s="32" t="inlineStr">
+      <c r="C8" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D8" s="42" t="inlineStr">
         <is>
           <t>Search: Results</t>
         </is>
       </c>
-      <c r="E8" s="32" t="inlineStr">
+      <c r="E8" s="42" t="inlineStr">
         <is>
           <t>Internal Search Click; Null Search Tracking; Search Close Click</t>
         </is>
       </c>
-      <c r="F8" s="32" t="inlineStr">
+      <c r="F8" s="42" t="inlineStr">
         <is>
           <t>web.webInteractions.searchResults</t>
         </is>
       </c>
-      <c r="G8" s="32" t="inlineStr"/>
+      <c r="G8" s="42" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="30" t="n">
+      <c r="A9" s="40" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="30" t="inlineStr">
+      <c r="B9" s="40" t="inlineStr">
         <is>
           <t>Search Results Page Type</t>
         </is>
       </c>
-      <c r="C9" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D9" s="32" t="inlineStr">
+      <c r="C9" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D9" s="42" t="inlineStr">
         <is>
           <t>Search: Result Page Type</t>
         </is>
       </c>
-      <c r="E9" s="32" t="inlineStr">
+      <c r="E9" s="42" t="inlineStr">
         <is>
           <t>Internal Search Click; Null Search Tracking; Search Close Click</t>
         </is>
       </c>
-      <c r="F9" s="32" t="inlineStr">
+      <c r="F9" s="42" t="inlineStr">
         <is>
           <t>internalSearchInfo.searchResultPageType</t>
         </is>
       </c>
-      <c r="G9" s="32" t="inlineStr"/>
+      <c r="G9" s="42" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="30" t="n">
+      <c r="A10" s="40" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="30" t="inlineStr">
+      <c r="B10" s="40" t="inlineStr">
         <is>
           <t>Content Type</t>
         </is>
       </c>
-      <c r="C10" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D10" s="32" t="inlineStr">
+      <c r="C10" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D10" s="42" t="inlineStr">
         <is>
           <t>Content: Type</t>
         </is>
       </c>
-      <c r="E10" s="32" t="inlineStr">
+      <c r="E10" s="42" t="inlineStr">
         <is>
           <t>Global Page Load Rule</t>
         </is>
       </c>
-      <c r="F10" s="32" t="inlineStr">
+      <c r="F10" s="42" t="inlineStr">
         <is>
           <t>web.webPageDetails.pageType</t>
         </is>
       </c>
-      <c r="G10" s="32" t="inlineStr"/>
+      <c r="G10" s="42" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="30" t="n">
+      <c r="A11" s="40" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="30" t="inlineStr">
+      <c r="B11" s="40" t="inlineStr">
         <is>
           <t>Form Name</t>
         </is>
       </c>
-      <c r="C11" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D11" s="32" t="inlineStr">
+      <c r="C11" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D11" s="42" t="inlineStr">
         <is>
           <t>Form: Name</t>
         </is>
       </c>
-      <c r="E11" s="32" t="inlineStr">
+      <c r="E11" s="42" t="inlineStr">
         <is>
           <t>Form Complete; Form Error Tracking; Form Start</t>
         </is>
       </c>
-      <c r="F11" s="32" t="inlineStr">
+      <c r="F11" s="42" t="inlineStr">
         <is>
           <t>web.webInteractions.formName</t>
         </is>
       </c>
-      <c r="G11" s="32" t="inlineStr"/>
+      <c r="G11" s="42" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="30" t="n">
+      <c r="A12" s="40" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="30" t="inlineStr">
+      <c r="B12" s="40" t="inlineStr">
         <is>
           <t>Video Title</t>
         </is>
       </c>
-      <c r="C12" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D12" s="32" t="inlineStr">
+      <c r="C12" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D12" s="42" t="inlineStr">
         <is>
           <t>Video: Name</t>
         </is>
       </c>
-      <c r="E12" s="32" t="inlineStr">
+      <c r="E12" s="42" t="inlineStr">
         <is>
           <t>Video 100 percentage complete; Video 25 percentage complete; Video 50 percentage complete; Video 75 percentage complete; Video Pause; Video Start</t>
         </is>
       </c>
-      <c r="F12" s="32" t="inlineStr">
+      <c r="F12" s="42" t="inlineStr">
         <is>
           <t>web.webInteractions.video.title</t>
         </is>
       </c>
-      <c r="G12" s="32" t="inlineStr"/>
+      <c r="G12" s="42" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="30" t="n">
+      <c r="A13" s="40" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="30" t="inlineStr">
+      <c r="B13" s="40" t="inlineStr">
         <is>
           <t>Page URL</t>
         </is>
       </c>
-      <c r="C13" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D13" s="32" t="inlineStr">
+      <c r="C13" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D13" s="42" t="inlineStr">
         <is>
           <t>Page: URL</t>
         </is>
       </c>
-      <c r="E13" s="32" t="inlineStr">
+      <c r="E13" s="42" t="inlineStr">
         <is>
           <t>Global Page Load Rule</t>
         </is>
       </c>
-      <c r="F13" s="32" t="inlineStr">
+      <c r="F13" s="42" t="inlineStr">
         <is>
           <t>web.webPageDetails.pageUrl</t>
         </is>
       </c>
-      <c r="G13" s="32" t="inlineStr"/>
+      <c r="G13" s="42" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="30" t="n">
+      <c r="A14" s="40" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="30" t="inlineStr">
+      <c r="B14" s="40" t="inlineStr">
         <is>
           <t>Page Query String</t>
         </is>
       </c>
-      <c r="C14" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D14" s="32" t="inlineStr">
+      <c r="C14" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D14" s="42" t="inlineStr">
         <is>
           <t>Core: Page Query String</t>
         </is>
       </c>
-      <c r="E14" s="32" t="inlineStr">
+      <c r="E14" s="42" t="inlineStr">
         <is>
           <t>Global Page Load Rule</t>
         </is>
       </c>
-      <c r="F14" s="32" t="inlineStr">
+      <c r="F14" s="42" t="inlineStr">
         <is>
           <t>custom code</t>
         </is>
       </c>
-      <c r="G14" s="32" t="inlineStr"/>
+      <c r="G14" s="42" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="36" t="n">
+      <c r="A15" s="46" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="36" t="inlineStr">
+      <c r="B15" s="46" t="inlineStr">
         <is>
           <t>ECID</t>
         </is>
       </c>
-      <c r="C15" s="37" t="inlineStr">
+      <c r="C15" s="47" t="inlineStr">
         <is>
           <t>Excluded by design</t>
         </is>
       </c>
-      <c r="D15" s="38" t="inlineStr">
+      <c r="D15" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E15" s="38" t="inlineStr">
+      <c r="E15" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F15" s="38" t="inlineStr">
+      <c r="F15" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G15" s="38" t="inlineStr">
+      <c r="G15" s="48" t="inlineStr">
         <is>
           <t>ECID intentionally not captured — Web SDK manages identity natively. Source element was a broken recursive stub.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="33" t="n">
+      <c r="A16" s="43" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="33" t="inlineStr">
+      <c r="B16" s="43" t="inlineStr">
         <is>
           <t>User Type</t>
         </is>
       </c>
-      <c r="C16" s="34" t="inlineStr">
+      <c r="C16" s="44" t="inlineStr">
         <is>
           <t>No data (element is a no-op)</t>
         </is>
       </c>
-      <c r="D16" s="35" t="inlineStr">
+      <c r="D16" s="45" t="inlineStr">
         <is>
           <t>User: Type</t>
         </is>
       </c>
-      <c r="E16" s="35" t="inlineStr">
+      <c r="E16" s="45" t="inlineStr">
         <is>
           <t>Global Page Load Rule</t>
         </is>
       </c>
-      <c r="F16" s="35" t="inlineStr">
+      <c r="F16" s="45" t="inlineStr">
         <is>
           <t>custom code</t>
         </is>
       </c>
-      <c r="G16" s="35" t="inlineStr">
+      <c r="G16" s="45" t="inlineStr">
         <is>
           <t>Element wired but returns no value — variable never populates.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="39" t="n">
+      <c r="A17" s="49" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="39" t="inlineStr">
+      <c r="B17" s="49" t="inlineStr">
         <is>
           <t>Internal Campaign Displayed</t>
         </is>
       </c>
-      <c r="C17" s="40" t="inlineStr">
+      <c r="C17" s="50" t="inlineStr">
         <is>
           <t>Defined, old property never sent</t>
         </is>
       </c>
-      <c r="D17" s="41" t="inlineStr">
+      <c r="D17" s="51" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E17" s="41" t="inlineStr">
+      <c r="E17" s="51" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F17" s="41" t="inlineStr">
+      <c r="F17" s="51" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G17" s="41" t="inlineStr">
+      <c r="G17" s="51" t="inlineStr">
         <is>
           <t>Old property never sent this.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="30" t="n">
+      <c r="A18" s="40" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="30" t="inlineStr">
+      <c r="B18" s="40" t="inlineStr">
         <is>
           <t>Social Link Name</t>
         </is>
       </c>
-      <c r="C18" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D18" s="32" t="inlineStr">
+      <c r="C18" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D18" s="42" t="inlineStr">
         <is>
           <t>Social: Interaction Info</t>
         </is>
       </c>
-      <c r="E18" s="32" t="inlineStr">
+      <c r="E18" s="42" t="inlineStr">
         <is>
           <t>Social Interaction Tracking</t>
         </is>
       </c>
-      <c r="F18" s="32" t="inlineStr">
+      <c r="F18" s="42" t="inlineStr">
         <is>
           <t>web.webInteractions.socialInteractionInfo</t>
         </is>
       </c>
-      <c r="G18" s="32" t="inlineStr"/>
+      <c r="G18" s="42" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="30" t="n">
+      <c r="A19" s="40" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="30" t="inlineStr">
+      <c r="B19" s="40" t="inlineStr">
         <is>
           <t>Language</t>
         </is>
       </c>
-      <c r="C19" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D19" s="32" t="inlineStr">
+      <c r="C19" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D19" s="42" t="inlineStr">
         <is>
           <t>Geo: Language</t>
         </is>
       </c>
-      <c r="E19" s="32" t="inlineStr">
+      <c r="E19" s="42" t="inlineStr">
         <is>
           <t>Global Page Load Rule</t>
         </is>
       </c>
-      <c r="F19" s="32" t="inlineStr">
+      <c r="F19" s="42" t="inlineStr">
         <is>
           <t>web.webPageDetails.language</t>
         </is>
       </c>
-      <c r="G19" s="32" t="inlineStr"/>
+      <c r="G19" s="42" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="30" t="n">
+      <c r="A20" s="40" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="30" t="inlineStr">
+      <c r="B20" s="40" t="inlineStr">
         <is>
           <t>Email Registration Location</t>
         </is>
       </c>
-      <c r="C20" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D20" s="32" t="inlineStr">
+      <c r="C20" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D20" s="42" t="inlineStr">
         <is>
           <t>Form: Location</t>
         </is>
       </c>
-      <c r="E20" s="32" t="inlineStr">
+      <c r="E20" s="42" t="inlineStr">
         <is>
           <t>Form Complete; Form Error Tracking; Form Start</t>
         </is>
       </c>
-      <c r="F20" s="32" t="inlineStr">
+      <c r="F20" s="42" t="inlineStr">
         <is>
           <t>web.webInteractions.formLocation</t>
         </is>
       </c>
-      <c r="G20" s="32" t="inlineStr"/>
+      <c r="G20" s="42" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="30" t="n">
+      <c r="A21" s="40" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="30" t="inlineStr">
+      <c r="B21" s="40" t="inlineStr">
         <is>
           <t>Scroll Depth</t>
         </is>
       </c>
-      <c r="C21" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D21" s="32" t="inlineStr">
+      <c r="C21" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D21" s="42" t="inlineStr">
         <is>
           <t>Scroll Depth</t>
         </is>
       </c>
-      <c r="E21" s="32" t="inlineStr">
+      <c r="E21" s="42" t="inlineStr">
         <is>
           <t>Scroll 100 percentage; Scroll 25 percentage; Scroll 50 percentage; Scroll 75 percentage</t>
         </is>
       </c>
-      <c r="F21" s="32" t="inlineStr">
+      <c r="F21" s="42" t="inlineStr">
         <is>
           <t>web.webInteractions.scrollInfo.depth</t>
         </is>
       </c>
-      <c r="G21" s="32" t="inlineStr"/>
+      <c r="G21" s="42" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="30" t="n">
+      <c r="A22" s="40" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="30" t="inlineStr">
+      <c r="B22" s="40" t="inlineStr">
         <is>
           <t>Redirect Link</t>
         </is>
       </c>
-      <c r="C22" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D22" s="32" t="inlineStr">
+      <c r="C22" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D22" s="42" t="inlineStr">
         <is>
           <t>Link: Redirect Text</t>
         </is>
       </c>
-      <c r="E22" s="32" t="inlineStr">
+      <c r="E22" s="42" t="inlineStr">
         <is>
           <t>Redirect Link Click Tracking</t>
         </is>
       </c>
-      <c r="F22" s="32" t="inlineStr">
+      <c r="F22" s="42" t="inlineStr">
         <is>
           <t>web.webInteractions.RedirectLinkText</t>
         </is>
       </c>
-      <c r="G22" s="32" t="inlineStr"/>
+      <c r="G22" s="42" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="30" t="n">
+      <c r="A23" s="40" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="30" t="inlineStr">
+      <c r="B23" s="40" t="inlineStr">
         <is>
           <t>CTA Button Text</t>
         </is>
       </c>
-      <c r="C23" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D23" s="32" t="inlineStr">
+      <c r="C23" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D23" s="42" t="inlineStr">
         <is>
           <t>Link: CTA Button Name</t>
         </is>
       </c>
-      <c r="E23" s="32" t="inlineStr">
+      <c r="E23" s="42" t="inlineStr">
         <is>
           <t>Global CTA Button Tracking</t>
         </is>
       </c>
-      <c r="F23" s="32" t="inlineStr">
+      <c r="F23" s="42" t="inlineStr">
         <is>
           <t>web.webInteractions.CTAButtonName</t>
         </is>
       </c>
-      <c r="G23" s="32" t="inlineStr"/>
+      <c r="G23" s="42" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="30" t="n">
+      <c r="A24" s="40" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="30" t="inlineStr">
+      <c r="B24" s="40" t="inlineStr">
         <is>
           <t>Destination Link</t>
         </is>
       </c>
-      <c r="C24" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D24" s="32" t="inlineStr">
+      <c r="C24" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D24" s="42" t="inlineStr">
         <is>
           <t>Link: Destination</t>
         </is>
       </c>
-      <c r="E24" s="32" t="inlineStr">
+      <c r="E24" s="42" t="inlineStr">
         <is>
           <t>Amazon Redirect Link Click; Global CTA Button Tracking; Redirect Link Click Tracking</t>
         </is>
       </c>
-      <c r="F24" s="32" t="inlineStr">
+      <c r="F24" s="42" t="inlineStr">
         <is>
           <t>web.webInteractions.DestinationLink</t>
         </is>
       </c>
-      <c r="G24" s="32" t="inlineStr"/>
+      <c r="G24" s="42" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="30" t="n">
+      <c r="A25" s="40" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="30" t="inlineStr">
+      <c r="B25" s="40" t="inlineStr">
         <is>
           <t>Menu Link</t>
         </is>
       </c>
-      <c r="C25" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D25" s="32" t="inlineStr">
+      <c r="C25" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D25" s="42" t="inlineStr">
         <is>
           <t>Link: Menu Name</t>
         </is>
       </c>
-      <c r="E25" s="32" t="inlineStr">
+      <c r="E25" s="42" t="inlineStr">
         <is>
           <t>Menu Link Click Tracking</t>
         </is>
       </c>
-      <c r="F25" s="32" t="inlineStr">
+      <c r="F25" s="42" t="inlineStr">
         <is>
           <t>web.webInteractions.MenuLinkName</t>
         </is>
       </c>
-      <c r="G25" s="32" t="inlineStr"/>
+      <c r="G25" s="42" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="30" t="n">
+      <c r="A26" s="40" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="30" t="inlineStr">
+      <c r="B26" s="40" t="inlineStr">
         <is>
           <t>Publish Date</t>
         </is>
       </c>
-      <c r="C26" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D26" s="32" t="inlineStr">
+      <c r="C26" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D26" s="42" t="inlineStr">
         <is>
           <t>Content: Publish Date</t>
         </is>
       </c>
-      <c r="E26" s="32" t="inlineStr">
+      <c r="E26" s="42" t="inlineStr">
         <is>
           <t>Global Page Load Rule</t>
         </is>
       </c>
-      <c r="F26" s="32" t="inlineStr">
+      <c r="F26" s="42" t="inlineStr">
         <is>
           <t>web.webPageDetails.publishDate</t>
         </is>
       </c>
-      <c r="G26" s="32" t="inlineStr"/>
+      <c r="G26" s="42" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="39" t="n">
+      <c r="A27" s="49" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="39" t="inlineStr">
+      <c r="B27" s="49" t="inlineStr">
         <is>
           <t>Content Type</t>
         </is>
       </c>
-      <c r="C27" s="40" t="inlineStr">
+      <c r="C27" s="50" t="inlineStr">
         <is>
           <t>Defined, old property never sent</t>
         </is>
       </c>
-      <c r="D27" s="41" t="inlineStr">
+      <c r="D27" s="51" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E27" s="41" t="inlineStr">
+      <c r="E27" s="51" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F27" s="41" t="inlineStr">
+      <c r="F27" s="51" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G27" s="41" t="inlineStr">
+      <c r="G27" s="51" t="inlineStr">
         <is>
           <t>Duplicate label of eVar9 (which is populated).</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="30" t="n">
+      <c r="A28" s="40" t="n">
         <v>27</v>
       </c>
-      <c r="B28" s="30" t="inlineStr">
+      <c r="B28" s="40" t="inlineStr">
         <is>
           <t>Filter</t>
         </is>
       </c>
-      <c r="C28" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D28" s="32" t="inlineStr">
+      <c r="C28" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D28" s="42" t="inlineStr">
         <is>
           <t>News: Filter</t>
         </is>
       </c>
-      <c r="E28" s="32" t="inlineStr">
+      <c r="E28" s="42" t="inlineStr">
         <is>
           <t>Filter Click Tracking</t>
         </is>
       </c>
-      <c r="F28" s="32" t="inlineStr">
+      <c r="F28" s="42" t="inlineStr">
         <is>
           <t>web.webInteractions.Filter</t>
         </is>
       </c>
-      <c r="G28" s="32" t="inlineStr"/>
+      <c r="G28" s="42" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="30" t="n">
+      <c r="A29" s="40" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="30" t="inlineStr">
+      <c r="B29" s="40" t="inlineStr">
         <is>
           <t>Amazon Redirect Link</t>
         </is>
       </c>
-      <c r="C29" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D29" s="32" t="inlineStr">
+      <c r="C29" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D29" s="42" t="inlineStr">
         <is>
           <t>Link: Redirect Text</t>
         </is>
       </c>
-      <c r="E29" s="32" t="inlineStr">
+      <c r="E29" s="42" t="inlineStr">
         <is>
           <t>Amazon Redirect Link Click</t>
         </is>
       </c>
-      <c r="F29" s="32" t="inlineStr">
+      <c r="F29" s="42" t="inlineStr">
         <is>
           <t>web.webInteractions.RedirectLinkText</t>
         </is>
       </c>
-      <c r="G29" s="32" t="inlineStr"/>
+      <c r="G29" s="42" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="30" t="n">
+      <c r="A30" s="40" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="30" t="inlineStr">
+      <c r="B30" s="40" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="C30" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D30" s="32" t="inlineStr">
+      <c r="C30" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D30" s="42" t="inlineStr">
         <is>
           <t>Content: Category</t>
         </is>
       </c>
-      <c r="E30" s="32" t="inlineStr">
+      <c r="E30" s="42" t="inlineStr">
         <is>
           <t>Global Page Load Rule</t>
         </is>
       </c>
-      <c r="F30" s="32" t="inlineStr">
+      <c r="F30" s="42" t="inlineStr">
         <is>
           <t>web.webPageDetails.category</t>
         </is>
       </c>
-      <c r="G30" s="32" t="inlineStr"/>
+      <c r="G30" s="42" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="30" t="n">
+      <c r="A31" s="40" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="30" t="inlineStr">
+      <c r="B31" s="40" t="inlineStr">
         <is>
           <t>Tag Text</t>
         </is>
       </c>
-      <c r="C31" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D31" s="32" t="inlineStr">
+      <c r="C31" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D31" s="42" t="inlineStr">
         <is>
           <t>Content: Tags</t>
         </is>
       </c>
-      <c r="E31" s="32" t="inlineStr">
+      <c r="E31" s="42" t="inlineStr">
         <is>
           <t>Global Page Load Rule</t>
         </is>
       </c>
-      <c r="F31" s="32" t="inlineStr">
+      <c r="F31" s="42" t="inlineStr">
         <is>
           <t>web.webPageDetails.tags</t>
         </is>
       </c>
-      <c r="G31" s="32" t="inlineStr"/>
+      <c r="G31" s="42" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="39" t="n">
+      <c r="A32" s="49" t="n">
         <v>31</v>
       </c>
-      <c r="B32" s="39" t="inlineStr">
+      <c r="B32" s="49" t="inlineStr">
         <is>
           <t>MetaTags</t>
         </is>
       </c>
-      <c r="C32" s="40" t="inlineStr">
+      <c r="C32" s="50" t="inlineStr">
         <is>
           <t>Defined, old property never sent</t>
         </is>
       </c>
-      <c r="D32" s="41" t="inlineStr">
+      <c r="D32" s="51" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E32" s="41" t="inlineStr">
+      <c r="E32" s="51" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F32" s="41" t="inlineStr">
+      <c r="F32" s="51" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G32" s="41" t="inlineStr">
+      <c r="G32" s="51" t="inlineStr">
         <is>
           <t>Old property never sent this.</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="30" t="n">
+      <c r="A33" s="40" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="30" t="inlineStr">
+      <c r="B33" s="40" t="inlineStr">
         <is>
           <t>Search Result Selection</t>
         </is>
       </c>
-      <c r="C33" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D33" s="32" t="inlineStr">
+      <c r="C33" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D33" s="42" t="inlineStr">
         <is>
           <t>Search: Result Click Name</t>
         </is>
       </c>
-      <c r="E33" s="32" t="inlineStr">
+      <c r="E33" s="42" t="inlineStr">
         <is>
           <t>Internal Search ClickThrough</t>
         </is>
       </c>
-      <c r="F33" s="32" t="inlineStr">
+      <c r="F33" s="42" t="inlineStr">
         <is>
           <t>web.webInteractions.searchResultClickName</t>
         </is>
       </c>
-      <c r="G33" s="32" t="inlineStr"/>
+      <c r="G33" s="42" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="30" t="n">
+      <c r="A34" s="40" t="n">
         <v>33</v>
       </c>
-      <c r="B34" s="30" t="inlineStr">
+      <c r="B34" s="40" t="inlineStr">
         <is>
           <t>File Name</t>
         </is>
       </c>
-      <c r="C34" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D34" s="32" t="inlineStr">
+      <c r="C34" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D34" s="42" t="inlineStr">
         <is>
           <t>File: Name</t>
         </is>
       </c>
-      <c r="E34" s="32" t="inlineStr">
+      <c r="E34" s="42" t="inlineStr">
         <is>
           <t>File Download Tracking</t>
         </is>
       </c>
-      <c r="F34" s="32" t="inlineStr">
+      <c r="F34" s="42" t="inlineStr">
         <is>
           <t>web.webInteractions.FileName</t>
         </is>
       </c>
-      <c r="G34" s="32" t="inlineStr"/>
+      <c r="G34" s="42" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="30" t="n">
+      <c r="A35" s="40" t="n">
         <v>34</v>
       </c>
-      <c r="B35" s="30" t="inlineStr">
+      <c r="B35" s="40" t="inlineStr">
         <is>
           <t>File Type</t>
         </is>
       </c>
-      <c r="C35" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D35" s="32" t="inlineStr">
+      <c r="C35" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D35" s="42" t="inlineStr">
         <is>
           <t>File: Type</t>
         </is>
       </c>
-      <c r="E35" s="32" t="inlineStr">
+      <c r="E35" s="42" t="inlineStr">
         <is>
           <t>File Download Tracking</t>
         </is>
       </c>
-      <c r="F35" s="32" t="inlineStr">
+      <c r="F35" s="42" t="inlineStr">
         <is>
           <t>web.webInteractions.FileType</t>
         </is>
       </c>
-      <c r="G35" s="32" t="inlineStr"/>
+      <c r="G35" s="42" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="30" t="n">
+      <c r="A36" s="40" t="n">
         <v>35</v>
       </c>
-      <c r="B36" s="30" t="inlineStr">
+      <c r="B36" s="40" t="inlineStr">
         <is>
           <t>Video Type</t>
         </is>
       </c>
-      <c r="C36" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D36" s="32" t="inlineStr">
+      <c r="C36" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D36" s="42" t="inlineStr">
         <is>
           <t>Video: Type</t>
         </is>
       </c>
-      <c r="E36" s="32" t="inlineStr">
+      <c r="E36" s="42" t="inlineStr">
         <is>
           <t>Video 100 percentage complete; Video 50 percentage complete; Video 75 percentage complete; Video Start</t>
         </is>
       </c>
-      <c r="F36" s="32" t="inlineStr">
+      <c r="F36" s="42" t="inlineStr">
         <is>
           <t>web.webInteractions.VideoType</t>
         </is>
       </c>
-      <c r="G36" s="32" t="inlineStr"/>
+      <c r="G36" s="42" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="30" t="n">
+      <c r="A37" s="40" t="n">
         <v>37</v>
       </c>
-      <c r="B37" s="30" t="inlineStr">
+      <c r="B37" s="40" t="inlineStr">
         <is>
           <t>Visit Duration</t>
         </is>
       </c>
-      <c r="C37" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D37" s="32" t="inlineStr">
+      <c r="C37" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D37" s="42" t="inlineStr">
         <is>
           <t>Plugin: Visit Duration</t>
         </is>
       </c>
-      <c r="E37" s="32" t="inlineStr">
+      <c r="E37" s="42" t="inlineStr">
         <is>
           <t>Global Page Load Rule</t>
         </is>
       </c>
-      <c r="F37" s="32" t="inlineStr">
+      <c r="F37" s="42" t="inlineStr">
         <is>
           <t>cwsdkp-getvisitduration</t>
         </is>
       </c>
-      <c r="G37" s="32" t="inlineStr"/>
+      <c r="G37" s="42" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="30" t="n">
+      <c r="A38" s="40" t="n">
         <v>38</v>
       </c>
-      <c r="B38" s="30" t="inlineStr">
+      <c r="B38" s="40" t="inlineStr">
         <is>
           <t>UTM Source</t>
         </is>
       </c>
-      <c r="C38" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D38" s="32" t="inlineStr">
+      <c r="C38" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D38" s="42" t="inlineStr">
         <is>
           <t>UTM: Source</t>
         </is>
       </c>
-      <c r="E38" s="32" t="inlineStr">
+      <c r="E38" s="42" t="inlineStr">
         <is>
           <t>Global Page Load Rule</t>
         </is>
       </c>
-      <c r="F38" s="32" t="inlineStr">
+      <c r="F38" s="42" t="inlineStr">
         <is>
           <t>UTM_Source</t>
         </is>
       </c>
-      <c r="G38" s="32" t="inlineStr"/>
+      <c r="G38" s="42" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="30" t="n">
+      <c r="A39" s="40" t="n">
         <v>39</v>
       </c>
-      <c r="B39" s="30" t="inlineStr">
+      <c r="B39" s="40" t="inlineStr">
         <is>
           <t>UTM Medium</t>
         </is>
       </c>
-      <c r="C39" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D39" s="32" t="inlineStr">
+      <c r="C39" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D39" s="42" t="inlineStr">
         <is>
           <t>UTM: Medium</t>
         </is>
       </c>
-      <c r="E39" s="32" t="inlineStr">
+      <c r="E39" s="42" t="inlineStr">
         <is>
           <t>Global Page Load Rule</t>
         </is>
       </c>
-      <c r="F39" s="32" t="inlineStr">
+      <c r="F39" s="42" t="inlineStr">
         <is>
           <t>UTM_Medium</t>
         </is>
       </c>
-      <c r="G39" s="32" t="inlineStr"/>
+      <c r="G39" s="42" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="30" t="n">
+      <c r="A40" s="40" t="n">
         <v>40</v>
       </c>
-      <c r="B40" s="30" t="inlineStr">
+      <c r="B40" s="40" t="inlineStr">
         <is>
           <t>UTM Content</t>
         </is>
       </c>
-      <c r="C40" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D40" s="32" t="inlineStr">
+      <c r="C40" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D40" s="42" t="inlineStr">
         <is>
           <t>UTM: Content</t>
         </is>
       </c>
-      <c r="E40" s="32" t="inlineStr">
+      <c r="E40" s="42" t="inlineStr">
         <is>
           <t>Global Page Load Rule</t>
         </is>
       </c>
-      <c r="F40" s="32" t="inlineStr">
+      <c r="F40" s="42" t="inlineStr">
         <is>
           <t>UTM_Content</t>
         </is>
       </c>
-      <c r="G40" s="32" t="inlineStr"/>
+      <c r="G40" s="42" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="30" t="n">
+      <c r="A41" s="40" t="n">
         <v>41</v>
       </c>
-      <c r="B41" s="30" t="inlineStr">
+      <c r="B41" s="40" t="inlineStr">
         <is>
           <t>UTM Campaign</t>
         </is>
       </c>
-      <c r="C41" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D41" s="32" t="inlineStr">
+      <c r="C41" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D41" s="42" t="inlineStr">
         <is>
           <t>UTM: Campaign</t>
         </is>
       </c>
-      <c r="E41" s="32" t="inlineStr">
+      <c r="E41" s="42" t="inlineStr">
         <is>
           <t>Global Page Load Rule</t>
         </is>
       </c>
-      <c r="F41" s="32" t="inlineStr">
+      <c r="F41" s="42" t="inlineStr">
         <is>
           <t>UTM_Campaign</t>
         </is>
       </c>
-      <c r="G41" s="32" t="inlineStr"/>
+      <c r="G41" s="42" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="30" t="n">
+      <c r="A42" s="40" t="n">
         <v>42</v>
       </c>
-      <c r="B42" s="30" t="inlineStr">
+      <c r="B42" s="40" t="inlineStr">
         <is>
           <t>UTM Term</t>
         </is>
       </c>
-      <c r="C42" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D42" s="32" t="inlineStr">
+      <c r="C42" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D42" s="42" t="inlineStr">
         <is>
           <t>UTM: Term</t>
         </is>
       </c>
-      <c r="E42" s="32" t="inlineStr">
+      <c r="E42" s="42" t="inlineStr">
         <is>
           <t>Global Page Load Rule</t>
         </is>
       </c>
-      <c r="F42" s="32" t="inlineStr">
+      <c r="F42" s="42" t="inlineStr">
         <is>
           <t>UTM_Term</t>
         </is>
       </c>
-      <c r="G42" s="32" t="inlineStr"/>
+      <c r="G42" s="42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="30" t="n">
+      <c r="A43" s="40" t="n">
         <v>43</v>
       </c>
-      <c r="B43" s="30" t="inlineStr">
+      <c r="B43" s="40" t="inlineStr">
         <is>
           <t>Related Tag Text</t>
         </is>
       </c>
-      <c r="C43" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D43" s="32" t="inlineStr">
+      <c r="C43" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D43" s="42" t="inlineStr">
         <is>
           <t>Link: Related Tag</t>
         </is>
       </c>
-      <c r="E43" s="32" t="inlineStr">
+      <c r="E43" s="42" t="inlineStr">
         <is>
           <t>Related Tag Click Tracking</t>
         </is>
       </c>
-      <c r="F43" s="32" t="inlineStr">
+      <c r="F43" s="42" t="inlineStr">
         <is>
           <t>web.webInteractions.TagLinkClick</t>
         </is>
       </c>
-      <c r="G43" s="32" t="inlineStr"/>
+      <c r="G43" s="42" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="30" t="n">
+      <c r="A44" s="40" t="n">
         <v>44</v>
       </c>
-      <c r="B44" s="30" t="inlineStr">
+      <c r="B44" s="40" t="inlineStr">
         <is>
           <t>More Amazon News Title</t>
         </is>
       </c>
-      <c r="C44" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D44" s="32" t="inlineStr">
+      <c r="C44" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D44" s="42" t="inlineStr">
         <is>
           <t>Link: More Amazon News</t>
         </is>
       </c>
-      <c r="E44" s="32" t="inlineStr">
+      <c r="E44" s="42" t="inlineStr">
         <is>
           <t>Amazon More News Tracking</t>
         </is>
       </c>
-      <c r="F44" s="32" t="inlineStr">
+      <c r="F44" s="42" t="inlineStr">
         <is>
           <t>web.webInteractions.moreAmazonNewsText</t>
         </is>
       </c>
-      <c r="G44" s="32" t="inlineStr"/>
+      <c r="G44" s="42" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="30" t="n">
+      <c r="A45" s="40" t="n">
         <v>45</v>
       </c>
-      <c r="B45" s="30" t="inlineStr">
+      <c r="B45" s="40" t="inlineStr">
         <is>
           <t>Stories Title</t>
         </is>
       </c>
-      <c r="C45" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D45" s="32" t="inlineStr">
+      <c r="C45" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D45" s="42" t="inlineStr">
         <is>
           <t>Link: Stories Text</t>
         </is>
       </c>
-      <c r="E45" s="32" t="inlineStr">
+      <c r="E45" s="42" t="inlineStr">
         <is>
           <t>Amazon Stories Link Click Tracking</t>
         </is>
       </c>
-      <c r="F45" s="32" t="inlineStr">
+      <c r="F45" s="42" t="inlineStr">
         <is>
           <t>web.webInteractions.storiesLinkText</t>
         </is>
       </c>
-      <c r="G45" s="32" t="inlineStr"/>
+      <c r="G45" s="42" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="30" t="n">
+      <c r="A46" s="40" t="n">
         <v>46</v>
       </c>
-      <c r="B46" s="30" t="inlineStr">
+      <c r="B46" s="40" t="inlineStr">
         <is>
           <t>Related Tags Link</t>
         </is>
       </c>
-      <c r="C46" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D46" s="32" t="inlineStr">
+      <c r="C46" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D46" s="42" t="inlineStr">
         <is>
           <t>Link: Related Tag URL</t>
         </is>
       </c>
-      <c r="E46" s="32" t="inlineStr">
+      <c r="E46" s="42" t="inlineStr">
         <is>
           <t>Related Tag Click Tracking</t>
         </is>
       </c>
-      <c r="F46" s="32" t="inlineStr">
+      <c r="F46" s="42" t="inlineStr">
         <is>
           <t>web.webInteractions.linkUrl</t>
         </is>
       </c>
-      <c r="G46" s="32" t="inlineStr"/>
+      <c r="G46" s="42" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="30" t="n">
+      <c r="A47" s="40" t="n">
         <v>47</v>
       </c>
-      <c r="B47" s="30" t="inlineStr">
+      <c r="B47" s="40" t="inlineStr">
         <is>
           <t>Country Code</t>
         </is>
       </c>
-      <c r="C47" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D47" s="32" t="inlineStr">
+      <c r="C47" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D47" s="42" t="inlineStr">
         <is>
           <t>Geo: Country</t>
         </is>
       </c>
-      <c r="E47" s="32" t="inlineStr">
+      <c r="E47" s="42" t="inlineStr">
         <is>
           <t>Global Page Load Rule</t>
         </is>
       </c>
-      <c r="F47" s="32" t="inlineStr">
+      <c r="F47" s="42" t="inlineStr">
         <is>
           <t>web.webPageDetails.country</t>
         </is>
       </c>
-      <c r="G47" s="32" t="inlineStr"/>
+      <c r="G47" s="42" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="30" t="n">
+      <c r="A48" s="40" t="n">
         <v>48</v>
       </c>
-      <c r="B48" s="30" t="inlineStr">
+      <c r="B48" s="40" t="inlineStr">
         <is>
           <t>Cookie Consent Selection</t>
         </is>
       </c>
-      <c r="C48" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D48" s="32" t="inlineStr">
+      <c r="C48" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D48" s="42" t="inlineStr">
         <is>
           <t>Consent: Selected</t>
         </is>
       </c>
-      <c r="E48" s="32" t="inlineStr">
+      <c r="E48" s="42" t="inlineStr">
         <is>
           <t>Consent Selection</t>
         </is>
       </c>
-      <c r="F48" s="32" t="inlineStr">
+      <c r="F48" s="42" t="inlineStr">
         <is>
           <t>web.webInteractions.cookieConsent.consentSelected</t>
         </is>
       </c>
-      <c r="G48" s="32" t="inlineStr"/>
+      <c r="G48" s="42" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="30" t="n">
+      <c r="A49" s="40" t="n">
         <v>49</v>
       </c>
-      <c r="B49" s="30" t="inlineStr">
+      <c r="B49" s="40" t="inlineStr">
         <is>
           <t>Map Name</t>
         </is>
       </c>
-      <c r="C49" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D49" s="32" t="inlineStr">
+      <c r="C49" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D49" s="42" t="inlineStr">
         <is>
           <t>Map: Name</t>
         </is>
       </c>
-      <c r="E49" s="32" t="inlineStr">
+      <c r="E49" s="42" t="inlineStr">
         <is>
           <t>Map Button Click; Map Button Close; Map Zoom In; Map Zoom Out</t>
         </is>
       </c>
-      <c r="F49" s="32" t="inlineStr">
+      <c r="F49" s="42" t="inlineStr">
         <is>
           <t>map.mapName</t>
         </is>
       </c>
-      <c r="G49" s="32" t="inlineStr"/>
+      <c r="G49" s="42" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="30" t="n">
+      <c r="A50" s="40" t="n">
         <v>50</v>
       </c>
-      <c r="B50" s="30" t="inlineStr">
+      <c r="B50" s="40" t="inlineStr">
         <is>
           <t>Map Button Name</t>
         </is>
       </c>
-      <c r="C50" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D50" s="32" t="inlineStr">
+      <c r="C50" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D50" s="42" t="inlineStr">
         <is>
           <t>Map: Button Name</t>
         </is>
       </c>
-      <c r="E50" s="32" t="inlineStr">
+      <c r="E50" s="42" t="inlineStr">
         <is>
           <t>Map Button Click; Map Button Close; Map Zoom In; Map Zoom Out</t>
         </is>
       </c>
-      <c r="F50" s="32" t="inlineStr">
+      <c r="F50" s="42" t="inlineStr">
         <is>
           <t>map.mapButtonName</t>
         </is>
       </c>
-      <c r="G50" s="32" t="inlineStr"/>
+      <c r="G50" s="42" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="42" t="n">
+      <c r="A51" s="52" t="n">
         <v>51</v>
       </c>
-      <c r="B51" s="42" t="inlineStr">
+      <c r="B51" s="52" t="inlineStr">
         <is>
           <t>Audio Title</t>
         </is>
       </c>
-      <c r="C51" s="43" t="inlineStr">
+      <c r="C51" s="53" t="inlineStr">
         <is>
           <t>Not implemented (never built)</t>
         </is>
       </c>
-      <c r="D51" s="44" t="inlineStr">
+      <c r="D51" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E51" s="44" t="inlineStr">
+      <c r="E51" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F51" s="44" t="inlineStr">
+      <c r="F51" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G51" s="44" t="inlineStr">
+      <c r="G51" s="54" t="inlineStr">
         <is>
           <t>AUDIO: defined in report suite but never implemented in the old Launch property. Net-new scope (Web SDK media collection).</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="42" t="n">
+      <c r="A52" s="52" t="n">
         <v>52</v>
       </c>
-      <c r="B52" s="42" t="inlineStr">
+      <c r="B52" s="52" t="inlineStr">
         <is>
           <t>Audio Action</t>
         </is>
       </c>
-      <c r="C52" s="43" t="inlineStr">
+      <c r="C52" s="53" t="inlineStr">
         <is>
           <t>Not implemented (never built)</t>
         </is>
       </c>
-      <c r="D52" s="44" t="inlineStr">
+      <c r="D52" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E52" s="44" t="inlineStr">
+      <c r="E52" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F52" s="44" t="inlineStr">
+      <c r="F52" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G52" s="44" t="inlineStr">
+      <c r="G52" s="54" t="inlineStr">
         <is>
           <t>AUDIO: defined in report suite but never implemented in the old Launch property. Net-new scope (Web SDK media collection).</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="42" t="n">
+      <c r="A53" s="52" t="n">
         <v>53</v>
       </c>
-      <c r="B53" s="42" t="inlineStr">
+      <c r="B53" s="52" t="inlineStr">
         <is>
           <t>Audio Duration</t>
         </is>
       </c>
-      <c r="C53" s="43" t="inlineStr">
+      <c r="C53" s="53" t="inlineStr">
         <is>
           <t>Not implemented (never built)</t>
         </is>
       </c>
-      <c r="D53" s="44" t="inlineStr">
+      <c r="D53" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E53" s="44" t="inlineStr">
+      <c r="E53" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F53" s="44" t="inlineStr">
+      <c r="F53" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G53" s="44" t="inlineStr">
+      <c r="G53" s="54" t="inlineStr">
         <is>
           <t>AUDIO: defined in report suite but never implemented in the old Launch property. Net-new scope (Web SDK media collection).</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="42" t="n">
+      <c r="A54" s="52" t="n">
         <v>54</v>
       </c>
-      <c r="B54" s="42" t="inlineStr">
+      <c r="B54" s="52" t="inlineStr">
         <is>
           <t>Audio Percent Played</t>
         </is>
       </c>
-      <c r="C54" s="43" t="inlineStr">
+      <c r="C54" s="53" t="inlineStr">
         <is>
           <t>Not implemented (never built)</t>
         </is>
       </c>
-      <c r="D54" s="44" t="inlineStr">
+      <c r="D54" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E54" s="44" t="inlineStr">
+      <c r="E54" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F54" s="44" t="inlineStr">
+      <c r="F54" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G54" s="44" t="inlineStr">
+      <c r="G54" s="54" t="inlineStr">
         <is>
           <t>AUDIO: defined in report suite but never implemented in the old Launch property. Net-new scope (Web SDK media collection).</t>
         </is>
@@ -2758,7 +3161,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2777,665 +3180,665 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="29" t="inlineStr">
+      <c r="A1" s="39" t="inlineStr">
         <is>
           <t>Prop #</t>
         </is>
       </c>
-      <c r="B1" s="29" t="inlineStr">
+      <c r="B1" s="39" t="inlineStr">
         <is>
           <t>Report Suite Name</t>
         </is>
       </c>
-      <c r="C1" s="29" t="inlineStr">
+      <c r="C1" s="39" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="D1" s="29" t="inlineStr">
+      <c r="D1" s="39" t="inlineStr">
         <is>
           <t>Data Element(s)</t>
         </is>
       </c>
-      <c r="E1" s="29" t="inlineStr">
+      <c r="E1" s="39" t="inlineStr">
         <is>
           <t>Sent By Rule(s)</t>
         </is>
       </c>
-      <c r="F1" s="29" t="inlineStr">
+      <c r="F1" s="39" t="inlineStr">
         <is>
           <t>Data Element Source</t>
         </is>
       </c>
-      <c r="G1" s="29" t="inlineStr">
+      <c r="G1" s="39" t="inlineStr">
         <is>
           <t>Notes / Issue</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="30" t="n">
+      <c r="A2" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="30" t="inlineStr">
+      <c r="B2" s="40" t="inlineStr">
         <is>
           <t>Page Name</t>
         </is>
       </c>
-      <c r="C2" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D2" s="32" t="inlineStr">
+      <c r="C2" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D2" s="42" t="inlineStr">
         <is>
           <t>Page: Name</t>
         </is>
       </c>
-      <c r="E2" s="32" t="inlineStr">
+      <c r="E2" s="42" t="inlineStr">
         <is>
           <t>Global Page Load Rule</t>
         </is>
       </c>
-      <c r="F2" s="32" t="inlineStr">
+      <c r="F2" s="42" t="inlineStr">
         <is>
           <t>web.webPageDetails.pageName</t>
         </is>
       </c>
-      <c r="G2" s="32" t="inlineStr"/>
+      <c r="G2" s="42" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="30" t="n">
+      <c r="A3" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="30" t="inlineStr">
+      <c r="B3" s="40" t="inlineStr">
         <is>
           <t>Referrer</t>
         </is>
       </c>
-      <c r="C3" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D3" s="32" t="inlineStr">
+      <c r="C3" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D3" s="42" t="inlineStr">
         <is>
           <t>Core: Referrer</t>
         </is>
       </c>
-      <c r="E3" s="32" t="inlineStr">
+      <c r="E3" s="42" t="inlineStr">
         <is>
           <t>Global Page Load Rule</t>
         </is>
       </c>
-      <c r="F3" s="32" t="inlineStr">
+      <c r="F3" s="42" t="inlineStr">
         <is>
           <t>core-page-info</t>
         </is>
       </c>
-      <c r="G3" s="32" t="inlineStr"/>
+      <c r="G3" s="42" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="30" t="n">
+      <c r="A4" s="40" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="30" t="inlineStr">
+      <c r="B4" s="40" t="inlineStr">
         <is>
           <t>Time Stamp</t>
         </is>
       </c>
-      <c r="C4" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D4" s="32" t="inlineStr">
+      <c r="C4" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D4" s="42" t="inlineStr">
         <is>
           <t>Core: Timestamp</t>
         </is>
       </c>
-      <c r="E4" s="32" t="inlineStr">
+      <c r="E4" s="42" t="inlineStr">
         <is>
           <t>Global Page Load Rule</t>
         </is>
       </c>
-      <c r="F4" s="32" t="inlineStr">
+      <c r="F4" s="42" t="inlineStr">
         <is>
           <t>custom code</t>
         </is>
       </c>
-      <c r="G4" s="32" t="inlineStr"/>
+      <c r="G4" s="42" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="30" t="n">
+      <c r="A5" s="40" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="30" t="inlineStr">
+      <c r="B5" s="40" t="inlineStr">
         <is>
           <t>Page Title</t>
         </is>
       </c>
-      <c r="C5" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D5" s="32" t="inlineStr">
+      <c r="C5" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D5" s="42" t="inlineStr">
         <is>
           <t>Page: Title</t>
         </is>
       </c>
-      <c r="E5" s="32" t="inlineStr">
+      <c r="E5" s="42" t="inlineStr">
         <is>
           <t>Global Page Load Rule</t>
         </is>
       </c>
-      <c r="F5" s="32" t="inlineStr">
+      <c r="F5" s="42" t="inlineStr">
         <is>
           <t>web.webPageDetails.pageTitle</t>
         </is>
       </c>
-      <c r="G5" s="32" t="inlineStr"/>
+      <c r="G5" s="42" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="30" t="n">
+      <c r="A6" s="40" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="30" t="inlineStr">
+      <c r="B6" s="40" t="inlineStr">
         <is>
           <t>Clean URL</t>
         </is>
       </c>
-      <c r="C6" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D6" s="32" t="inlineStr">
+      <c r="C6" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D6" s="42" t="inlineStr">
         <is>
           <t>Core: Clean URL</t>
         </is>
       </c>
-      <c r="E6" s="32" t="inlineStr">
+      <c r="E6" s="42" t="inlineStr">
         <is>
           <t>Global Page Load Rule</t>
         </is>
       </c>
-      <c r="F6" s="32" t="inlineStr">
+      <c r="F6" s="42" t="inlineStr">
         <is>
           <t>custom code</t>
         </is>
       </c>
-      <c r="G6" s="32" t="inlineStr"/>
+      <c r="G6" s="42" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="30" t="n">
+      <c r="A7" s="40" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="30" t="inlineStr">
+      <c r="B7" s="40" t="inlineStr">
         <is>
           <t>Site Section</t>
         </is>
       </c>
-      <c r="C7" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D7" s="32" t="inlineStr">
+      <c r="C7" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D7" s="42" t="inlineStr">
         <is>
           <t>Site: Section</t>
         </is>
       </c>
-      <c r="E7" s="32" t="inlineStr">
+      <c r="E7" s="42" t="inlineStr">
         <is>
           <t>Global Page Load Rule</t>
         </is>
       </c>
-      <c r="F7" s="32" t="inlineStr">
+      <c r="F7" s="42" t="inlineStr">
         <is>
           <t>web.webPageDetails.siteSection</t>
         </is>
       </c>
-      <c r="G7" s="32" t="inlineStr"/>
+      <c r="G7" s="42" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="30" t="n">
+      <c r="A8" s="40" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="30" t="inlineStr">
+      <c r="B8" s="40" t="inlineStr">
         <is>
           <t>Site Section2</t>
         </is>
       </c>
-      <c r="C8" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D8" s="32" t="inlineStr">
+      <c r="C8" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D8" s="42" t="inlineStr">
         <is>
           <t>Site: Section 2</t>
         </is>
       </c>
-      <c r="E8" s="32" t="inlineStr">
+      <c r="E8" s="42" t="inlineStr">
         <is>
           <t>Global Page Load Rule</t>
         </is>
       </c>
-      <c r="F8" s="32" t="inlineStr">
+      <c r="F8" s="42" t="inlineStr">
         <is>
           <t>web.webPageDetails.siteSectionTwo</t>
         </is>
       </c>
-      <c r="G8" s="32" t="inlineStr"/>
+      <c r="G8" s="42" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="30" t="n">
+      <c r="A9" s="40" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="30" t="inlineStr">
+      <c r="B9" s="40" t="inlineStr">
         <is>
           <t>Site Section3</t>
         </is>
       </c>
-      <c r="C9" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D9" s="32" t="inlineStr">
+      <c r="C9" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D9" s="42" t="inlineStr">
         <is>
           <t>Site: Section 3</t>
         </is>
       </c>
-      <c r="E9" s="32" t="inlineStr">
+      <c r="E9" s="42" t="inlineStr">
         <is>
           <t>Global Page Load Rule</t>
         </is>
       </c>
-      <c r="F9" s="32" t="inlineStr">
+      <c r="F9" s="42" t="inlineStr">
         <is>
           <t>web.webPageDetails.siteSectionThree</t>
         </is>
       </c>
-      <c r="G9" s="32" t="inlineStr"/>
+      <c r="G9" s="42" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="30" t="n">
+      <c r="A10" s="40" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="30" t="inlineStr">
+      <c r="B10" s="40" t="inlineStr">
         <is>
           <t>Site Section4</t>
         </is>
       </c>
-      <c r="C10" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D10" s="32" t="inlineStr">
+      <c r="C10" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D10" s="42" t="inlineStr">
         <is>
           <t>Site: Section 4</t>
         </is>
       </c>
-      <c r="E10" s="32" t="inlineStr">
+      <c r="E10" s="42" t="inlineStr">
         <is>
           <t>Global Page Load Rule</t>
         </is>
       </c>
-      <c r="F10" s="32" t="inlineStr">
+      <c r="F10" s="42" t="inlineStr">
         <is>
           <t>siteSection4</t>
         </is>
       </c>
-      <c r="G10" s="32" t="inlineStr"/>
+      <c r="G10" s="42" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="30" t="n">
+      <c r="A11" s="40" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="30" t="inlineStr">
+      <c r="B11" s="40" t="inlineStr">
         <is>
           <t>Site Section5</t>
         </is>
       </c>
-      <c r="C11" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D11" s="32" t="inlineStr">
+      <c r="C11" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D11" s="42" t="inlineStr">
         <is>
           <t>Site: Section 5</t>
         </is>
       </c>
-      <c r="E11" s="32" t="inlineStr">
+      <c r="E11" s="42" t="inlineStr">
         <is>
           <t>Global Page Load Rule</t>
         </is>
       </c>
-      <c r="F11" s="32" t="inlineStr">
+      <c r="F11" s="42" t="inlineStr">
         <is>
           <t>siteSection5</t>
         </is>
       </c>
-      <c r="G11" s="32" t="inlineStr"/>
+      <c r="G11" s="42" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="30" t="n">
+      <c r="A12" s="40" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="30" t="inlineStr">
+      <c r="B12" s="40" t="inlineStr">
         <is>
           <t>Previous Page Name</t>
         </is>
       </c>
-      <c r="C12" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D12" s="32" t="inlineStr">
+      <c r="C12" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D12" s="42" t="inlineStr">
         <is>
           <t>Plugin: Previous Page Name</t>
         </is>
       </c>
-      <c r="E12" s="32" t="inlineStr">
+      <c r="E12" s="42" t="inlineStr">
         <is>
           <t>Global Page Load Rule</t>
         </is>
       </c>
-      <c r="F12" s="32" t="inlineStr">
+      <c r="F12" s="42" t="inlineStr">
         <is>
           <t>cwsdkp-getpreviousvalue</t>
         </is>
       </c>
-      <c r="G12" s="32" t="inlineStr"/>
+      <c r="G12" s="42" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="30" t="n">
+      <c r="A13" s="40" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="30" t="inlineStr">
+      <c r="B13" s="40" t="inlineStr">
         <is>
           <t>Page URL</t>
         </is>
       </c>
-      <c r="C13" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D13" s="32" t="inlineStr">
+      <c r="C13" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D13" s="42" t="inlineStr">
         <is>
           <t>Page: URL</t>
         </is>
       </c>
-      <c r="E13" s="32" t="inlineStr">
+      <c r="E13" s="42" t="inlineStr">
         <is>
           <t>Global Page Load Rule</t>
         </is>
       </c>
-      <c r="F13" s="32" t="inlineStr">
+      <c r="F13" s="42" t="inlineStr">
         <is>
           <t>web.webPageDetails.pageUrl</t>
         </is>
       </c>
-      <c r="G13" s="32" t="inlineStr"/>
+      <c r="G13" s="42" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="36" t="n">
+      <c r="A14" s="46" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="36" t="inlineStr">
+      <c r="B14" s="46" t="inlineStr">
         <is>
           <t>ECID</t>
         </is>
       </c>
-      <c r="C14" s="37" t="inlineStr">
+      <c r="C14" s="47" t="inlineStr">
         <is>
           <t>Excluded by design</t>
         </is>
       </c>
-      <c r="D14" s="38" t="inlineStr">
+      <c r="D14" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E14" s="38" t="inlineStr">
+      <c r="E14" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F14" s="38" t="inlineStr">
+      <c r="F14" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G14" s="38" t="inlineStr">
+      <c r="G14" s="48" t="inlineStr">
         <is>
           <t>ECID intentionally not captured — Web SDK manages identity natively. Source element was a broken recursive stub.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="30" t="n">
+      <c r="A15" s="40" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="30" t="inlineStr">
+      <c r="B15" s="40" t="inlineStr">
         <is>
           <t>Visit Number</t>
         </is>
       </c>
-      <c r="C15" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D15" s="32" t="inlineStr">
+      <c r="C15" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D15" s="42" t="inlineStr">
         <is>
           <t>Plugin: Visit Number</t>
         </is>
       </c>
-      <c r="E15" s="32" t="inlineStr">
+      <c r="E15" s="42" t="inlineStr">
         <is>
           <t>Global Page Load Rule</t>
         </is>
       </c>
-      <c r="F15" s="32" t="inlineStr">
+      <c r="F15" s="42" t="inlineStr">
         <is>
           <t>cwsdkp-getvisitnum</t>
         </is>
       </c>
-      <c r="G15" s="32" t="inlineStr"/>
+      <c r="G15" s="42" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="30" t="n">
+      <c r="A16" s="40" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="30" t="inlineStr">
+      <c r="B16" s="40" t="inlineStr">
         <is>
           <t>Time Since Last Visit</t>
         </is>
       </c>
-      <c r="C16" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D16" s="32" t="inlineStr">
+      <c r="C16" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D16" s="42" t="inlineStr">
         <is>
           <t>Plugin: Time Since Last Visit</t>
         </is>
       </c>
-      <c r="E16" s="32" t="inlineStr">
+      <c r="E16" s="42" t="inlineStr">
         <is>
           <t>Global Page Load Rule</t>
         </is>
       </c>
-      <c r="F16" s="32" t="inlineStr">
+      <c r="F16" s="42" t="inlineStr">
         <is>
           <t>cwsdkp-gettimesincelastvisit</t>
         </is>
       </c>
-      <c r="G16" s="32" t="inlineStr"/>
+      <c r="G16" s="42" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="30" t="n">
+      <c r="A17" s="40" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="30" t="inlineStr">
+      <c r="B17" s="40" t="inlineStr">
         <is>
           <t>Repeat Vs New</t>
         </is>
       </c>
-      <c r="C17" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D17" s="32" t="inlineStr">
+      <c r="C17" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D17" s="42" t="inlineStr">
         <is>
           <t>Plugin: Repeat Vs New</t>
         </is>
       </c>
-      <c r="E17" s="32" t="inlineStr">
+      <c r="E17" s="42" t="inlineStr">
         <is>
           <t>Global Page Load Rule</t>
         </is>
       </c>
-      <c r="F17" s="32" t="inlineStr">
+      <c r="F17" s="42" t="inlineStr">
         <is>
           <t>cwsdkp-getnewrepeat</t>
         </is>
       </c>
-      <c r="G17" s="32" t="inlineStr"/>
+      <c r="G17" s="42" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="30" t="n">
+      <c r="A18" s="40" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="30" t="inlineStr">
+      <c r="B18" s="40" t="inlineStr">
         <is>
           <t>Visit Duration</t>
         </is>
       </c>
-      <c r="C18" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D18" s="32" t="inlineStr">
+      <c r="C18" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D18" s="42" t="inlineStr">
         <is>
           <t>Plugin: Visit Duration</t>
         </is>
       </c>
-      <c r="E18" s="32" t="inlineStr">
+      <c r="E18" s="42" t="inlineStr">
         <is>
           <t>Global Page Load Rule</t>
         </is>
       </c>
-      <c r="F18" s="32" t="inlineStr">
+      <c r="F18" s="42" t="inlineStr">
         <is>
           <t>cwsdkp-getvisitduration</t>
         </is>
       </c>
-      <c r="G18" s="32" t="inlineStr"/>
+      <c r="G18" s="42" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="30" t="n">
+      <c r="A19" s="40" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="30" t="inlineStr">
+      <c r="B19" s="40" t="inlineStr">
         <is>
           <t>Page Title</t>
         </is>
       </c>
-      <c r="C19" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D19" s="32" t="inlineStr">
+      <c r="C19" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D19" s="42" t="inlineStr">
         <is>
           <t>Page: Title</t>
         </is>
       </c>
-      <c r="E19" s="32" t="inlineStr">
+      <c r="E19" s="42" t="inlineStr">
         <is>
           <t>Global Page Load Rule</t>
         </is>
       </c>
-      <c r="F19" s="32" t="inlineStr">
+      <c r="F19" s="42" t="inlineStr">
         <is>
           <t>web.webPageDetails.pageTitle</t>
         </is>
       </c>
-      <c r="G19" s="32" t="inlineStr"/>
+      <c r="G19" s="42" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="30" t="n">
+      <c r="A20" s="40" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="30" t="inlineStr">
+      <c r="B20" s="40" t="inlineStr">
         <is>
           <t>Site Error</t>
         </is>
       </c>
-      <c r="C20" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D20" s="32" t="inlineStr">
+      <c r="C20" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D20" s="42" t="inlineStr">
         <is>
           <t>Page: Error</t>
         </is>
       </c>
-      <c r="E20" s="32" t="inlineStr">
+      <c r="E20" s="42" t="inlineStr">
         <is>
           <t>Global Page Load Rule; Site Error</t>
         </is>
       </c>
-      <c r="F20" s="32" t="inlineStr">
+      <c r="F20" s="42" t="inlineStr">
         <is>
           <t>web.webPageDetails.siteError</t>
         </is>
       </c>
-      <c r="G20" s="32" t="inlineStr"/>
+      <c r="G20" s="42" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="30" t="n">
+      <c r="A21" s="40" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="30" t="inlineStr">
+      <c r="B21" s="40" t="inlineStr">
         <is>
           <t>Locale</t>
         </is>
       </c>
-      <c r="C21" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D21" s="32" t="inlineStr">
+      <c r="C21" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D21" s="42" t="inlineStr">
         <is>
           <t>Geo: Locale</t>
         </is>
       </c>
-      <c r="E21" s="32" t="inlineStr">
+      <c r="E21" s="42" t="inlineStr">
         <is>
           <t>Global Page Load Rule</t>
         </is>
       </c>
-      <c r="F21" s="32" t="inlineStr">
+      <c r="F21" s="42" t="inlineStr">
         <is>
           <t>web.webPageDetails.locale</t>
         </is>
       </c>
-      <c r="G21" s="32" t="inlineStr"/>
+      <c r="G21" s="42" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:G21"/>
@@ -3443,7 +3846,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3460,861 +3863,861 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="29" t="inlineStr">
+      <c r="A1" s="39" t="inlineStr">
         <is>
           <t>Event #</t>
         </is>
       </c>
-      <c r="B1" s="29" t="inlineStr">
+      <c r="B1" s="39" t="inlineStr">
         <is>
           <t>Report Suite Name</t>
         </is>
       </c>
-      <c r="C1" s="29" t="inlineStr">
+      <c r="C1" s="39" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="D1" s="29" t="inlineStr">
+      <c r="D1" s="39" t="inlineStr">
         <is>
           <t>Sent By Rule(s)</t>
         </is>
       </c>
-      <c r="E1" s="29" t="inlineStr">
+      <c r="E1" s="39" t="inlineStr">
         <is>
           <t>Notes / Issue</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="30" t="n">
+      <c r="A2" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="30" t="inlineStr">
+      <c r="B2" s="40" t="inlineStr">
         <is>
           <t>Social Interactions</t>
         </is>
       </c>
-      <c r="C2" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D2" s="32" t="inlineStr">
+      <c r="C2" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D2" s="42" t="inlineStr">
         <is>
           <t>Social Interaction Tracking</t>
         </is>
       </c>
-      <c r="E2" s="32" t="inlineStr"/>
+      <c r="E2" s="42" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="30" t="n">
+      <c r="A3" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="30" t="inlineStr">
+      <c r="B3" s="40" t="inlineStr">
         <is>
           <t>Page Load</t>
         </is>
       </c>
-      <c r="C3" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D3" s="32" t="inlineStr">
+      <c r="C3" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D3" s="42" t="inlineStr">
         <is>
           <t>Global Page Load Rule</t>
         </is>
       </c>
-      <c r="E3" s="32" t="inlineStr"/>
+      <c r="E3" s="42" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="39" t="n">
+      <c r="A4" s="49" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="39" t="inlineStr">
+      <c r="B4" s="49" t="inlineStr">
         <is>
           <t>Internal Campaign Click</t>
         </is>
       </c>
-      <c r="C4" s="40" t="inlineStr">
+      <c r="C4" s="50" t="inlineStr">
         <is>
           <t>Defined, old property never sent</t>
         </is>
       </c>
-      <c r="D4" s="41" t="inlineStr">
+      <c r="D4" s="51" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E4" s="41" t="inlineStr">
+      <c r="E4" s="51" t="inlineStr">
         <is>
           <t>Old property never sent it (deferred internal-campaign feature).</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="33" t="n">
+      <c r="A5" s="43" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="33" t="inlineStr">
+      <c r="B5" s="43" t="inlineStr">
         <is>
           <t>Internal Campaign Impressions</t>
         </is>
       </c>
-      <c r="C5" s="34" t="inlineStr">
+      <c r="C5" s="44" t="inlineStr">
         <is>
           <t>No data (element is a no-op)</t>
         </is>
       </c>
-      <c r="D5" s="35" t="inlineStr">
+      <c r="D5" s="45" t="inlineStr">
         <is>
           <t>Global Page Load Rule</t>
         </is>
       </c>
-      <c r="E5" s="35" t="inlineStr">
+      <c r="E5" s="45" t="inlineStr">
         <is>
           <t>Filtered out of the page view (valued event fed by a no-op counter) — deferred with Internal Campaign.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="39" t="n">
+      <c r="A6" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="39" t="inlineStr">
+      <c r="B6" s="49" t="inlineStr">
         <is>
           <t>Internal Search</t>
         </is>
       </c>
-      <c r="C6" s="40" t="inlineStr">
+      <c r="C6" s="50" t="inlineStr">
         <is>
           <t>Defined, old property never sent</t>
         </is>
       </c>
-      <c r="D6" s="41" t="inlineStr">
+      <c r="D6" s="51" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E6" s="41" t="inlineStr">
+      <c r="E6" s="51" t="inlineStr">
         <is>
           <t>Old property used event26 (Internal Search Click) instead.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="30" t="n">
+      <c r="A7" s="40" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="30" t="inlineStr">
+      <c r="B7" s="40" t="inlineStr">
         <is>
           <t>Null Search Results</t>
         </is>
       </c>
-      <c r="C7" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D7" s="32" t="inlineStr">
+      <c r="C7" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D7" s="42" t="inlineStr">
         <is>
           <t>Null Search Tracking</t>
         </is>
       </c>
-      <c r="E7" s="32" t="inlineStr"/>
+      <c r="E7" s="42" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="30" t="n">
+      <c r="A8" s="40" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="30" t="inlineStr">
+      <c r="B8" s="40" t="inlineStr">
         <is>
           <t>Internal Search Click-through</t>
         </is>
       </c>
-      <c r="C8" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D8" s="32" t="inlineStr">
+      <c r="C8" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D8" s="42" t="inlineStr">
         <is>
           <t>Internal Search ClickThrough</t>
         </is>
       </c>
-      <c r="E8" s="32" t="inlineStr"/>
+      <c r="E8" s="42" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="30" t="n">
+      <c r="A9" s="40" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="30" t="inlineStr">
+      <c r="B9" s="40" t="inlineStr">
         <is>
           <t>Form Error</t>
         </is>
       </c>
-      <c r="C9" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D9" s="32" t="inlineStr">
+      <c r="C9" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D9" s="42" t="inlineStr">
         <is>
           <t>Form Error Tracking</t>
         </is>
       </c>
-      <c r="E9" s="32" t="inlineStr"/>
+      <c r="E9" s="42" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="30" t="n">
+      <c r="A10" s="40" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="30" t="inlineStr">
+      <c r="B10" s="40" t="inlineStr">
         <is>
           <t>Form Starts</t>
         </is>
       </c>
-      <c r="C10" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D10" s="32" t="inlineStr">
+      <c r="C10" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D10" s="42" t="inlineStr">
         <is>
           <t>Form Start</t>
         </is>
       </c>
-      <c r="E10" s="32" t="inlineStr"/>
+      <c r="E10" s="42" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="30" t="n">
+      <c r="A11" s="40" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="30" t="inlineStr">
+      <c r="B11" s="40" t="inlineStr">
         <is>
           <t>Form Completes</t>
         </is>
       </c>
-      <c r="C11" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D11" s="32" t="inlineStr">
+      <c r="C11" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D11" s="42" t="inlineStr">
         <is>
           <t>Form Complete</t>
         </is>
       </c>
-      <c r="E11" s="32" t="inlineStr"/>
+      <c r="E11" s="42" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="30" t="n">
+      <c r="A12" s="40" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="30" t="inlineStr">
+      <c r="B12" s="40" t="inlineStr">
         <is>
           <t>Video Start</t>
         </is>
       </c>
-      <c r="C12" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D12" s="32" t="inlineStr">
+      <c r="C12" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D12" s="42" t="inlineStr">
         <is>
           <t>Video Start</t>
         </is>
       </c>
-      <c r="E12" s="32" t="inlineStr"/>
+      <c r="E12" s="42" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="30" t="n">
+      <c r="A13" s="40" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="30" t="inlineStr">
+      <c r="B13" s="40" t="inlineStr">
         <is>
           <t>Video Complete</t>
         </is>
       </c>
-      <c r="C13" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D13" s="32" t="inlineStr">
+      <c r="C13" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D13" s="42" t="inlineStr">
         <is>
           <t>Video 100 percentage complete</t>
         </is>
       </c>
-      <c r="E13" s="32" t="inlineStr"/>
+      <c r="E13" s="42" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="30" t="n">
+      <c r="A14" s="40" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="30" t="inlineStr">
+      <c r="B14" s="40" t="inlineStr">
         <is>
           <t>Video 25% Milestone</t>
         </is>
       </c>
-      <c r="C14" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D14" s="32" t="inlineStr">
+      <c r="C14" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D14" s="42" t="inlineStr">
         <is>
           <t>Video 25 percentage complete</t>
         </is>
       </c>
-      <c r="E14" s="32" t="inlineStr"/>
+      <c r="E14" s="42" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="30" t="n">
+      <c r="A15" s="40" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="30" t="inlineStr">
+      <c r="B15" s="40" t="inlineStr">
         <is>
           <t>Video 50% Milestone</t>
         </is>
       </c>
-      <c r="C15" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D15" s="32" t="inlineStr">
+      <c r="C15" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D15" s="42" t="inlineStr">
         <is>
           <t>Video 50 percentage complete</t>
         </is>
       </c>
-      <c r="E15" s="32" t="inlineStr"/>
+      <c r="E15" s="42" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="30" t="n">
+      <c r="A16" s="40" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="30" t="inlineStr">
+      <c r="B16" s="40" t="inlineStr">
         <is>
           <t>Video 75% Milestone</t>
         </is>
       </c>
-      <c r="C16" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D16" s="32" t="inlineStr">
+      <c r="C16" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D16" s="42" t="inlineStr">
         <is>
           <t>Video 75 percentage complete</t>
         </is>
       </c>
-      <c r="E16" s="32" t="inlineStr"/>
+      <c r="E16" s="42" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="30" t="n">
+      <c r="A17" s="40" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="30" t="inlineStr">
+      <c r="B17" s="40" t="inlineStr">
         <is>
           <t>File Downloads</t>
         </is>
       </c>
-      <c r="C17" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D17" s="32" t="inlineStr">
+      <c r="C17" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D17" s="42" t="inlineStr">
         <is>
           <t>File Download Tracking</t>
         </is>
       </c>
-      <c r="E17" s="32" t="inlineStr"/>
+      <c r="E17" s="42" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="30" t="n">
+      <c r="A18" s="40" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="30" t="inlineStr">
+      <c r="B18" s="40" t="inlineStr">
         <is>
           <t>Scroll Reach 25%</t>
         </is>
       </c>
-      <c r="C18" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D18" s="32" t="inlineStr">
+      <c r="C18" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D18" s="42" t="inlineStr">
         <is>
           <t>Scroll 25 percentage</t>
         </is>
       </c>
-      <c r="E18" s="32" t="inlineStr"/>
+      <c r="E18" s="42" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="30" t="n">
+      <c r="A19" s="40" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="30" t="inlineStr">
+      <c r="B19" s="40" t="inlineStr">
         <is>
           <t>Scroll Reach 50%</t>
         </is>
       </c>
-      <c r="C19" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D19" s="32" t="inlineStr">
+      <c r="C19" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D19" s="42" t="inlineStr">
         <is>
           <t>Scroll 50 percentage</t>
         </is>
       </c>
-      <c r="E19" s="32" t="inlineStr"/>
+      <c r="E19" s="42" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="30" t="n">
+      <c r="A20" s="40" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="30" t="inlineStr">
+      <c r="B20" s="40" t="inlineStr">
         <is>
           <t>Scroll Reach 75%</t>
         </is>
       </c>
-      <c r="C20" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D20" s="32" t="inlineStr">
+      <c r="C20" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D20" s="42" t="inlineStr">
         <is>
           <t>Scroll 75 percentage</t>
         </is>
       </c>
-      <c r="E20" s="32" t="inlineStr"/>
+      <c r="E20" s="42" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="30" t="n">
+      <c r="A21" s="40" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="30" t="inlineStr">
+      <c r="B21" s="40" t="inlineStr">
         <is>
           <t>Scroll Reach 100%</t>
         </is>
       </c>
-      <c r="C21" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D21" s="32" t="inlineStr">
+      <c r="C21" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D21" s="42" t="inlineStr">
         <is>
           <t>Scroll 100 percentage</t>
         </is>
       </c>
-      <c r="E21" s="32" t="inlineStr"/>
+      <c r="E21" s="42" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="30" t="n">
+      <c r="A22" s="40" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="30" t="inlineStr">
+      <c r="B22" s="40" t="inlineStr">
         <is>
           <t>Link Click</t>
         </is>
       </c>
-      <c r="C22" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D22" s="32" t="inlineStr">
+      <c r="C22" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D22" s="42" t="inlineStr">
         <is>
           <t>Amazon Redirect Link Click; Redirect Link Click Tracking</t>
         </is>
       </c>
-      <c r="E22" s="32" t="inlineStr"/>
+      <c r="E22" s="42" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="30" t="n">
+      <c r="A23" s="40" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="30" t="inlineStr">
+      <c r="B23" s="40" t="inlineStr">
         <is>
           <t>CTA Click</t>
         </is>
       </c>
-      <c r="C23" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D23" s="32" t="inlineStr">
+      <c r="C23" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D23" s="42" t="inlineStr">
         <is>
           <t>Amazon More News Tracking; Amazon Redirect Link Click; Amazon Stories Link Click Tracking; Global CTA Button Tracking; Redirect Link Click Tracking</t>
         </is>
       </c>
-      <c r="E23" s="32" t="inlineStr"/>
+      <c r="E23" s="42" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="30" t="n">
+      <c r="A24" s="40" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="30" t="inlineStr">
+      <c r="B24" s="40" t="inlineStr">
         <is>
           <t>Menu Click</t>
         </is>
       </c>
-      <c r="C24" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D24" s="32" t="inlineStr">
+      <c r="C24" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D24" s="42" t="inlineStr">
         <is>
           <t>Menu Link Click Tracking</t>
         </is>
       </c>
-      <c r="E24" s="32" t="inlineStr"/>
+      <c r="E24" s="42" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="30" t="n">
+      <c r="A25" s="40" t="n">
         <v>25</v>
       </c>
-      <c r="B25" s="30" t="inlineStr">
+      <c r="B25" s="40" t="inlineStr">
         <is>
           <t>Filter Applied</t>
         </is>
       </c>
-      <c r="C25" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D25" s="32" t="inlineStr">
+      <c r="C25" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D25" s="42" t="inlineStr">
         <is>
           <t>Filter Click Tracking</t>
         </is>
       </c>
-      <c r="E25" s="32" t="inlineStr"/>
+      <c r="E25" s="42" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="30" t="n">
+      <c r="A26" s="40" t="n">
         <v>26</v>
       </c>
-      <c r="B26" s="30" t="inlineStr">
+      <c r="B26" s="40" t="inlineStr">
         <is>
           <t>Internal Search Click</t>
         </is>
       </c>
-      <c r="C26" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D26" s="32" t="inlineStr">
+      <c r="C26" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D26" s="42" t="inlineStr">
         <is>
           <t>Internal Search Click</t>
         </is>
       </c>
-      <c r="E26" s="32" t="inlineStr"/>
+      <c r="E26" s="42" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="30" t="n">
+      <c r="A27" s="40" t="n">
         <v>27</v>
       </c>
-      <c r="B27" s="30" t="inlineStr">
+      <c r="B27" s="40" t="inlineStr">
         <is>
           <t>Search Close Click</t>
         </is>
       </c>
-      <c r="C27" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D27" s="32" t="inlineStr">
+      <c r="C27" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D27" s="42" t="inlineStr">
         <is>
           <t>Search Close Click</t>
         </is>
       </c>
-      <c r="E27" s="32" t="inlineStr"/>
+      <c r="E27" s="42" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="30" t="n">
+      <c r="A28" s="40" t="n">
         <v>28</v>
       </c>
-      <c r="B28" s="30" t="inlineStr">
+      <c r="B28" s="40" t="inlineStr">
         <is>
           <t>Video Pause</t>
         </is>
       </c>
-      <c r="C28" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D28" s="32" t="inlineStr">
+      <c r="C28" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D28" s="42" t="inlineStr">
         <is>
           <t>Video Pause</t>
         </is>
       </c>
-      <c r="E28" s="32" t="inlineStr"/>
+      <c r="E28" s="42" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="30" t="n">
+      <c r="A29" s="40" t="n">
         <v>29</v>
       </c>
-      <c r="B29" s="30" t="inlineStr">
+      <c r="B29" s="40" t="inlineStr">
         <is>
           <t>Tag Click</t>
         </is>
       </c>
-      <c r="C29" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D29" s="32" t="inlineStr">
+      <c r="C29" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D29" s="42" t="inlineStr">
         <is>
           <t>Related Tag Click Tracking</t>
         </is>
       </c>
-      <c r="E29" s="32" t="inlineStr"/>
+      <c r="E29" s="42" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="30" t="n">
+      <c r="A30" s="40" t="n">
         <v>30</v>
       </c>
-      <c r="B30" s="30" t="inlineStr">
+      <c r="B30" s="40" t="inlineStr">
         <is>
           <t>Cookie Consent Click</t>
         </is>
       </c>
-      <c r="C30" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D30" s="32" t="inlineStr">
+      <c r="C30" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D30" s="42" t="inlineStr">
         <is>
           <t>Consent Selection</t>
         </is>
       </c>
-      <c r="E30" s="32" t="inlineStr">
+      <c r="E30" s="42" t="inlineStr">
         <is>
           <t>value from: Consent: Click Count</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="30" t="n">
+      <c r="A31" s="40" t="n">
         <v>31</v>
       </c>
-      <c r="B31" s="30" t="inlineStr">
+      <c r="B31" s="40" t="inlineStr">
         <is>
           <t>Map Zoom Out</t>
         </is>
       </c>
-      <c r="C31" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D31" s="32" t="inlineStr">
+      <c r="C31" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D31" s="42" t="inlineStr">
         <is>
           <t>Map Zoom Out</t>
         </is>
       </c>
-      <c r="E31" s="32" t="inlineStr"/>
+      <c r="E31" s="42" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="30" t="n">
+      <c r="A32" s="40" t="n">
         <v>32</v>
       </c>
-      <c r="B32" s="30" t="inlineStr">
+      <c r="B32" s="40" t="inlineStr">
         <is>
           <t>Map Button Click</t>
         </is>
       </c>
-      <c r="C32" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D32" s="32" t="inlineStr">
+      <c r="C32" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D32" s="42" t="inlineStr">
         <is>
           <t>Map Button Click</t>
         </is>
       </c>
-      <c r="E32" s="32" t="inlineStr"/>
+      <c r="E32" s="42" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="30" t="n">
+      <c r="A33" s="40" t="n">
         <v>33</v>
       </c>
-      <c r="B33" s="30" t="inlineStr">
+      <c r="B33" s="40" t="inlineStr">
         <is>
           <t>Map Button Close</t>
         </is>
       </c>
-      <c r="C33" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D33" s="32" t="inlineStr">
+      <c r="C33" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D33" s="42" t="inlineStr">
         <is>
           <t>Map Button Close</t>
         </is>
       </c>
-      <c r="E33" s="32" t="inlineStr"/>
+      <c r="E33" s="42" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="30" t="n">
+      <c r="A34" s="40" t="n">
         <v>34</v>
       </c>
-      <c r="B34" s="30" t="inlineStr">
+      <c r="B34" s="40" t="inlineStr">
         <is>
           <t>Map Zoom In</t>
         </is>
       </c>
-      <c r="C34" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D34" s="32" t="inlineStr">
+      <c r="C34" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D34" s="42" t="inlineStr">
         <is>
           <t>Map Zoom In</t>
         </is>
       </c>
-      <c r="E34" s="32" t="inlineStr"/>
+      <c r="E34" s="42" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="42" t="n">
+      <c r="A35" s="52" t="n">
         <v>35</v>
       </c>
-      <c r="B35" s="42" t="inlineStr">
+      <c r="B35" s="52" t="inlineStr">
         <is>
           <t>Audio Start</t>
         </is>
       </c>
-      <c r="C35" s="43" t="inlineStr">
+      <c r="C35" s="53" t="inlineStr">
         <is>
           <t>Not implemented (never built)</t>
         </is>
       </c>
-      <c r="D35" s="44" t="inlineStr">
+      <c r="D35" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E35" s="44" t="inlineStr">
+      <c r="E35" s="54" t="inlineStr">
         <is>
           <t>AUDIO event — never implemented in the old Launch property.</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="42" t="n">
+      <c r="A36" s="52" t="n">
         <v>36</v>
       </c>
-      <c r="B36" s="42" t="inlineStr">
+      <c r="B36" s="52" t="inlineStr">
         <is>
           <t>Audio Complete</t>
         </is>
       </c>
-      <c r="C36" s="43" t="inlineStr">
+      <c r="C36" s="53" t="inlineStr">
         <is>
           <t>Not implemented (never built)</t>
         </is>
       </c>
-      <c r="D36" s="44" t="inlineStr">
+      <c r="D36" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E36" s="44" t="inlineStr">
+      <c r="E36" s="54" t="inlineStr">
         <is>
           <t>AUDIO event — never implemented in the old Launch property.</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="42" t="n">
+      <c r="A37" s="52" t="n">
         <v>37</v>
       </c>
-      <c r="B37" s="42" t="inlineStr">
+      <c r="B37" s="52" t="inlineStr">
         <is>
           <t>Audio Milestone 25%</t>
         </is>
       </c>
-      <c r="C37" s="43" t="inlineStr">
+      <c r="C37" s="53" t="inlineStr">
         <is>
           <t>Not implemented (never built)</t>
         </is>
       </c>
-      <c r="D37" s="44" t="inlineStr">
+      <c r="D37" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E37" s="44" t="inlineStr">
+      <c r="E37" s="54" t="inlineStr">
         <is>
           <t>AUDIO event — never implemented in the old Launch property.</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="42" t="n">
+      <c r="A38" s="52" t="n">
         <v>38</v>
       </c>
-      <c r="B38" s="42" t="inlineStr">
+      <c r="B38" s="52" t="inlineStr">
         <is>
           <t>Audio Milestone 50%</t>
         </is>
       </c>
-      <c r="C38" s="43" t="inlineStr">
+      <c r="C38" s="53" t="inlineStr">
         <is>
           <t>Not implemented (never built)</t>
         </is>
       </c>
-      <c r="D38" s="44" t="inlineStr">
+      <c r="D38" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E38" s="44" t="inlineStr">
+      <c r="E38" s="54" t="inlineStr">
         <is>
           <t>AUDIO event — never implemented in the old Launch property.</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="42" t="n">
+      <c r="A39" s="52" t="n">
         <v>39</v>
       </c>
-      <c r="B39" s="42" t="inlineStr">
+      <c r="B39" s="52" t="inlineStr">
         <is>
           <t>Audio Milestone 75%</t>
         </is>
       </c>
-      <c r="C39" s="43" t="inlineStr">
+      <c r="C39" s="53" t="inlineStr">
         <is>
           <t>Not implemented (never built)</t>
         </is>
       </c>
-      <c r="D39" s="44" t="inlineStr">
+      <c r="D39" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E39" s="44" t="inlineStr">
+      <c r="E39" s="54" t="inlineStr">
         <is>
           <t>AUDIO event — never implemented in the old Launch property.</t>
         </is>
@@ -4326,7 +4729,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4342,1348 +4745,1348 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="29" t="inlineStr">
+      <c r="A1" s="39" t="inlineStr">
         <is>
           <t>Data Element</t>
         </is>
       </c>
-      <c r="B1" s="29" t="inlineStr">
+      <c r="B1" s="39" t="inlineStr">
         <is>
           <t>Feeds Variable(s)</t>
         </is>
       </c>
-      <c r="C1" s="29" t="inlineStr">
+      <c r="C1" s="39" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="D1" s="29" t="inlineStr">
+      <c r="D1" s="39" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="45" t="inlineStr">
+      <c r="A2" s="55" t="inlineStr">
         <is>
           <t>Article: Content Type</t>
         </is>
       </c>
-      <c r="B2" s="45" t="inlineStr">
+      <c r="B2" s="55" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C2" s="46" t="inlineStr">
+      <c r="C2" s="56" t="inlineStr">
         <is>
           <t>Not wired (orphan element)</t>
         </is>
       </c>
-      <c r="D2" s="47" t="inlineStr">
+      <c r="D2" s="57" t="inlineStr">
         <is>
           <t>For the excluded (never-published) Article Interaction Tracking rule. Activates only if Article tracking is revived.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="45" t="inlineStr">
+      <c r="A3" s="55" t="inlineStr">
         <is>
           <t>Article: Name</t>
         </is>
       </c>
-      <c r="B3" s="45" t="inlineStr">
+      <c r="B3" s="55" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C3" s="46" t="inlineStr">
+      <c r="C3" s="56" t="inlineStr">
         <is>
           <t>Not wired (orphan element)</t>
         </is>
       </c>
-      <c r="D3" s="47" t="inlineStr">
+      <c r="D3" s="57" t="inlineStr">
         <is>
           <t>For the excluded (never-published) Article Interaction Tracking rule. Activates only if Article tracking is revived.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="30" t="inlineStr">
+      <c r="A4" s="40" t="inlineStr">
         <is>
           <t>Campaign: External</t>
         </is>
       </c>
-      <c r="B4" s="30" t="inlineStr">
+      <c r="B4" s="40" t="inlineStr">
         <is>
           <t>s.campaign</t>
         </is>
       </c>
-      <c r="C4" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D4" s="32" t="inlineStr"/>
+      <c r="C4" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D4" s="42" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="33" t="inlineStr">
+      <c r="A5" s="43" t="inlineStr">
         <is>
           <t>Campaign: Internal</t>
         </is>
       </c>
-      <c r="B5" s="33" t="inlineStr">
+      <c r="B5" s="43" t="inlineStr">
         <is>
           <t>eVar5 (Internal Campaign)</t>
         </is>
       </c>
-      <c r="C5" s="34" t="inlineStr">
+      <c r="C5" s="44" t="inlineStr">
         <is>
           <t>No data (element is a no-op)</t>
         </is>
       </c>
-      <c r="D5" s="35" t="inlineStr">
+      <c r="D5" s="45" t="inlineStr">
         <is>
           <t>Returns no value (no-op) — the variable it feeds never populates. Decision needed.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="30" t="inlineStr">
+      <c r="A6" s="40" t="inlineStr">
         <is>
           <t>Campaign: Internal Count</t>
         </is>
       </c>
-      <c r="B6" s="30" t="inlineStr">
+      <c r="B6" s="40" t="inlineStr">
         <is>
           <t>event4 value</t>
         </is>
       </c>
-      <c r="C6" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D6" s="32" t="inlineStr"/>
+      <c r="C6" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D6" s="42" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="30" t="inlineStr">
+      <c r="A7" s="40" t="inlineStr">
         <is>
           <t>Consent: Click Count</t>
         </is>
       </c>
-      <c r="B7" s="30" t="inlineStr">
+      <c r="B7" s="40" t="inlineStr">
         <is>
           <t>event30 value</t>
         </is>
       </c>
-      <c r="C7" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D7" s="32" t="inlineStr"/>
+      <c r="C7" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D7" s="42" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="30" t="inlineStr">
+      <c r="A8" s="40" t="inlineStr">
         <is>
           <t>Consent: Selected</t>
         </is>
       </c>
-      <c r="B8" s="30" t="inlineStr">
+      <c r="B8" s="40" t="inlineStr">
         <is>
           <t>eVar48 (Cookie Consent Selection)</t>
         </is>
       </c>
-      <c r="C8" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D8" s="32" t="inlineStr"/>
+      <c r="C8" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D8" s="42" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="30" t="inlineStr">
+      <c r="A9" s="40" t="inlineStr">
         <is>
           <t>Content: Category</t>
         </is>
       </c>
-      <c r="B9" s="30" t="inlineStr">
+      <c r="B9" s="40" t="inlineStr">
         <is>
           <t>eVar29 (Category)</t>
         </is>
       </c>
-      <c r="C9" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D9" s="32" t="inlineStr"/>
+      <c r="C9" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D9" s="42" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="30" t="inlineStr">
+      <c r="A10" s="40" t="inlineStr">
         <is>
           <t>Content: Hidden Tags</t>
         </is>
       </c>
-      <c r="B10" s="30" t="inlineStr">
+      <c r="B10" s="40" t="inlineStr">
         <is>
           <t>list2 (list)</t>
         </is>
       </c>
-      <c r="C10" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D10" s="32" t="inlineStr"/>
+      <c r="C10" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D10" s="42" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="30" t="inlineStr">
+      <c r="A11" s="40" t="inlineStr">
         <is>
           <t>Content: Publish Date</t>
         </is>
       </c>
-      <c r="B11" s="30" t="inlineStr">
+      <c r="B11" s="40" t="inlineStr">
         <is>
           <t>eVar25 (Publish Date)</t>
         </is>
       </c>
-      <c r="C11" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D11" s="32" t="inlineStr"/>
+      <c r="C11" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D11" s="42" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="30" t="inlineStr">
+      <c r="A12" s="40" t="inlineStr">
         <is>
           <t>Content: Tags</t>
         </is>
       </c>
-      <c r="B12" s="30" t="inlineStr">
+      <c r="B12" s="40" t="inlineStr">
         <is>
           <t>eVar30 (Tag Text)</t>
         </is>
       </c>
-      <c r="C12" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D12" s="32" t="inlineStr"/>
+      <c r="C12" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D12" s="42" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="30" t="inlineStr">
+      <c r="A13" s="40" t="inlineStr">
         <is>
           <t>Content: Type</t>
         </is>
       </c>
-      <c r="B13" s="30" t="inlineStr">
+      <c r="B13" s="40" t="inlineStr">
         <is>
           <t>eVar9 (Content Type)</t>
         </is>
       </c>
-      <c r="C13" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D13" s="32" t="inlineStr"/>
+      <c r="C13" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D13" s="42" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="30" t="inlineStr">
+      <c r="A14" s="40" t="inlineStr">
         <is>
           <t>Core: Clean URL</t>
         </is>
       </c>
-      <c r="B14" s="30" t="inlineStr">
+      <c r="B14" s="40" t="inlineStr">
         <is>
           <t>prop5 (Clean URL)</t>
         </is>
       </c>
-      <c r="C14" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D14" s="32" t="inlineStr"/>
+      <c r="C14" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D14" s="42" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="30" t="inlineStr">
+      <c r="A15" s="40" t="inlineStr">
         <is>
           <t>Core: Page Query String</t>
         </is>
       </c>
-      <c r="B15" s="30" t="inlineStr">
+      <c r="B15" s="40" t="inlineStr">
         <is>
           <t>eVar13 (Page Query String)</t>
         </is>
       </c>
-      <c r="C15" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D15" s="32" t="inlineStr"/>
+      <c r="C15" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D15" s="42" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="30" t="inlineStr">
+      <c r="A16" s="40" t="inlineStr">
         <is>
           <t>Core: Referrer</t>
         </is>
       </c>
-      <c r="B16" s="30" t="inlineStr">
+      <c r="B16" s="40" t="inlineStr">
         <is>
           <t>prop2 (Referrer); s.referrer</t>
         </is>
       </c>
-      <c r="C16" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D16" s="32" t="inlineStr"/>
+      <c r="C16" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D16" s="42" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="30" t="inlineStr">
+      <c r="A17" s="40" t="inlineStr">
         <is>
           <t>Core: Timestamp</t>
         </is>
       </c>
-      <c r="B17" s="30" t="inlineStr">
+      <c r="B17" s="40" t="inlineStr">
         <is>
           <t>prop3 (Time Stamp)</t>
         </is>
       </c>
-      <c r="C17" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D17" s="32" t="inlineStr"/>
+      <c r="C17" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D17" s="42" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="30" t="inlineStr">
+      <c r="A18" s="40" t="inlineStr">
         <is>
           <t>File: Name</t>
         </is>
       </c>
-      <c r="B18" s="30" t="inlineStr">
+      <c r="B18" s="40" t="inlineStr">
         <is>
           <t>eVar33 (File Name)</t>
         </is>
       </c>
-      <c r="C18" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D18" s="32" t="inlineStr"/>
+      <c r="C18" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D18" s="42" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="30" t="inlineStr">
+      <c r="A19" s="40" t="inlineStr">
         <is>
           <t>File: Type</t>
         </is>
       </c>
-      <c r="B19" s="30" t="inlineStr">
+      <c r="B19" s="40" t="inlineStr">
         <is>
           <t>eVar34 (File Type)</t>
         </is>
       </c>
-      <c r="C19" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D19" s="32" t="inlineStr"/>
+      <c r="C19" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D19" s="42" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="45" t="inlineStr">
+      <c r="A20" s="55" t="inlineStr">
         <is>
           <t>File: URL</t>
         </is>
       </c>
-      <c r="B20" s="45" t="inlineStr">
+      <c r="B20" s="55" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C20" s="46" t="inlineStr">
+      <c r="C20" s="56" t="inlineStr">
         <is>
           <t>Not wired (orphan element)</t>
         </is>
       </c>
-      <c r="D20" s="47" t="inlineStr">
+      <c r="D20" s="57" t="inlineStr">
         <is>
           <t>File downloads capture Name + Type; URL is carried but not sent.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="30" t="inlineStr">
+      <c r="A21" s="40" t="inlineStr">
         <is>
           <t>Form: Error Name</t>
         </is>
       </c>
-      <c r="B21" s="30" t="inlineStr">
+      <c r="B21" s="40" t="inlineStr">
         <is>
           <t>list1 (list)</t>
         </is>
       </c>
-      <c r="C21" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D21" s="32" t="inlineStr"/>
+      <c r="C21" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D21" s="42" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="30" t="inlineStr">
+      <c r="A22" s="40" t="inlineStr">
         <is>
           <t>Form: Location</t>
         </is>
       </c>
-      <c r="B22" s="30" t="inlineStr">
+      <c r="B22" s="40" t="inlineStr">
         <is>
           <t>eVar19 (Email Registration Location)</t>
         </is>
       </c>
-      <c r="C22" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D22" s="32" t="inlineStr"/>
+      <c r="C22" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D22" s="42" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="30" t="inlineStr">
+      <c r="A23" s="40" t="inlineStr">
         <is>
           <t>Form: Name</t>
         </is>
       </c>
-      <c r="B23" s="30" t="inlineStr">
+      <c r="B23" s="40" t="inlineStr">
         <is>
           <t>eVar10 (Form Name)</t>
         </is>
       </c>
-      <c r="C23" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D23" s="32" t="inlineStr"/>
+      <c r="C23" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D23" s="42" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="30" t="inlineStr">
+      <c r="A24" s="40" t="inlineStr">
         <is>
           <t>Geo: Country</t>
         </is>
       </c>
-      <c r="B24" s="30" t="inlineStr">
+      <c r="B24" s="40" t="inlineStr">
         <is>
           <t>eVar47 (Country Code)</t>
         </is>
       </c>
-      <c r="C24" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D24" s="32" t="inlineStr"/>
+      <c r="C24" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D24" s="42" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="30" t="inlineStr">
+      <c r="A25" s="40" t="inlineStr">
         <is>
           <t>Geo: Language</t>
         </is>
       </c>
-      <c r="B25" s="30" t="inlineStr">
+      <c r="B25" s="40" t="inlineStr">
         <is>
           <t>eVar18 (Language)</t>
         </is>
       </c>
-      <c r="C25" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D25" s="32" t="inlineStr"/>
+      <c r="C25" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D25" s="42" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="30" t="inlineStr">
+      <c r="A26" s="40" t="inlineStr">
         <is>
           <t>Geo: Locale</t>
         </is>
       </c>
-      <c r="B26" s="30" t="inlineStr">
+      <c r="B26" s="40" t="inlineStr">
         <is>
           <t>prop20 (Locale)</t>
         </is>
       </c>
-      <c r="C26" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D26" s="32" t="inlineStr"/>
+      <c r="C26" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D26" s="42" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="45" t="inlineStr">
+      <c r="A27" s="55" t="inlineStr">
         <is>
           <t>Link: Amazon Redirect</t>
         </is>
       </c>
-      <c r="B27" s="45" t="inlineStr">
+      <c r="B27" s="55" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C27" s="46" t="inlineStr">
+      <c r="C27" s="56" t="inlineStr">
         <is>
           <t>Not wired (orphan element)</t>
         </is>
       </c>
-      <c r="D27" s="47" t="inlineStr">
+      <c r="D27" s="57" t="inlineStr">
         <is>
           <t>Not sent — eVar28 (labeled "Amazon Redirect Link") is fed by Link: Redirect Text instead. Possible pre-existing mislabel.</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="30" t="inlineStr">
+      <c r="A28" s="40" t="inlineStr">
         <is>
           <t>Link: CTA Button Name</t>
         </is>
       </c>
-      <c r="B28" s="30" t="inlineStr">
+      <c r="B28" s="40" t="inlineStr">
         <is>
           <t>eVar22 (CTA Button Text)</t>
         </is>
       </c>
-      <c r="C28" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D28" s="32" t="inlineStr"/>
+      <c r="C28" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D28" s="42" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="30" t="inlineStr">
+      <c r="A29" s="40" t="inlineStr">
         <is>
           <t>Link: Destination</t>
         </is>
       </c>
-      <c r="B29" s="30" t="inlineStr">
+      <c r="B29" s="40" t="inlineStr">
         <is>
           <t>eVar23 (Destination Link)</t>
         </is>
       </c>
-      <c r="C29" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D29" s="32" t="inlineStr"/>
+      <c r="C29" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D29" s="42" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="30" t="inlineStr">
+      <c r="A30" s="40" t="inlineStr">
         <is>
           <t>Link: Menu Name</t>
         </is>
       </c>
-      <c r="B30" s="30" t="inlineStr">
+      <c r="B30" s="40" t="inlineStr">
         <is>
           <t>eVar24 (Menu Link)</t>
         </is>
       </c>
-      <c r="C30" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D30" s="32" t="inlineStr"/>
+      <c r="C30" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D30" s="42" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="30" t="inlineStr">
+      <c r="A31" s="40" t="inlineStr">
         <is>
           <t>Link: More Amazon News</t>
         </is>
       </c>
-      <c r="B31" s="30" t="inlineStr">
+      <c r="B31" s="40" t="inlineStr">
         <is>
           <t>eVar44 (More Amazon News Title)</t>
         </is>
       </c>
-      <c r="C31" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D31" s="32" t="inlineStr"/>
+      <c r="C31" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D31" s="42" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="45" t="inlineStr">
+      <c r="A32" s="55" t="inlineStr">
         <is>
           <t>Link: Name</t>
         </is>
       </c>
-      <c r="B32" s="45" t="inlineStr">
+      <c r="B32" s="55" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C32" s="46" t="inlineStr">
+      <c r="C32" s="56" t="inlineStr">
         <is>
           <t>Not wired (orphan element)</t>
         </is>
       </c>
-      <c r="D32" s="47" t="inlineStr">
+      <c r="D32" s="57" t="inlineStr">
         <is>
           <t>Generic link name — carried but not wired to any variable.</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="30" t="inlineStr">
+      <c r="A33" s="40" t="inlineStr">
         <is>
           <t>Link: Redirect Text</t>
         </is>
       </c>
-      <c r="B33" s="30" t="inlineStr">
+      <c r="B33" s="40" t="inlineStr">
         <is>
           <t>eVar21 (Redirect Link); eVar28 (Amazon Redirect Link)</t>
         </is>
       </c>
-      <c r="C33" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D33" s="32" t="inlineStr"/>
+      <c r="C33" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D33" s="42" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="30" t="inlineStr">
+      <c r="A34" s="40" t="inlineStr">
         <is>
           <t>Link: Related Tag</t>
         </is>
       </c>
-      <c r="B34" s="30" t="inlineStr">
+      <c r="B34" s="40" t="inlineStr">
         <is>
           <t>eVar43 (Related Tag Text)</t>
         </is>
       </c>
-      <c r="C34" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D34" s="32" t="inlineStr"/>
+      <c r="C34" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D34" s="42" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="30" t="inlineStr">
+      <c r="A35" s="40" t="inlineStr">
         <is>
           <t>Link: Related Tag URL</t>
         </is>
       </c>
-      <c r="B35" s="30" t="inlineStr">
+      <c r="B35" s="40" t="inlineStr">
         <is>
           <t>eVar46 (Related Tags Link)</t>
         </is>
       </c>
-      <c r="C35" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D35" s="32" t="inlineStr"/>
+      <c r="C35" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D35" s="42" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="30" t="inlineStr">
+      <c r="A36" s="40" t="inlineStr">
         <is>
           <t>Link: Stories Text</t>
         </is>
       </c>
-      <c r="B36" s="30" t="inlineStr">
+      <c r="B36" s="40" t="inlineStr">
         <is>
           <t>eVar45 (Stories Title)</t>
         </is>
       </c>
-      <c r="C36" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D36" s="32" t="inlineStr"/>
+      <c r="C36" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D36" s="42" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="30" t="inlineStr">
+      <c r="A37" s="40" t="inlineStr">
         <is>
           <t>Map: Button Name</t>
         </is>
       </c>
-      <c r="B37" s="30" t="inlineStr">
+      <c r="B37" s="40" t="inlineStr">
         <is>
           <t>eVar50 (Map Button Name)</t>
         </is>
       </c>
-      <c r="C37" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D37" s="32" t="inlineStr"/>
+      <c r="C37" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D37" s="42" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="30" t="inlineStr">
+      <c r="A38" s="40" t="inlineStr">
         <is>
           <t>Map: Name</t>
         </is>
       </c>
-      <c r="B38" s="30" t="inlineStr">
+      <c r="B38" s="40" t="inlineStr">
         <is>
           <t>eVar49 (Map Name)</t>
         </is>
       </c>
-      <c r="C38" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D38" s="32" t="inlineStr"/>
+      <c r="C38" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D38" s="42" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="30" t="inlineStr">
+      <c r="A39" s="40" t="inlineStr">
         <is>
           <t>News: Filter</t>
         </is>
       </c>
-      <c r="B39" s="30" t="inlineStr">
+      <c r="B39" s="40" t="inlineStr">
         <is>
           <t>eVar27 (Filter)</t>
         </is>
       </c>
-      <c r="C39" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D39" s="32" t="inlineStr"/>
+      <c r="C39" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D39" s="42" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="30" t="inlineStr">
+      <c r="A40" s="40" t="inlineStr">
         <is>
           <t>Page: Error</t>
         </is>
       </c>
-      <c r="B40" s="30" t="inlineStr">
+      <c r="B40" s="40" t="inlineStr">
         <is>
           <t>list1 (list); prop19 (Site Error)</t>
         </is>
       </c>
-      <c r="C40" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D40" s="32" t="inlineStr"/>
+      <c r="C40" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D40" s="42" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="30" t="inlineStr">
+      <c r="A41" s="40" t="inlineStr">
         <is>
           <t>Page: Name</t>
         </is>
       </c>
-      <c r="B41" s="30" t="inlineStr">
+      <c r="B41" s="40" t="inlineStr">
         <is>
           <t>eVar3 (Page Name); prop1 (Page Name); s.pageName</t>
         </is>
       </c>
-      <c r="C41" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D41" s="32" t="inlineStr"/>
+      <c r="C41" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D41" s="42" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="30" t="inlineStr">
+      <c r="A42" s="40" t="inlineStr">
         <is>
           <t>Page: Title</t>
         </is>
       </c>
-      <c r="B42" s="30" t="inlineStr">
+      <c r="B42" s="40" t="inlineStr">
         <is>
           <t>prop18 (Page Title); prop4 (Page Title)</t>
         </is>
       </c>
-      <c r="C42" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D42" s="32" t="inlineStr"/>
+      <c r="C42" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D42" s="42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="30" t="inlineStr">
+      <c r="A43" s="40" t="inlineStr">
         <is>
           <t>Page: URL</t>
         </is>
       </c>
-      <c r="B43" s="30" t="inlineStr">
+      <c r="B43" s="40" t="inlineStr">
         <is>
           <t>eVar12 (Page URL); prop12 (Page URL); s.pageURL</t>
         </is>
       </c>
-      <c r="C43" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D43" s="32" t="inlineStr"/>
+      <c r="C43" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D43" s="42" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="45" t="inlineStr">
+      <c r="A44" s="55" t="inlineStr">
         <is>
           <t>Page: View Count</t>
         </is>
       </c>
-      <c r="B44" s="45" t="inlineStr">
+      <c r="B44" s="55" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C44" s="46" t="inlineStr">
+      <c r="C44" s="56" t="inlineStr">
         <is>
           <t>Not wired (orphan element)</t>
         </is>
       </c>
-      <c r="D44" s="47" t="inlineStr">
+      <c r="D44" s="57" t="inlineStr">
         <is>
           <t>Reads pageLoaded.value; not assigned to any variable.</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="30" t="inlineStr">
+      <c r="A45" s="40" t="inlineStr">
         <is>
           <t>Plugin: Previous Page Name</t>
         </is>
       </c>
-      <c r="B45" s="30" t="inlineStr">
+      <c r="B45" s="40" t="inlineStr">
         <is>
           <t>eVar2 (Previous Page Name); prop11 (Previous Page Name)</t>
         </is>
       </c>
-      <c r="C45" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D45" s="32" t="inlineStr"/>
+      <c r="C45" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D45" s="42" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="30" t="inlineStr">
+      <c r="A46" s="40" t="inlineStr">
         <is>
           <t>Plugin: Repeat Vs New</t>
         </is>
       </c>
-      <c r="B46" s="30" t="inlineStr">
+      <c r="B46" s="40" t="inlineStr">
         <is>
           <t>prop16 (Repeat Vs New)</t>
         </is>
       </c>
-      <c r="C46" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D46" s="32" t="inlineStr"/>
+      <c r="C46" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D46" s="42" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="45" t="inlineStr">
+      <c r="A47" s="55" t="inlineStr">
         <is>
           <t>Plugin: Time Parting</t>
         </is>
       </c>
-      <c r="B47" s="45" t="inlineStr">
+      <c r="B47" s="55" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C47" s="46" t="inlineStr">
+      <c r="C47" s="56" t="inlineStr">
         <is>
           <t>Not wired (orphan element)</t>
         </is>
       </c>
-      <c r="D47" s="47" t="inlineStr">
+      <c r="D47" s="57" t="inlineStr">
         <is>
           <t>Time-parting plugin value; carried but not wired to any variable.</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="30" t="inlineStr">
+      <c r="A48" s="40" t="inlineStr">
         <is>
           <t>Plugin: Time Since Last Visit</t>
         </is>
       </c>
-      <c r="B48" s="30" t="inlineStr">
+      <c r="B48" s="40" t="inlineStr">
         <is>
           <t>prop15 (Time Since Last Visit)</t>
         </is>
       </c>
-      <c r="C48" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D48" s="32" t="inlineStr"/>
+      <c r="C48" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D48" s="42" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="30" t="inlineStr">
+      <c r="A49" s="40" t="inlineStr">
         <is>
           <t>Plugin: Visit Duration</t>
         </is>
       </c>
-      <c r="B49" s="30" t="inlineStr">
+      <c r="B49" s="40" t="inlineStr">
         <is>
           <t>eVar37 (Visit Duration); prop17 (Visit Duration)</t>
         </is>
       </c>
-      <c r="C49" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D49" s="32" t="inlineStr"/>
+      <c r="C49" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D49" s="42" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="30" t="inlineStr">
+      <c r="A50" s="40" t="inlineStr">
         <is>
           <t>Plugin: Visit Number</t>
         </is>
       </c>
-      <c r="B50" s="30" t="inlineStr">
+      <c r="B50" s="40" t="inlineStr">
         <is>
           <t>prop14 (Visit Number)</t>
         </is>
       </c>
-      <c r="C50" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D50" s="32" t="inlineStr"/>
+      <c r="C50" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D50" s="42" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="30" t="inlineStr">
+      <c r="A51" s="40" t="inlineStr">
         <is>
           <t>Scroll Depth</t>
         </is>
       </c>
-      <c r="B51" s="30" t="inlineStr">
+      <c r="B51" s="40" t="inlineStr">
         <is>
           <t>eVar20 (Scroll Depth)</t>
         </is>
       </c>
-      <c r="C51" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D51" s="32" t="inlineStr"/>
+      <c r="C51" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D51" s="42" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="45" t="inlineStr">
+      <c r="A52" s="55" t="inlineStr">
         <is>
           <t>Search: Filter</t>
         </is>
       </c>
-      <c r="B52" s="45" t="inlineStr">
+      <c r="B52" s="55" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C52" s="46" t="inlineStr">
+      <c r="C52" s="56" t="inlineStr">
         <is>
           <t>Not wired (orphan element)</t>
         </is>
       </c>
-      <c r="D52" s="47" t="inlineStr">
+      <c r="D52" s="57" t="inlineStr">
         <is>
           <t>Carried but not sent (eVar27 Filter is fed by News: Filter).</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="30" t="inlineStr">
+      <c r="A53" s="40" t="inlineStr">
         <is>
           <t>Search: Result Click Name</t>
         </is>
       </c>
-      <c r="B53" s="30" t="inlineStr">
+      <c r="B53" s="40" t="inlineStr">
         <is>
           <t>eVar32 (Search Result Selection)</t>
         </is>
       </c>
-      <c r="C53" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D53" s="32" t="inlineStr"/>
+      <c r="C53" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D53" s="42" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="30" t="inlineStr">
+      <c r="A54" s="40" t="inlineStr">
         <is>
           <t>Search: Result Page Type</t>
         </is>
       </c>
-      <c r="B54" s="30" t="inlineStr">
+      <c r="B54" s="40" t="inlineStr">
         <is>
           <t>eVar8 (Search Results Page Type)</t>
         </is>
       </c>
-      <c r="C54" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D54" s="32" t="inlineStr"/>
+      <c r="C54" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D54" s="42" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="30" t="inlineStr">
+      <c r="A55" s="40" t="inlineStr">
         <is>
           <t>Search: Results</t>
         </is>
       </c>
-      <c r="B55" s="30" t="inlineStr">
+      <c r="B55" s="40" t="inlineStr">
         <is>
           <t>eVar7 (# Search Results)</t>
         </is>
       </c>
-      <c r="C55" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D55" s="32" t="inlineStr"/>
+      <c r="C55" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D55" s="42" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="30" t="inlineStr">
+      <c r="A56" s="40" t="inlineStr">
         <is>
           <t>Search: Term</t>
         </is>
       </c>
-      <c r="B56" s="30" t="inlineStr">
+      <c r="B56" s="40" t="inlineStr">
         <is>
           <t>eVar6 (Internal Search Term)</t>
         </is>
       </c>
-      <c r="C56" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D56" s="32" t="inlineStr"/>
+      <c r="C56" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D56" s="42" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="30" t="inlineStr">
+      <c r="A57" s="40" t="inlineStr">
         <is>
           <t>Site: Domain</t>
         </is>
       </c>
-      <c r="B57" s="30" t="inlineStr">
+      <c r="B57" s="40" t="inlineStr">
         <is>
           <t>eVar1 (Domain)</t>
         </is>
       </c>
-      <c r="C57" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D57" s="32" t="inlineStr"/>
+      <c r="C57" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D57" s="42" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="30" t="inlineStr">
+      <c r="A58" s="40" t="inlineStr">
         <is>
           <t>Site: Section</t>
         </is>
       </c>
-      <c r="B58" s="30" t="inlineStr">
+      <c r="B58" s="40" t="inlineStr">
         <is>
           <t>eVar4 (Site Section); prop6 (Site Section); s.channel</t>
         </is>
       </c>
-      <c r="C58" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D58" s="32" t="inlineStr"/>
+      <c r="C58" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D58" s="42" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="30" t="inlineStr">
+      <c r="A59" s="40" t="inlineStr">
         <is>
           <t>Site: Section 2</t>
         </is>
       </c>
-      <c r="B59" s="30" t="inlineStr">
+      <c r="B59" s="40" t="inlineStr">
         <is>
           <t>prop7 (Site Section2)</t>
         </is>
       </c>
-      <c r="C59" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D59" s="32" t="inlineStr"/>
+      <c r="C59" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D59" s="42" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="30" t="inlineStr">
+      <c r="A60" s="40" t="inlineStr">
         <is>
           <t>Site: Section 3</t>
         </is>
       </c>
-      <c r="B60" s="30" t="inlineStr">
+      <c r="B60" s="40" t="inlineStr">
         <is>
           <t>prop8 (Site Section3)</t>
         </is>
       </c>
-      <c r="C60" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D60" s="32" t="inlineStr"/>
+      <c r="C60" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D60" s="42" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="30" t="inlineStr">
+      <c r="A61" s="40" t="inlineStr">
         <is>
           <t>Site: Section 4</t>
         </is>
       </c>
-      <c r="B61" s="30" t="inlineStr">
+      <c r="B61" s="40" t="inlineStr">
         <is>
           <t>prop9 (Site Section4)</t>
         </is>
       </c>
-      <c r="C61" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D61" s="32" t="inlineStr"/>
+      <c r="C61" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D61" s="42" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="30" t="inlineStr">
+      <c r="A62" s="40" t="inlineStr">
         <is>
           <t>Site: Section 5</t>
         </is>
       </c>
-      <c r="B62" s="30" t="inlineStr">
+      <c r="B62" s="40" t="inlineStr">
         <is>
           <t>prop10 (Site Section5)</t>
         </is>
       </c>
-      <c r="C62" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D62" s="32" t="inlineStr"/>
+      <c r="C62" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D62" s="42" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="30" t="inlineStr">
+      <c r="A63" s="40" t="inlineStr">
         <is>
           <t>Social: Interaction Info</t>
         </is>
       </c>
-      <c r="B63" s="30" t="inlineStr">
+      <c r="B63" s="40" t="inlineStr">
         <is>
           <t>eVar17 (Social Link Name)</t>
         </is>
       </c>
-      <c r="C63" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D63" s="32" t="inlineStr"/>
+      <c r="C63" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D63" s="42" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="30" t="inlineStr">
+      <c r="A64" s="40" t="inlineStr">
         <is>
           <t>UTM: Campaign</t>
         </is>
       </c>
-      <c r="B64" s="30" t="inlineStr">
+      <c r="B64" s="40" t="inlineStr">
         <is>
           <t>eVar41 (UTM Campaign)</t>
         </is>
       </c>
-      <c r="C64" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D64" s="32" t="inlineStr"/>
+      <c r="C64" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D64" s="42" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="30" t="inlineStr">
+      <c r="A65" s="40" t="inlineStr">
         <is>
           <t>UTM: Content</t>
         </is>
       </c>
-      <c r="B65" s="30" t="inlineStr">
+      <c r="B65" s="40" t="inlineStr">
         <is>
           <t>eVar40 (UTM Content)</t>
         </is>
       </c>
-      <c r="C65" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D65" s="32" t="inlineStr"/>
+      <c r="C65" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D65" s="42" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="30" t="inlineStr">
+      <c r="A66" s="40" t="inlineStr">
         <is>
           <t>UTM: Medium</t>
         </is>
       </c>
-      <c r="B66" s="30" t="inlineStr">
+      <c r="B66" s="40" t="inlineStr">
         <is>
           <t>eVar39 (UTM Medium)</t>
         </is>
       </c>
-      <c r="C66" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D66" s="32" t="inlineStr"/>
+      <c r="C66" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D66" s="42" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="30" t="inlineStr">
+      <c r="A67" s="40" t="inlineStr">
         <is>
           <t>UTM: Source</t>
         </is>
       </c>
-      <c r="B67" s="30" t="inlineStr">
+      <c r="B67" s="40" t="inlineStr">
         <is>
           <t>eVar38 (UTM Source)</t>
         </is>
       </c>
-      <c r="C67" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D67" s="32" t="inlineStr"/>
+      <c r="C67" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D67" s="42" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="30" t="inlineStr">
+      <c r="A68" s="40" t="inlineStr">
         <is>
           <t>UTM: Term</t>
         </is>
       </c>
-      <c r="B68" s="30" t="inlineStr">
+      <c r="B68" s="40" t="inlineStr">
         <is>
           <t>eVar42 (UTM Term)</t>
         </is>
       </c>
-      <c r="C68" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D68" s="32" t="inlineStr"/>
+      <c r="C68" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D68" s="42" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="45" t="inlineStr">
+      <c r="A69" s="55" t="inlineStr">
         <is>
           <t>User: Login ID</t>
         </is>
       </c>
-      <c r="B69" s="45" t="inlineStr">
+      <c r="B69" s="55" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C69" s="46" t="inlineStr">
+      <c r="C69" s="56" t="inlineStr">
         <is>
           <t>Not wired (orphan element)</t>
         </is>
       </c>
-      <c r="D69" s="47" t="inlineStr">
+      <c r="D69" s="57" t="inlineStr">
         <is>
           <t>Reads loginID from the data layer but no rule sends it and no eVar/prop is assigned. PII review needed.</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="33" t="inlineStr">
+      <c r="A70" s="43" t="inlineStr">
         <is>
           <t>User: Type</t>
         </is>
       </c>
-      <c r="B70" s="33" t="inlineStr">
+      <c r="B70" s="43" t="inlineStr">
         <is>
           <t>eVar15 (User Type)</t>
         </is>
       </c>
-      <c r="C70" s="34" t="inlineStr">
+      <c r="C70" s="44" t="inlineStr">
         <is>
           <t>No data (element is a no-op)</t>
         </is>
       </c>
-      <c r="D70" s="35" t="inlineStr">
+      <c r="D70" s="45" t="inlineStr">
         <is>
           <t>Returns no value (no-op) — the variable it feeds never populates. Decision needed.</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="30" t="inlineStr">
+      <c r="A71" s="40" t="inlineStr">
         <is>
           <t>Video: Name</t>
         </is>
       </c>
-      <c r="B71" s="30" t="inlineStr">
+      <c r="B71" s="40" t="inlineStr">
         <is>
           <t>eVar11 (Video Title)</t>
         </is>
       </c>
-      <c r="C71" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D71" s="32" t="inlineStr"/>
+      <c r="C71" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D71" s="42" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="30" t="inlineStr">
+      <c r="A72" s="40" t="inlineStr">
         <is>
           <t>Video: Type</t>
         </is>
       </c>
-      <c r="B72" s="30" t="inlineStr">
+      <c r="B72" s="40" t="inlineStr">
         <is>
           <t>eVar35 (Video Type)</t>
         </is>
       </c>
-      <c r="C72" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D72" s="32" t="inlineStr"/>
+      <c r="C72" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D72" s="42" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D72"/>
@@ -5691,7 +6094,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5709,124 +6112,124 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="29" t="inlineStr">
+      <c r="A1" s="39" t="inlineStr">
         <is>
           <t>List Var</t>
         </is>
       </c>
-      <c r="B1" s="29" t="inlineStr">
+      <c r="B1" s="39" t="inlineStr">
         <is>
           <t>Report Suite Name</t>
         </is>
       </c>
-      <c r="C1" s="29" t="inlineStr">
+      <c r="C1" s="39" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="D1" s="29" t="inlineStr">
+      <c r="D1" s="39" t="inlineStr">
         <is>
           <t>Data Element(s)</t>
         </is>
       </c>
-      <c r="E1" s="29" t="inlineStr">
+      <c r="E1" s="39" t="inlineStr">
         <is>
           <t>Sent By Rule(s)</t>
         </is>
       </c>
-      <c r="F1" s="29" t="inlineStr">
+      <c r="F1" s="39" t="inlineStr">
         <is>
           <t>Notes / Issue</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="30" t="inlineStr">
+      <c r="A2" s="40" t="inlineStr">
         <is>
           <t>list1</t>
         </is>
       </c>
-      <c r="B2" s="30" t="inlineStr">
+      <c r="B2" s="40" t="inlineStr">
         <is>
           <t>(config not captured — see note)</t>
         </is>
       </c>
-      <c r="C2" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D2" s="32" t="inlineStr">
+      <c r="C2" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D2" s="42" t="inlineStr">
         <is>
           <t>Form: Error Name; Page: Error</t>
         </is>
       </c>
-      <c r="E2" s="32" t="inlineStr">
+      <c r="E2" s="42" t="inlineStr">
         <is>
           <t>Form Error Tracking; Global Page Load Rule; Site Error</t>
         </is>
       </c>
-      <c r="F2" s="32" t="inlineStr">
+      <c r="F2" s="42" t="inlineStr">
         <is>
           <t>SHARED list: carries Form: Error Name + Page: Error from different rules (a unified error list). Parity with the source property — confirm with the analytics owner it is intended, not a collision.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="30" t="inlineStr">
+      <c r="A3" s="40" t="inlineStr">
         <is>
           <t>list2</t>
         </is>
       </c>
-      <c r="B3" s="30" t="inlineStr">
+      <c r="B3" s="40" t="inlineStr">
         <is>
           <t>(config not captured — see note)</t>
         </is>
       </c>
-      <c r="C3" s="31" t="inlineStr">
-        <is>
-          <t>Collected</t>
-        </is>
-      </c>
-      <c r="D3" s="32" t="inlineStr">
+      <c r="C3" s="41" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="D3" s="42" t="inlineStr">
         <is>
           <t>Content: Hidden Tags</t>
         </is>
       </c>
-      <c r="E3" s="32" t="inlineStr">
+      <c r="E3" s="42" t="inlineStr">
         <is>
           <t>Global Page Load Rule</t>
         </is>
       </c>
-      <c r="F3" s="32" t="inlineStr"/>
+      <c r="F3" s="42" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="39" t="inlineStr">
+      <c r="A4" s="49" t="inlineStr">
         <is>
           <t>list3</t>
         </is>
       </c>
-      <c r="B4" s="39" t="inlineStr">
+      <c r="B4" s="49" t="inlineStr">
         <is>
           <t>(config not captured)</t>
         </is>
       </c>
-      <c r="C4" s="40" t="inlineStr">
+      <c r="C4" s="50" t="inlineStr">
         <is>
           <t>Defined, old property never sent</t>
         </is>
       </c>
-      <c r="D4" s="41" t="inlineStr">
+      <c r="D4" s="51" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E4" s="41" t="inlineStr">
+      <c r="E4" s="51" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F4" s="41" t="inlineStr">
+      <c r="F4" s="51" t="inlineStr">
         <is>
           <t>Not populated by this build. Adobe supports list1-3; provide the report suite List Variables config (Admin &gt; Report Suite &gt; Edit Settings &gt; Conversion &gt; List Variables) to reconcile names/delimiters.</t>
         </is>
@@ -5838,7 +6241,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5856,362 +6259,362 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="29" t="inlineStr">
+      <c r="A1" s="39" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B1" s="29" t="inlineStr">
+      <c r="B1" s="39" t="inlineStr">
         <is>
           <t>Issue</t>
         </is>
       </c>
-      <c r="C1" s="29" t="inlineStr">
+      <c r="C1" s="39" t="inlineStr">
         <is>
           <t>Severity</t>
         </is>
       </c>
-      <c r="D1" s="29" t="inlineStr">
+      <c r="D1" s="39" t="inlineStr">
         <is>
           <t>Affected Variables / Elements</t>
         </is>
       </c>
-      <c r="E1" s="29" t="inlineStr">
+      <c r="E1" s="39" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="F1" s="29" t="inlineStr">
+      <c r="F1" s="39" t="inlineStr">
         <is>
           <t>Recommendation</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="48" t="n">
+      <c r="A2" s="58" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="48" t="inlineStr">
+      <c r="B2" s="58" t="inlineStr">
         <is>
           <t>User Type never collects</t>
         </is>
       </c>
-      <c r="C2" s="49" t="inlineStr">
+      <c r="C2" s="59" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="D2" s="49" t="inlineStr">
+      <c r="D2" s="59" t="inlineStr">
         <is>
           <t>eVar15 · User: Type</t>
         </is>
       </c>
-      <c r="E2" s="49" t="inlineStr">
+      <c r="E2" s="59" t="inlineStr">
         <is>
           <t>The User: Type element is a stub that returns an empty string, so eVar15 has never captured a value in the current property.</t>
         </is>
       </c>
-      <c r="F2" s="49" t="inlineStr">
+      <c r="F2" s="59" t="inlineStr">
         <is>
           <t>Confirm what defines "user type" (logged-in vs anonymous, subscriber tier, etc.) and where it lives, then implement — or exclude. See client email #1.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="48" t="n">
+      <c r="A3" s="58" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="48" t="inlineStr">
+      <c r="B3" s="58" t="inlineStr">
         <is>
           <t>Login ID orphan + PII</t>
         </is>
       </c>
-      <c r="C3" s="49" t="inlineStr">
+      <c r="C3" s="59" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="D3" s="49" t="inlineStr">
+      <c r="D3" s="59" t="inlineStr">
         <is>
           <t>User: Login ID (no eVar/prop)</t>
         </is>
       </c>
-      <c r="E3" s="49" t="inlineStr">
+      <c r="E3" s="59" t="inlineStr">
         <is>
           <t>The User: Login ID element reads loginID from the data layer, but no rule sends it and no report variable is assigned — it is never collected.</t>
         </is>
       </c>
-      <c r="F3" s="49" t="inlineStr">
+      <c r="F3" s="59" t="inlineStr">
         <is>
           <t>Confirm whether login ID is wanted and which variable holds it. If it can identify a person, hash before collection. See client email #2.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="48" t="n">
+      <c r="A4" s="58" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="48" t="inlineStr">
+      <c r="B4" s="58" t="inlineStr">
         <is>
           <t>Internal Campaign no-op</t>
         </is>
       </c>
-      <c r="C4" s="49" t="inlineStr">
+      <c r="C4" s="59" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="D4" s="49" t="inlineStr">
+      <c r="D4" s="59" t="inlineStr">
         <is>
           <t>eVar5 · event4 · Campaign: Internal</t>
         </is>
       </c>
-      <c r="E4" s="49" t="inlineStr">
+      <c r="E4" s="59" t="inlineStr">
         <is>
           <t>Campaign: Internal is console.log(); (returns undefined) — parity with the source, where eVar5/event4 have never populated. event4 is filtered out of the page view.</t>
         </is>
       </c>
-      <c r="F4" s="49" t="inlineStr">
+      <c r="F4" s="59" t="inlineStr">
         <is>
           <t>Keep as-is for parity, or supply the real internal-campaign parameter to activate eVar5/event4. Deferred by design.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="48" t="n">
+      <c r="A5" s="58" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="48" t="inlineStr">
+      <c r="B5" s="58" t="inlineStr">
         <is>
           <t>Audio feature not implemented</t>
         </is>
       </c>
-      <c r="C5" s="49" t="inlineStr">
+      <c r="C5" s="59" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="D5" s="49" t="inlineStr">
+      <c r="D5" s="59" t="inlineStr">
         <is>
           <t>eVar51-54 · event35-39</t>
         </is>
       </c>
-      <c r="E5" s="49" t="inlineStr">
+      <c r="E5" s="59" t="inlineStr">
         <is>
           <t>A complete audio tracking feature (Start/Complete/Milestones + Title/Action/Duration/% Played) is defined in the report suite but was NEVER implemented in the old Launch property. Video is implemented; audio is not.</t>
         </is>
       </c>
-      <c r="F5" s="49" t="inlineStr">
+      <c r="F5" s="59" t="inlineStr">
         <is>
           <t>Net-new scope if wanted — typically Web SDK media (streaming) collection, separate from data-layer rules. Scope + estimate separately. See client email #3.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="48" t="n">
+      <c r="A6" s="58" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="48" t="inlineStr">
+      <c r="B6" s="58" t="inlineStr">
         <is>
           <t>ECID not captured (by design)</t>
         </is>
       </c>
-      <c r="C6" s="49" t="inlineStr">
+      <c r="C6" s="59" t="inlineStr">
         <is>
           <t>Info</t>
         </is>
       </c>
-      <c r="D6" s="49" t="inlineStr">
+      <c r="D6" s="59" t="inlineStr">
         <is>
           <t>eVar14 · prop13</t>
         </is>
       </c>
-      <c r="E6" s="49" t="inlineStr">
+      <c r="E6" s="59" t="inlineStr">
         <is>
           <t>ECID is intentionally not written to an eVar/prop under Web SDK — the SDK manages identity natively. The source ECID element was a broken recursive stub (excluded).</t>
         </is>
       </c>
-      <c r="F6" s="49" t="inlineStr">
+      <c r="F6" s="59" t="inlineStr">
         <is>
           <t>No action — correct Web SDK design. Confirm the client does not specifically need ECID surfaced in a variable.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="48" t="n">
+      <c r="A7" s="58" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="48" t="inlineStr">
+      <c r="B7" s="58" t="inlineStr">
         <is>
           <t>event28 double-booked</t>
         </is>
       </c>
-      <c r="C7" s="49" t="inlineStr">
+      <c r="C7" s="59" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="D7" s="49" t="inlineStr">
+      <c r="D7" s="59" t="inlineStr">
         <is>
           <t>event28 (Video Pause + Article draft)</t>
         </is>
       </c>
-      <c r="E7" s="49" t="inlineStr">
+      <c r="E7" s="59" t="inlineStr">
         <is>
           <t>event28 is used by Video Pause (live) and by the excluded, never-published Article Interaction Tracking draft. Currently latent because the Article rule is excluded.</t>
         </is>
       </c>
-      <c r="F7" s="49" t="inlineStr">
+      <c r="F7" s="59" t="inlineStr">
         <is>
           <t>If Article tracking is ever revived, assign it a fresh event number so it does not collide with Video Pause.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="48" t="n">
+      <c r="A8" s="58" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="48" t="inlineStr">
+      <c r="B8" s="58" t="inlineStr">
         <is>
           <t>eVar28 label vs value</t>
         </is>
       </c>
-      <c r="C8" s="49" t="inlineStr">
+      <c r="C8" s="59" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="D8" s="49" t="inlineStr">
+      <c r="D8" s="59" t="inlineStr">
         <is>
           <t>eVar28 · Link: Redirect Text · Link: Amazon Redirect</t>
         </is>
       </c>
-      <c r="E8" s="49" t="inlineStr">
+      <c r="E8" s="59" t="inlineStr">
         <is>
           <t>eVar28 is labeled "Amazon Redirect Link" in the report suite but is fed by Link: Redirect Text (the redirect link TEXT). eVar21 (Redirect Link) is also fed by Link: Redirect Text. The Link: Amazon Redirect element is unused.</t>
         </is>
       </c>
-      <c r="F8" s="49" t="inlineStr">
+      <c r="F8" s="59" t="inlineStr">
         <is>
           <t>Carried as-is for parity. Analytics owner should confirm the intended eVar28 mapping (label vs value) — likely a pre-existing mislabel in the source.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="48" t="n">
+      <c r="A9" s="58" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="48" t="inlineStr">
+      <c r="B9" s="58" t="inlineStr">
         <is>
           <t>eVar26 duplicate label</t>
         </is>
       </c>
-      <c r="C9" s="49" t="inlineStr">
+      <c r="C9" s="59" t="inlineStr">
         <is>
           <t>Info</t>
         </is>
       </c>
-      <c r="D9" s="49" t="inlineStr">
+      <c r="D9" s="59" t="inlineStr">
         <is>
           <t>eVar26 (duplicate of eVar9)</t>
         </is>
       </c>
-      <c r="E9" s="49" t="inlineStr">
+      <c r="E9" s="59" t="inlineStr">
         <is>
           <t>eVar26 is labeled "Content Type", the same as eVar9. eVar9 is populated; eVar26 is not — it appears to be an unused duplicate.</t>
         </is>
       </c>
-      <c r="F9" s="49" t="inlineStr">
+      <c r="F9" s="59" t="inlineStr">
         <is>
           <t>No action needed, or repurpose eVar26 for a new dimension. Confirm with analytics owner.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="48" t="n">
+      <c r="A10" s="58" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="48" t="inlineStr">
+      <c r="B10" s="58" t="inlineStr">
         <is>
           <t>Orphan data elements</t>
         </is>
       </c>
-      <c r="C10" s="49" t="inlineStr">
+      <c r="C10" s="59" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="D10" s="49" t="inlineStr">
+      <c r="D10" s="59" t="inlineStr">
         <is>
           <t>9 elements (see Data Elements tab)</t>
         </is>
       </c>
-      <c r="E10" s="49" t="inlineStr">
+      <c r="E10" s="59" t="inlineStr">
         <is>
           <t>Nine carried elements are not wired to any variable: Article: Content Type/Name (excluded rule), File: URL, Link: Amazon Redirect, Link: Name, Page: View Count, Plugin: Time Parting, Search: Filter, User: Login ID.</t>
         </is>
       </c>
-      <c r="F10" s="49" t="inlineStr">
+      <c r="F10" s="59" t="inlineStr">
         <is>
           <t>Review use-or-remove. Most are harmless carry-overs; User: Login ID and Link: Amazon Redirect are called out separately (issues #2, #7).</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="48" t="n">
+      <c r="A11" s="58" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="48" t="inlineStr">
+      <c r="B11" s="58" t="inlineStr">
         <is>
           <t>list1 shared across error types</t>
         </is>
       </c>
-      <c r="C11" s="49" t="inlineStr">
+      <c r="C11" s="59" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="D11" s="49" t="inlineStr">
+      <c r="D11" s="59" t="inlineStr">
         <is>
           <t>list1 · Page: Error · Form: Error Name</t>
         </is>
       </c>
-      <c r="E11" s="49" t="inlineStr">
+      <c r="E11" s="59" t="inlineStr">
         <is>
           <t>list1 carries Site Error (page views + Site Error rule) AND Form Error Name (Form Error Tracking) — a unified error list. Carried from the source property (parity).</t>
         </is>
       </c>
-      <c r="F11" s="49" t="inlineStr">
+      <c r="F11" s="59" t="inlineStr">
         <is>
           <t>Confirm with the analytics owner that list1 is intended as a combined error list. Provide the report suite List Variables config to reconcile names/delimiters and confirm list3 status.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="48" t="n">
+      <c r="A12" s="58" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="48" t="inlineStr">
+      <c r="B12" s="58" t="inlineStr">
         <is>
           <t>Empty values omitted</t>
         </is>
       </c>
-      <c r="C12" s="49" t="inlineStr">
+      <c r="C12" s="59" t="inlineStr">
         <is>
           <t>Info</t>
         </is>
       </c>
-      <c r="D12" s="49" t="inlineStr">
+      <c r="D12" s="59" t="inlineStr">
         <is>
           <t>All payloads</t>
         </is>
       </c>
-      <c r="E12" s="49" t="inlineStr">
+      <c r="E12" s="59" t="inlineStr">
         <is>
           <t>The Web SDK build omits empty values, whereas the old XDM elements could emit empty strings. Beacons are cleaner but hit-level QA diffs will show absent-vs-empty differences.</t>
         </is>
       </c>
-      <c r="F12" s="49" t="inlineStr">
+      <c r="F12" s="59" t="inlineStr">
         <is>
           <t>Expected behavior — note for anyone comparing old vs new beacons during QA.</t>
         </is>
